--- a/src/main/resources/templates/summaryReportForm5.xlsx
+++ b/src/main/resources/templates/summaryReportForm5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{342326C8-5100-421E-9D3E-1A9B81C3B33A}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD654E5D-A0A3-4FDF-8E7B-11F759315ECF}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2205,47 +2205,7 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="10" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="6" fillId="2" borderId="31" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment vertical="center" wrapText="1"/>
       <protection locked="0"/>
@@ -2262,22 +2222,43 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2286,40 +2267,52 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2349,12 +2342,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2373,168 +2372,169 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2821,21 +2821,22 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="3" width="30.7109375" customWidth="1"/>
+    <col min="2" max="2" width="30.7109375" customWidth="1"/>
+    <col min="3" max="3" width="45.7109375" customWidth="1"/>
     <col min="4" max="7" width="16.7109375" customWidth="1"/>
     <col min="8" max="12" width="10.7109375" customWidth="1"/>
     <col min="13" max="210" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:210" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="81" t="s">
+      <c r="A1" s="95" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="81"/>
-      <c r="C1" s="81"/>
-      <c r="D1" s="81"/>
-      <c r="E1" s="81"/>
-      <c r="F1" s="81"/>
+      <c r="B1" s="95"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
       <c r="G1" s="18" t="s">
         <v>483</v>
       </c>
@@ -3256,255 +3257,255 @@
       <c r="HB2" s="7"/>
     </row>
     <row r="3" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="42" t="s">
+      <c r="A3" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="42" t="s">
+      <c r="B3" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="42" t="s">
+      <c r="C3" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="42" t="s">
+      <c r="D3" s="37" t="s">
         <v>476</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="37" t="s">
         <v>477</v>
       </c>
       <c r="G3" s="10"/>
-      <c r="H3" s="44" t="s">
+      <c r="H3" s="103" t="s">
         <v>478</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="45"/>
-      <c r="K3" s="45"/>
-      <c r="L3" s="46"/>
-      <c r="M3" s="37" t="s">
+      <c r="I3" s="104"/>
+      <c r="J3" s="104"/>
+      <c r="K3" s="104"/>
+      <c r="L3" s="105"/>
+      <c r="M3" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="37"/>
-      <c r="O3" s="37"/>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37"/>
-      <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="37"/>
-      <c r="W3" s="37"/>
-      <c r="X3" s="37"/>
-      <c r="Y3" s="37"/>
-      <c r="Z3" s="37"/>
-      <c r="AA3" s="37"/>
-      <c r="AB3" s="37"/>
-      <c r="AC3" s="37"/>
-      <c r="AD3" s="85"/>
-      <c r="AE3" s="85"/>
-      <c r="AF3" s="85"/>
-      <c r="AG3" s="85"/>
-      <c r="AH3" s="85"/>
-      <c r="AI3" s="85"/>
-      <c r="AJ3" s="85"/>
-      <c r="AK3" s="85"/>
-      <c r="AL3" s="85"/>
-      <c r="AM3" s="85"/>
-      <c r="AN3" s="37"/>
-      <c r="AO3" s="37"/>
-      <c r="AP3" s="37"/>
-      <c r="AQ3" s="37"/>
-      <c r="AR3" s="37"/>
+      <c r="N3" s="96"/>
+      <c r="O3" s="96"/>
+      <c r="P3" s="96"/>
+      <c r="Q3" s="96"/>
+      <c r="R3" s="96"/>
+      <c r="S3" s="96"/>
+      <c r="T3" s="96"/>
+      <c r="U3" s="96"/>
+      <c r="V3" s="96"/>
+      <c r="W3" s="96"/>
+      <c r="X3" s="96"/>
+      <c r="Y3" s="96"/>
+      <c r="Z3" s="96"/>
+      <c r="AA3" s="96"/>
+      <c r="AB3" s="96"/>
+      <c r="AC3" s="96"/>
+      <c r="AD3" s="97"/>
+      <c r="AE3" s="97"/>
+      <c r="AF3" s="97"/>
+      <c r="AG3" s="97"/>
+      <c r="AH3" s="97"/>
+      <c r="AI3" s="97"/>
+      <c r="AJ3" s="97"/>
+      <c r="AK3" s="97"/>
+      <c r="AL3" s="97"/>
+      <c r="AM3" s="97"/>
+      <c r="AN3" s="96"/>
+      <c r="AO3" s="96"/>
+      <c r="AP3" s="96"/>
+      <c r="AQ3" s="96"/>
+      <c r="AR3" s="96"/>
       <c r="AS3" s="11"/>
       <c r="AT3" s="11"/>
       <c r="AU3" s="11"/>
       <c r="AV3" s="11"/>
-      <c r="AW3" s="36" t="s">
+      <c r="AW3" s="98" t="s">
         <v>4</v>
       </c>
-      <c r="AX3" s="37"/>
-      <c r="AY3" s="37"/>
-      <c r="AZ3" s="37"/>
-      <c r="BA3" s="37"/>
-      <c r="BB3" s="37"/>
-      <c r="BC3" s="37"/>
-      <c r="BD3" s="37"/>
-      <c r="BE3" s="37"/>
-      <c r="BF3" s="37"/>
-      <c r="BG3" s="37"/>
-      <c r="BH3" s="37"/>
-      <c r="BI3" s="37"/>
-      <c r="BJ3" s="37"/>
-      <c r="BK3" s="37"/>
-      <c r="BL3" s="37"/>
-      <c r="BM3" s="37"/>
-      <c r="BN3" s="37"/>
-      <c r="BO3" s="37"/>
-      <c r="BP3" s="37"/>
-      <c r="BQ3" s="37"/>
-      <c r="BR3" s="37"/>
-      <c r="BS3" s="37"/>
-      <c r="BT3" s="37"/>
-      <c r="BU3" s="37"/>
-      <c r="BV3" s="37"/>
-      <c r="BW3" s="37"/>
-      <c r="BX3" s="37"/>
-      <c r="BY3" s="37"/>
-      <c r="BZ3" s="37"/>
-      <c r="CA3" s="37"/>
-      <c r="CB3" s="37"/>
-      <c r="CC3" s="37"/>
-      <c r="CD3" s="37"/>
-      <c r="CE3" s="37"/>
-      <c r="CF3" s="38"/>
-      <c r="CG3" s="36" t="s">
+      <c r="AX3" s="96"/>
+      <c r="AY3" s="96"/>
+      <c r="AZ3" s="96"/>
+      <c r="BA3" s="96"/>
+      <c r="BB3" s="96"/>
+      <c r="BC3" s="96"/>
+      <c r="BD3" s="96"/>
+      <c r="BE3" s="96"/>
+      <c r="BF3" s="96"/>
+      <c r="BG3" s="96"/>
+      <c r="BH3" s="96"/>
+      <c r="BI3" s="96"/>
+      <c r="BJ3" s="96"/>
+      <c r="BK3" s="96"/>
+      <c r="BL3" s="96"/>
+      <c r="BM3" s="96"/>
+      <c r="BN3" s="96"/>
+      <c r="BO3" s="96"/>
+      <c r="BP3" s="96"/>
+      <c r="BQ3" s="96"/>
+      <c r="BR3" s="96"/>
+      <c r="BS3" s="96"/>
+      <c r="BT3" s="96"/>
+      <c r="BU3" s="96"/>
+      <c r="BV3" s="96"/>
+      <c r="BW3" s="96"/>
+      <c r="BX3" s="96"/>
+      <c r="BY3" s="96"/>
+      <c r="BZ3" s="96"/>
+      <c r="CA3" s="96"/>
+      <c r="CB3" s="96"/>
+      <c r="CC3" s="96"/>
+      <c r="CD3" s="96"/>
+      <c r="CE3" s="96"/>
+      <c r="CF3" s="99"/>
+      <c r="CG3" s="98" t="s">
         <v>5</v>
       </c>
-      <c r="CH3" s="37"/>
-      <c r="CI3" s="37"/>
-      <c r="CJ3" s="37"/>
-      <c r="CK3" s="37"/>
-      <c r="CL3" s="37"/>
-      <c r="CM3" s="37"/>
-      <c r="CN3" s="37"/>
-      <c r="CO3" s="37"/>
-      <c r="CP3" s="37"/>
-      <c r="CQ3" s="37"/>
-      <c r="CR3" s="37"/>
-      <c r="CS3" s="37"/>
-      <c r="CT3" s="37"/>
-      <c r="CU3" s="37"/>
-      <c r="CV3" s="37"/>
-      <c r="CW3" s="37"/>
-      <c r="CX3" s="37"/>
-      <c r="CY3" s="37"/>
-      <c r="CZ3" s="37"/>
-      <c r="DA3" s="37"/>
-      <c r="DB3" s="37"/>
-      <c r="DC3" s="37"/>
-      <c r="DD3" s="37"/>
-      <c r="DE3" s="37"/>
-      <c r="DF3" s="37"/>
-      <c r="DG3" s="37"/>
-      <c r="DH3" s="37"/>
-      <c r="DI3" s="37"/>
-      <c r="DJ3" s="37"/>
-      <c r="DK3" s="37"/>
-      <c r="DL3" s="37"/>
-      <c r="DM3" s="37"/>
-      <c r="DN3" s="37"/>
-      <c r="DO3" s="37"/>
-      <c r="DP3" s="38"/>
-      <c r="DQ3" s="36" t="s">
+      <c r="CH3" s="96"/>
+      <c r="CI3" s="96"/>
+      <c r="CJ3" s="96"/>
+      <c r="CK3" s="96"/>
+      <c r="CL3" s="96"/>
+      <c r="CM3" s="96"/>
+      <c r="CN3" s="96"/>
+      <c r="CO3" s="96"/>
+      <c r="CP3" s="96"/>
+      <c r="CQ3" s="96"/>
+      <c r="CR3" s="96"/>
+      <c r="CS3" s="96"/>
+      <c r="CT3" s="96"/>
+      <c r="CU3" s="96"/>
+      <c r="CV3" s="96"/>
+      <c r="CW3" s="96"/>
+      <c r="CX3" s="96"/>
+      <c r="CY3" s="96"/>
+      <c r="CZ3" s="96"/>
+      <c r="DA3" s="96"/>
+      <c r="DB3" s="96"/>
+      <c r="DC3" s="96"/>
+      <c r="DD3" s="96"/>
+      <c r="DE3" s="96"/>
+      <c r="DF3" s="96"/>
+      <c r="DG3" s="96"/>
+      <c r="DH3" s="96"/>
+      <c r="DI3" s="96"/>
+      <c r="DJ3" s="96"/>
+      <c r="DK3" s="96"/>
+      <c r="DL3" s="96"/>
+      <c r="DM3" s="96"/>
+      <c r="DN3" s="96"/>
+      <c r="DO3" s="96"/>
+      <c r="DP3" s="99"/>
+      <c r="DQ3" s="98" t="s">
         <v>6</v>
       </c>
-      <c r="DR3" s="37"/>
-      <c r="DS3" s="37"/>
-      <c r="DT3" s="37"/>
-      <c r="DU3" s="37"/>
-      <c r="DV3" s="37"/>
-      <c r="DW3" s="37"/>
-      <c r="DX3" s="37"/>
-      <c r="DY3" s="37"/>
-      <c r="DZ3" s="37"/>
-      <c r="EA3" s="37"/>
-      <c r="EB3" s="37"/>
-      <c r="EC3" s="37"/>
-      <c r="ED3" s="37"/>
-      <c r="EE3" s="37"/>
-      <c r="EF3" s="37"/>
-      <c r="EG3" s="37"/>
-      <c r="EH3" s="37"/>
-      <c r="EI3" s="37"/>
-      <c r="EJ3" s="37"/>
-      <c r="EK3" s="37"/>
-      <c r="EL3" s="37"/>
-      <c r="EM3" s="37"/>
-      <c r="EN3" s="37"/>
-      <c r="EO3" s="37"/>
-      <c r="EP3" s="37"/>
-      <c r="EQ3" s="37"/>
-      <c r="ER3" s="37"/>
-      <c r="ES3" s="37"/>
-      <c r="ET3" s="37"/>
-      <c r="EU3" s="37"/>
-      <c r="EV3" s="37"/>
-      <c r="EW3" s="37"/>
-      <c r="EX3" s="37"/>
-      <c r="EY3" s="37"/>
-      <c r="EZ3" s="37"/>
-      <c r="FA3" s="37"/>
-      <c r="FB3" s="37"/>
-      <c r="FC3" s="37"/>
-      <c r="FD3" s="37"/>
-      <c r="FE3" s="37"/>
-      <c r="FF3" s="37"/>
-      <c r="FG3" s="37"/>
-      <c r="FH3" s="37"/>
-      <c r="FI3" s="37"/>
-      <c r="FJ3" s="37"/>
-      <c r="FK3" s="37"/>
-      <c r="FL3" s="39"/>
-      <c r="FM3" s="40" t="s">
+      <c r="DR3" s="96"/>
+      <c r="DS3" s="96"/>
+      <c r="DT3" s="96"/>
+      <c r="DU3" s="96"/>
+      <c r="DV3" s="96"/>
+      <c r="DW3" s="96"/>
+      <c r="DX3" s="96"/>
+      <c r="DY3" s="96"/>
+      <c r="DZ3" s="96"/>
+      <c r="EA3" s="96"/>
+      <c r="EB3" s="96"/>
+      <c r="EC3" s="96"/>
+      <c r="ED3" s="96"/>
+      <c r="EE3" s="96"/>
+      <c r="EF3" s="96"/>
+      <c r="EG3" s="96"/>
+      <c r="EH3" s="96"/>
+      <c r="EI3" s="96"/>
+      <c r="EJ3" s="96"/>
+      <c r="EK3" s="96"/>
+      <c r="EL3" s="96"/>
+      <c r="EM3" s="96"/>
+      <c r="EN3" s="96"/>
+      <c r="EO3" s="96"/>
+      <c r="EP3" s="96"/>
+      <c r="EQ3" s="96"/>
+      <c r="ER3" s="96"/>
+      <c r="ES3" s="96"/>
+      <c r="ET3" s="96"/>
+      <c r="EU3" s="96"/>
+      <c r="EV3" s="96"/>
+      <c r="EW3" s="96"/>
+      <c r="EX3" s="96"/>
+      <c r="EY3" s="96"/>
+      <c r="EZ3" s="96"/>
+      <c r="FA3" s="96"/>
+      <c r="FB3" s="96"/>
+      <c r="FC3" s="96"/>
+      <c r="FD3" s="96"/>
+      <c r="FE3" s="96"/>
+      <c r="FF3" s="96"/>
+      <c r="FG3" s="96"/>
+      <c r="FH3" s="96"/>
+      <c r="FI3" s="96"/>
+      <c r="FJ3" s="96"/>
+      <c r="FK3" s="96"/>
+      <c r="FL3" s="100"/>
+      <c r="FM3" s="101" t="s">
         <v>7</v>
       </c>
-      <c r="FN3" s="37"/>
-      <c r="FO3" s="37"/>
-      <c r="FP3" s="37"/>
-      <c r="FQ3" s="37"/>
-      <c r="FR3" s="37"/>
-      <c r="FS3" s="37"/>
-      <c r="FT3" s="37"/>
-      <c r="FU3" s="37"/>
-      <c r="FV3" s="37"/>
-      <c r="FW3" s="37"/>
-      <c r="FX3" s="37"/>
-      <c r="FY3" s="37"/>
-      <c r="FZ3" s="37"/>
-      <c r="GA3" s="37"/>
-      <c r="GB3" s="37"/>
-      <c r="GC3" s="37"/>
-      <c r="GD3" s="37"/>
-      <c r="GE3" s="37"/>
-      <c r="GF3" s="37"/>
-      <c r="GG3" s="37"/>
-      <c r="GH3" s="37"/>
-      <c r="GI3" s="37"/>
-      <c r="GJ3" s="37"/>
-      <c r="GK3" s="41" t="s">
+      <c r="FN3" s="96"/>
+      <c r="FO3" s="96"/>
+      <c r="FP3" s="96"/>
+      <c r="FQ3" s="96"/>
+      <c r="FR3" s="96"/>
+      <c r="FS3" s="96"/>
+      <c r="FT3" s="96"/>
+      <c r="FU3" s="96"/>
+      <c r="FV3" s="96"/>
+      <c r="FW3" s="96"/>
+      <c r="FX3" s="96"/>
+      <c r="FY3" s="96"/>
+      <c r="FZ3" s="96"/>
+      <c r="GA3" s="96"/>
+      <c r="GB3" s="96"/>
+      <c r="GC3" s="96"/>
+      <c r="GD3" s="96"/>
+      <c r="GE3" s="96"/>
+      <c r="GF3" s="96"/>
+      <c r="GG3" s="96"/>
+      <c r="GH3" s="96"/>
+      <c r="GI3" s="96"/>
+      <c r="GJ3" s="96"/>
+      <c r="GK3" s="102" t="s">
         <v>8</v>
       </c>
-      <c r="GL3" s="37"/>
-      <c r="GM3" s="37"/>
-      <c r="GN3" s="37"/>
-      <c r="GO3" s="37"/>
-      <c r="GP3" s="37"/>
-      <c r="GQ3" s="37"/>
-      <c r="GR3" s="37"/>
-      <c r="GS3" s="37"/>
-      <c r="GT3" s="37"/>
-      <c r="GU3" s="37"/>
-      <c r="GV3" s="37"/>
-      <c r="GW3" s="37"/>
-      <c r="GX3" s="37"/>
-      <c r="GY3" s="37"/>
-      <c r="GZ3" s="37"/>
-      <c r="HA3" s="37"/>
-      <c r="HB3" s="39"/>
+      <c r="GL3" s="96"/>
+      <c r="GM3" s="96"/>
+      <c r="GN3" s="96"/>
+      <c r="GO3" s="96"/>
+      <c r="GP3" s="96"/>
+      <c r="GQ3" s="96"/>
+      <c r="GR3" s="96"/>
+      <c r="GS3" s="96"/>
+      <c r="GT3" s="96"/>
+      <c r="GU3" s="96"/>
+      <c r="GV3" s="96"/>
+      <c r="GW3" s="96"/>
+      <c r="GX3" s="96"/>
+      <c r="GY3" s="96"/>
+      <c r="GZ3" s="96"/>
+      <c r="HA3" s="96"/>
+      <c r="HB3" s="100"/>
     </row>
     <row r="4" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="43"/>
-      <c r="B4" s="43"/>
-      <c r="C4" s="43"/>
-      <c r="D4" s="43"/>
+      <c r="A4" s="38"/>
+      <c r="B4" s="38"/>
+      <c r="C4" s="38"/>
+      <c r="D4" s="38"/>
       <c r="E4" s="12"/>
-      <c r="F4" s="43"/>
+      <c r="F4" s="38"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="47"/>
-      <c r="I4" s="48"/>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48"/>
-      <c r="L4" s="49"/>
-      <c r="M4" s="82" t="s">
+      <c r="H4" s="106"/>
+      <c r="I4" s="107"/>
+      <c r="J4" s="107"/>
+      <c r="K4" s="107"/>
+      <c r="L4" s="108"/>
+      <c r="M4" s="64" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="65"/>
@@ -3512,48 +3513,48 @@
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="66"/>
-      <c r="S4" s="69" t="s">
+      <c r="S4" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="69"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="69"/>
-      <c r="W4" s="69"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="56" t="s">
+      <c r="T4" s="70"/>
+      <c r="U4" s="70"/>
+      <c r="V4" s="70"/>
+      <c r="W4" s="70"/>
+      <c r="X4" s="70"/>
+      <c r="Y4" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="Z4" s="57"/>
-      <c r="AA4" s="70"/>
-      <c r="AB4" s="56" t="s">
+      <c r="Z4" s="56"/>
+      <c r="AA4" s="71"/>
+      <c r="AB4" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="AC4" s="57"/>
-      <c r="AD4" s="70"/>
-      <c r="AE4" s="73" t="s">
+      <c r="AC4" s="56"/>
+      <c r="AD4" s="71"/>
+      <c r="AE4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="AF4" s="73"/>
-      <c r="AG4" s="73"/>
-      <c r="AH4" s="73"/>
-      <c r="AI4" s="73"/>
-      <c r="AJ4" s="73"/>
-      <c r="AK4" s="73"/>
-      <c r="AL4" s="73"/>
-      <c r="AM4" s="73"/>
-      <c r="AN4" s="73" t="s">
+      <c r="AF4" s="54"/>
+      <c r="AG4" s="54"/>
+      <c r="AH4" s="54"/>
+      <c r="AI4" s="54"/>
+      <c r="AJ4" s="54"/>
+      <c r="AK4" s="54"/>
+      <c r="AL4" s="54"/>
+      <c r="AM4" s="54"/>
+      <c r="AN4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="AO4" s="73"/>
-      <c r="AP4" s="73"/>
-      <c r="AQ4" s="73"/>
-      <c r="AR4" s="73"/>
-      <c r="AS4" s="73"/>
-      <c r="AT4" s="56" t="s">
+      <c r="AO4" s="54"/>
+      <c r="AP4" s="54"/>
+      <c r="AQ4" s="54"/>
+      <c r="AR4" s="54"/>
+      <c r="AS4" s="54"/>
+      <c r="AT4" s="55" t="s">
         <v>56</v>
       </c>
-      <c r="AU4" s="57"/>
-      <c r="AV4" s="58"/>
+      <c r="AU4" s="56"/>
+      <c r="AV4" s="57"/>
       <c r="AW4" s="65" t="s">
         <v>9</v>
       </c>
@@ -3562,49 +3563,49 @@
       <c r="AZ4" s="65"/>
       <c r="BA4" s="65"/>
       <c r="BB4" s="66"/>
-      <c r="BC4" s="69" t="s">
+      <c r="BC4" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="BD4" s="69"/>
-      <c r="BE4" s="69"/>
-      <c r="BF4" s="69"/>
-      <c r="BG4" s="69"/>
-      <c r="BH4" s="69"/>
-      <c r="BI4" s="56" t="s">
+      <c r="BD4" s="70"/>
+      <c r="BE4" s="70"/>
+      <c r="BF4" s="70"/>
+      <c r="BG4" s="70"/>
+      <c r="BH4" s="70"/>
+      <c r="BI4" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="BJ4" s="57"/>
-      <c r="BK4" s="70"/>
-      <c r="BL4" s="56" t="s">
+      <c r="BJ4" s="56"/>
+      <c r="BK4" s="71"/>
+      <c r="BL4" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="BM4" s="57"/>
-      <c r="BN4" s="70"/>
-      <c r="BO4" s="73" t="s">
+      <c r="BM4" s="56"/>
+      <c r="BN4" s="71"/>
+      <c r="BO4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="BP4" s="73"/>
-      <c r="BQ4" s="73"/>
-      <c r="BR4" s="73"/>
-      <c r="BS4" s="73"/>
-      <c r="BT4" s="73"/>
-      <c r="BU4" s="73"/>
-      <c r="BV4" s="73"/>
-      <c r="BW4" s="73"/>
-      <c r="BX4" s="73" t="s">
+      <c r="BP4" s="54"/>
+      <c r="BQ4" s="54"/>
+      <c r="BR4" s="54"/>
+      <c r="BS4" s="54"/>
+      <c r="BT4" s="54"/>
+      <c r="BU4" s="54"/>
+      <c r="BV4" s="54"/>
+      <c r="BW4" s="54"/>
+      <c r="BX4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="BY4" s="73"/>
-      <c r="BZ4" s="73"/>
-      <c r="CA4" s="73"/>
-      <c r="CB4" s="73"/>
-      <c r="CC4" s="73"/>
-      <c r="CD4" s="56" t="s">
+      <c r="BY4" s="54"/>
+      <c r="BZ4" s="54"/>
+      <c r="CA4" s="54"/>
+      <c r="CB4" s="54"/>
+      <c r="CC4" s="54"/>
+      <c r="CD4" s="55" t="s">
         <v>57</v>
       </c>
-      <c r="CE4" s="57"/>
-      <c r="CF4" s="58"/>
-      <c r="CG4" s="82" t="s">
+      <c r="CE4" s="56"/>
+      <c r="CF4" s="57"/>
+      <c r="CG4" s="64" t="s">
         <v>9</v>
       </c>
       <c r="CH4" s="65"/>
@@ -3612,1611 +3613,1611 @@
       <c r="CJ4" s="65"/>
       <c r="CK4" s="65"/>
       <c r="CL4" s="66"/>
-      <c r="CM4" s="69" t="s">
+      <c r="CM4" s="70" t="s">
         <v>10</v>
       </c>
-      <c r="CN4" s="69"/>
-      <c r="CO4" s="69"/>
-      <c r="CP4" s="69"/>
-      <c r="CQ4" s="69"/>
-      <c r="CR4" s="69"/>
-      <c r="CS4" s="56" t="s">
+      <c r="CN4" s="70"/>
+      <c r="CO4" s="70"/>
+      <c r="CP4" s="70"/>
+      <c r="CQ4" s="70"/>
+      <c r="CR4" s="70"/>
+      <c r="CS4" s="55" t="s">
         <v>11</v>
       </c>
-      <c r="CT4" s="57"/>
-      <c r="CU4" s="70"/>
-      <c r="CV4" s="56" t="s">
+      <c r="CT4" s="56"/>
+      <c r="CU4" s="71"/>
+      <c r="CV4" s="55" t="s">
         <v>12</v>
       </c>
-      <c r="CW4" s="57"/>
-      <c r="CX4" s="70"/>
-      <c r="CY4" s="73" t="s">
+      <c r="CW4" s="56"/>
+      <c r="CX4" s="71"/>
+      <c r="CY4" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="CZ4" s="73"/>
-      <c r="DA4" s="73"/>
-      <c r="DB4" s="73"/>
-      <c r="DC4" s="73"/>
-      <c r="DD4" s="73"/>
-      <c r="DE4" s="73"/>
-      <c r="DF4" s="73"/>
-      <c r="DG4" s="73"/>
-      <c r="DH4" s="73" t="s">
+      <c r="CZ4" s="54"/>
+      <c r="DA4" s="54"/>
+      <c r="DB4" s="54"/>
+      <c r="DC4" s="54"/>
+      <c r="DD4" s="54"/>
+      <c r="DE4" s="54"/>
+      <c r="DF4" s="54"/>
+      <c r="DG4" s="54"/>
+      <c r="DH4" s="54" t="s">
         <v>14</v>
       </c>
-      <c r="DI4" s="73"/>
-      <c r="DJ4" s="73"/>
-      <c r="DK4" s="73"/>
-      <c r="DL4" s="73"/>
-      <c r="DM4" s="73"/>
-      <c r="DN4" s="56" t="s">
+      <c r="DI4" s="54"/>
+      <c r="DJ4" s="54"/>
+      <c r="DK4" s="54"/>
+      <c r="DL4" s="54"/>
+      <c r="DM4" s="54"/>
+      <c r="DN4" s="55" t="s">
         <v>58</v>
       </c>
-      <c r="DO4" s="57"/>
-      <c r="DP4" s="58"/>
-      <c r="DQ4" s="86" t="s">
+      <c r="DO4" s="56"/>
+      <c r="DP4" s="57"/>
+      <c r="DQ4" s="91" t="s">
         <v>15</v>
       </c>
-      <c r="DR4" s="87"/>
-      <c r="DS4" s="87"/>
-      <c r="DT4" s="87"/>
-      <c r="DU4" s="87"/>
-      <c r="DV4" s="87"/>
-      <c r="DW4" s="87"/>
-      <c r="DX4" s="87"/>
-      <c r="DY4" s="87"/>
-      <c r="DZ4" s="87"/>
-      <c r="EA4" s="87"/>
-      <c r="EB4" s="87"/>
-      <c r="EC4" s="87"/>
-      <c r="ED4" s="87"/>
-      <c r="EE4" s="87"/>
-      <c r="EF4" s="87"/>
-      <c r="EG4" s="87"/>
-      <c r="EH4" s="88"/>
-      <c r="EI4" s="89" t="s">
+      <c r="DR4" s="92"/>
+      <c r="DS4" s="92"/>
+      <c r="DT4" s="92"/>
+      <c r="DU4" s="92"/>
+      <c r="DV4" s="92"/>
+      <c r="DW4" s="92"/>
+      <c r="DX4" s="92"/>
+      <c r="DY4" s="92"/>
+      <c r="DZ4" s="92"/>
+      <c r="EA4" s="92"/>
+      <c r="EB4" s="92"/>
+      <c r="EC4" s="92"/>
+      <c r="ED4" s="92"/>
+      <c r="EE4" s="92"/>
+      <c r="EF4" s="92"/>
+      <c r="EG4" s="92"/>
+      <c r="EH4" s="93"/>
+      <c r="EI4" s="81" t="s">
         <v>10</v>
       </c>
-      <c r="EJ4" s="90"/>
-      <c r="EK4" s="90"/>
-      <c r="EL4" s="90"/>
-      <c r="EM4" s="90"/>
-      <c r="EN4" s="90"/>
-      <c r="EO4" s="90"/>
-      <c r="EP4" s="90"/>
-      <c r="EQ4" s="90"/>
-      <c r="ER4" s="90"/>
-      <c r="ES4" s="90"/>
-      <c r="ET4" s="90"/>
-      <c r="EU4" s="90"/>
-      <c r="EV4" s="90"/>
-      <c r="EW4" s="90"/>
-      <c r="EX4" s="90"/>
-      <c r="EY4" s="90"/>
-      <c r="EZ4" s="91"/>
-      <c r="FA4" s="89" t="s">
+      <c r="EJ4" s="82"/>
+      <c r="EK4" s="82"/>
+      <c r="EL4" s="82"/>
+      <c r="EM4" s="82"/>
+      <c r="EN4" s="82"/>
+      <c r="EO4" s="82"/>
+      <c r="EP4" s="82"/>
+      <c r="EQ4" s="82"/>
+      <c r="ER4" s="82"/>
+      <c r="ES4" s="82"/>
+      <c r="ET4" s="82"/>
+      <c r="EU4" s="82"/>
+      <c r="EV4" s="82"/>
+      <c r="EW4" s="82"/>
+      <c r="EX4" s="82"/>
+      <c r="EY4" s="82"/>
+      <c r="EZ4" s="83"/>
+      <c r="FA4" s="81" t="s">
         <v>11</v>
       </c>
-      <c r="FB4" s="90"/>
-      <c r="FC4" s="90"/>
-      <c r="FD4" s="90"/>
-      <c r="FE4" s="90"/>
-      <c r="FF4" s="91"/>
-      <c r="FG4" s="89" t="s">
+      <c r="FB4" s="82"/>
+      <c r="FC4" s="82"/>
+      <c r="FD4" s="82"/>
+      <c r="FE4" s="82"/>
+      <c r="FF4" s="83"/>
+      <c r="FG4" s="81" t="s">
         <v>12</v>
       </c>
-      <c r="FH4" s="90"/>
-      <c r="FI4" s="90"/>
-      <c r="FJ4" s="90"/>
-      <c r="FK4" s="90"/>
-      <c r="FL4" s="91"/>
-      <c r="FM4" s="110" t="s">
+      <c r="FH4" s="82"/>
+      <c r="FI4" s="82"/>
+      <c r="FJ4" s="82"/>
+      <c r="FK4" s="82"/>
+      <c r="FL4" s="83"/>
+      <c r="FM4" s="87" t="s">
         <v>13</v>
       </c>
-      <c r="FN4" s="111"/>
-      <c r="FO4" s="111"/>
-      <c r="FP4" s="111"/>
-      <c r="FQ4" s="111"/>
-      <c r="FR4" s="111"/>
-      <c r="FS4" s="111"/>
-      <c r="FT4" s="111"/>
-      <c r="FU4" s="111"/>
-      <c r="FV4" s="111"/>
-      <c r="FW4" s="111"/>
-      <c r="FX4" s="111"/>
-      <c r="FY4" s="111"/>
-      <c r="FZ4" s="111"/>
-      <c r="GA4" s="111"/>
-      <c r="GB4" s="111"/>
-      <c r="GC4" s="111"/>
-      <c r="GD4" s="111"/>
-      <c r="GE4" s="111"/>
-      <c r="GF4" s="111"/>
-      <c r="GG4" s="111"/>
-      <c r="GH4" s="111"/>
-      <c r="GI4" s="111"/>
-      <c r="GJ4" s="111"/>
-      <c r="GK4" s="112" t="s">
+      <c r="FN4" s="88"/>
+      <c r="FO4" s="88"/>
+      <c r="FP4" s="88"/>
+      <c r="FQ4" s="88"/>
+      <c r="FR4" s="88"/>
+      <c r="FS4" s="88"/>
+      <c r="FT4" s="88"/>
+      <c r="FU4" s="88"/>
+      <c r="FV4" s="88"/>
+      <c r="FW4" s="88"/>
+      <c r="FX4" s="88"/>
+      <c r="FY4" s="88"/>
+      <c r="FZ4" s="88"/>
+      <c r="GA4" s="88"/>
+      <c r="GB4" s="88"/>
+      <c r="GC4" s="88"/>
+      <c r="GD4" s="88"/>
+      <c r="GE4" s="88"/>
+      <c r="GF4" s="88"/>
+      <c r="GG4" s="88"/>
+      <c r="GH4" s="88"/>
+      <c r="GI4" s="88"/>
+      <c r="GJ4" s="88"/>
+      <c r="GK4" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="GL4" s="80" t="s">
+      <c r="GL4" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="GM4" s="84" t="s">
+      <c r="GM4" s="34" t="s">
         <v>18</v>
       </c>
-      <c r="GN4" s="84"/>
-      <c r="GO4" s="84"/>
-      <c r="GP4" s="84"/>
-      <c r="GQ4" s="84" t="s">
+      <c r="GN4" s="34"/>
+      <c r="GO4" s="34"/>
+      <c r="GP4" s="34"/>
+      <c r="GQ4" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="GR4" s="84"/>
-      <c r="GS4" s="84"/>
-      <c r="GT4" s="84"/>
-      <c r="GU4" s="84"/>
-      <c r="GV4" s="84"/>
-      <c r="GW4" s="84" t="s">
+      <c r="GR4" s="34"/>
+      <c r="GS4" s="34"/>
+      <c r="GT4" s="34"/>
+      <c r="GU4" s="34"/>
+      <c r="GV4" s="34"/>
+      <c r="GW4" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="GX4" s="84"/>
-      <c r="GY4" s="84"/>
-      <c r="GZ4" s="84"/>
-      <c r="HA4" s="84"/>
-      <c r="HB4" s="84"/>
+      <c r="GX4" s="34"/>
+      <c r="GY4" s="34"/>
+      <c r="GZ4" s="34"/>
+      <c r="HA4" s="34"/>
+      <c r="HB4" s="34"/>
     </row>
     <row r="5" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="43"/>
-      <c r="B5" s="43"/>
-      <c r="C5" s="43"/>
-      <c r="D5" s="43"/>
+      <c r="A5" s="38"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="38"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="43"/>
+      <c r="F5" s="38"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="50"/>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="52"/>
-      <c r="M5" s="83"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="67"/>
-      <c r="P5" s="67"/>
-      <c r="Q5" s="67"/>
-      <c r="R5" s="68"/>
-      <c r="S5" s="69"/>
-      <c r="T5" s="69"/>
-      <c r="U5" s="69"/>
-      <c r="V5" s="69"/>
-      <c r="W5" s="69"/>
-      <c r="X5" s="69"/>
-      <c r="Y5" s="59"/>
-      <c r="Z5" s="60"/>
-      <c r="AA5" s="71"/>
-      <c r="AB5" s="59"/>
-      <c r="AC5" s="60"/>
-      <c r="AD5" s="71"/>
-      <c r="AE5" s="84" t="s">
+      <c r="H5" s="109"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="110"/>
+      <c r="K5" s="110"/>
+      <c r="L5" s="111"/>
+      <c r="M5" s="67"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="69"/>
+      <c r="S5" s="70"/>
+      <c r="T5" s="70"/>
+      <c r="U5" s="70"/>
+      <c r="V5" s="70"/>
+      <c r="W5" s="70"/>
+      <c r="X5" s="70"/>
+      <c r="Y5" s="58"/>
+      <c r="Z5" s="59"/>
+      <c r="AA5" s="72"/>
+      <c r="AB5" s="58"/>
+      <c r="AC5" s="59"/>
+      <c r="AD5" s="72"/>
+      <c r="AE5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="AF5" s="84"/>
-      <c r="AG5" s="84"/>
-      <c r="AH5" s="84"/>
-      <c r="AI5" s="84"/>
-      <c r="AJ5" s="84"/>
-      <c r="AK5" s="84"/>
-      <c r="AL5" s="84"/>
-      <c r="AM5" s="84"/>
-      <c r="AN5" s="73"/>
-      <c r="AO5" s="73"/>
-      <c r="AP5" s="73"/>
-      <c r="AQ5" s="73"/>
-      <c r="AR5" s="73"/>
-      <c r="AS5" s="73"/>
-      <c r="AT5" s="59"/>
-      <c r="AU5" s="60"/>
-      <c r="AV5" s="61"/>
-      <c r="AW5" s="67"/>
-      <c r="AX5" s="67"/>
-      <c r="AY5" s="67"/>
-      <c r="AZ5" s="67"/>
-      <c r="BA5" s="67"/>
-      <c r="BB5" s="68"/>
-      <c r="BC5" s="69"/>
-      <c r="BD5" s="69"/>
-      <c r="BE5" s="69"/>
-      <c r="BF5" s="69"/>
-      <c r="BG5" s="69"/>
-      <c r="BH5" s="69"/>
-      <c r="BI5" s="59"/>
-      <c r="BJ5" s="60"/>
-      <c r="BK5" s="71"/>
-      <c r="BL5" s="59"/>
-      <c r="BM5" s="60"/>
-      <c r="BN5" s="71"/>
-      <c r="BO5" s="84" t="s">
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="34"/>
+      <c r="AH5" s="34"/>
+      <c r="AI5" s="34"/>
+      <c r="AJ5" s="34"/>
+      <c r="AK5" s="34"/>
+      <c r="AL5" s="34"/>
+      <c r="AM5" s="34"/>
+      <c r="AN5" s="54"/>
+      <c r="AO5" s="54"/>
+      <c r="AP5" s="54"/>
+      <c r="AQ5" s="54"/>
+      <c r="AR5" s="54"/>
+      <c r="AS5" s="54"/>
+      <c r="AT5" s="58"/>
+      <c r="AU5" s="59"/>
+      <c r="AV5" s="60"/>
+      <c r="AW5" s="68"/>
+      <c r="AX5" s="68"/>
+      <c r="AY5" s="68"/>
+      <c r="AZ5" s="68"/>
+      <c r="BA5" s="68"/>
+      <c r="BB5" s="69"/>
+      <c r="BC5" s="70"/>
+      <c r="BD5" s="70"/>
+      <c r="BE5" s="70"/>
+      <c r="BF5" s="70"/>
+      <c r="BG5" s="70"/>
+      <c r="BH5" s="70"/>
+      <c r="BI5" s="58"/>
+      <c r="BJ5" s="59"/>
+      <c r="BK5" s="72"/>
+      <c r="BL5" s="58"/>
+      <c r="BM5" s="59"/>
+      <c r="BN5" s="72"/>
+      <c r="BO5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="BP5" s="84"/>
-      <c r="BQ5" s="84"/>
-      <c r="BR5" s="84"/>
-      <c r="BS5" s="84"/>
-      <c r="BT5" s="84"/>
-      <c r="BU5" s="84"/>
-      <c r="BV5" s="84"/>
-      <c r="BW5" s="84"/>
-      <c r="BX5" s="73"/>
-      <c r="BY5" s="73"/>
-      <c r="BZ5" s="73"/>
-      <c r="CA5" s="73"/>
-      <c r="CB5" s="73"/>
-      <c r="CC5" s="73"/>
-      <c r="CD5" s="59"/>
-      <c r="CE5" s="60"/>
-      <c r="CF5" s="61"/>
-      <c r="CG5" s="83"/>
-      <c r="CH5" s="67"/>
-      <c r="CI5" s="67"/>
-      <c r="CJ5" s="67"/>
-      <c r="CK5" s="67"/>
-      <c r="CL5" s="68"/>
-      <c r="CM5" s="69"/>
-      <c r="CN5" s="69"/>
-      <c r="CO5" s="69"/>
-      <c r="CP5" s="69"/>
-      <c r="CQ5" s="69"/>
-      <c r="CR5" s="69"/>
-      <c r="CS5" s="59"/>
-      <c r="CT5" s="60"/>
-      <c r="CU5" s="71"/>
-      <c r="CV5" s="59"/>
-      <c r="CW5" s="60"/>
-      <c r="CX5" s="71"/>
-      <c r="CY5" s="84" t="s">
+      <c r="BP5" s="34"/>
+      <c r="BQ5" s="34"/>
+      <c r="BR5" s="34"/>
+      <c r="BS5" s="34"/>
+      <c r="BT5" s="34"/>
+      <c r="BU5" s="34"/>
+      <c r="BV5" s="34"/>
+      <c r="BW5" s="34"/>
+      <c r="BX5" s="54"/>
+      <c r="BY5" s="54"/>
+      <c r="BZ5" s="54"/>
+      <c r="CA5" s="54"/>
+      <c r="CB5" s="54"/>
+      <c r="CC5" s="54"/>
+      <c r="CD5" s="58"/>
+      <c r="CE5" s="59"/>
+      <c r="CF5" s="60"/>
+      <c r="CG5" s="67"/>
+      <c r="CH5" s="68"/>
+      <c r="CI5" s="68"/>
+      <c r="CJ5" s="68"/>
+      <c r="CK5" s="68"/>
+      <c r="CL5" s="69"/>
+      <c r="CM5" s="70"/>
+      <c r="CN5" s="70"/>
+      <c r="CO5" s="70"/>
+      <c r="CP5" s="70"/>
+      <c r="CQ5" s="70"/>
+      <c r="CR5" s="70"/>
+      <c r="CS5" s="58"/>
+      <c r="CT5" s="59"/>
+      <c r="CU5" s="72"/>
+      <c r="CV5" s="58"/>
+      <c r="CW5" s="59"/>
+      <c r="CX5" s="72"/>
+      <c r="CY5" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="CZ5" s="84"/>
-      <c r="DA5" s="84"/>
-      <c r="DB5" s="84"/>
-      <c r="DC5" s="84"/>
-      <c r="DD5" s="84"/>
-      <c r="DE5" s="84"/>
-      <c r="DF5" s="84"/>
-      <c r="DG5" s="84"/>
-      <c r="DH5" s="73"/>
-      <c r="DI5" s="73"/>
-      <c r="DJ5" s="73"/>
-      <c r="DK5" s="73"/>
-      <c r="DL5" s="73"/>
-      <c r="DM5" s="73"/>
-      <c r="DN5" s="59"/>
-      <c r="DO5" s="60"/>
-      <c r="DP5" s="61"/>
-      <c r="DQ5" s="105" t="s">
+      <c r="CZ5" s="34"/>
+      <c r="DA5" s="34"/>
+      <c r="DB5" s="34"/>
+      <c r="DC5" s="34"/>
+      <c r="DD5" s="34"/>
+      <c r="DE5" s="34"/>
+      <c r="DF5" s="34"/>
+      <c r="DG5" s="34"/>
+      <c r="DH5" s="54"/>
+      <c r="DI5" s="54"/>
+      <c r="DJ5" s="54"/>
+      <c r="DK5" s="54"/>
+      <c r="DL5" s="54"/>
+      <c r="DM5" s="54"/>
+      <c r="DN5" s="58"/>
+      <c r="DO5" s="59"/>
+      <c r="DP5" s="60"/>
+      <c r="DQ5" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="DR5" s="102" t="s">
+      <c r="DR5" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="DS5" s="95" t="s">
+      <c r="DS5" s="45" t="s">
         <v>479</v>
       </c>
-      <c r="DT5" s="96"/>
-      <c r="DU5" s="96"/>
-      <c r="DV5" s="97"/>
-      <c r="DW5" s="107" t="s">
+      <c r="DT5" s="46"/>
+      <c r="DU5" s="46"/>
+      <c r="DV5" s="47"/>
+      <c r="DW5" s="78" t="s">
         <v>24</v>
       </c>
-      <c r="DX5" s="108"/>
-      <c r="DY5" s="108"/>
-      <c r="DZ5" s="108"/>
-      <c r="EA5" s="108"/>
-      <c r="EB5" s="108"/>
-      <c r="EC5" s="108"/>
-      <c r="ED5" s="108"/>
-      <c r="EE5" s="108"/>
-      <c r="EF5" s="108"/>
-      <c r="EG5" s="108"/>
-      <c r="EH5" s="109"/>
-      <c r="EI5" s="102" t="s">
+      <c r="DX5" s="79"/>
+      <c r="DY5" s="79"/>
+      <c r="DZ5" s="79"/>
+      <c r="EA5" s="79"/>
+      <c r="EB5" s="79"/>
+      <c r="EC5" s="79"/>
+      <c r="ED5" s="79"/>
+      <c r="EE5" s="79"/>
+      <c r="EF5" s="79"/>
+      <c r="EG5" s="79"/>
+      <c r="EH5" s="80"/>
+      <c r="EI5" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="EJ5" s="102" t="s">
+      <c r="EJ5" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="EK5" s="95" t="s">
+      <c r="EK5" s="45" t="s">
         <v>480</v>
       </c>
-      <c r="EL5" s="96"/>
-      <c r="EM5" s="96"/>
-      <c r="EN5" s="97"/>
-      <c r="EO5" s="101" t="s">
+      <c r="EL5" s="46"/>
+      <c r="EM5" s="46"/>
+      <c r="EN5" s="47"/>
+      <c r="EO5" s="94" t="s">
         <v>21</v>
       </c>
-      <c r="EP5" s="101"/>
-      <c r="EQ5" s="101"/>
-      <c r="ER5" s="101"/>
-      <c r="ES5" s="101"/>
-      <c r="ET5" s="101"/>
-      <c r="EU5" s="101"/>
-      <c r="EV5" s="101"/>
-      <c r="EW5" s="101"/>
-      <c r="EX5" s="101"/>
-      <c r="EY5" s="101"/>
-      <c r="EZ5" s="101"/>
-      <c r="FA5" s="92"/>
-      <c r="FB5" s="93"/>
-      <c r="FC5" s="93"/>
-      <c r="FD5" s="93"/>
-      <c r="FE5" s="93"/>
-      <c r="FF5" s="94"/>
-      <c r="FG5" s="92"/>
-      <c r="FH5" s="93"/>
-      <c r="FI5" s="93"/>
-      <c r="FJ5" s="93"/>
-      <c r="FK5" s="93"/>
-      <c r="FL5" s="94"/>
-      <c r="FM5" s="104" t="s">
+      <c r="EP5" s="94"/>
+      <c r="EQ5" s="94"/>
+      <c r="ER5" s="94"/>
+      <c r="ES5" s="94"/>
+      <c r="ET5" s="94"/>
+      <c r="EU5" s="94"/>
+      <c r="EV5" s="94"/>
+      <c r="EW5" s="94"/>
+      <c r="EX5" s="94"/>
+      <c r="EY5" s="94"/>
+      <c r="EZ5" s="94"/>
+      <c r="FA5" s="84"/>
+      <c r="FB5" s="85"/>
+      <c r="FC5" s="85"/>
+      <c r="FD5" s="85"/>
+      <c r="FE5" s="85"/>
+      <c r="FF5" s="86"/>
+      <c r="FG5" s="84"/>
+      <c r="FH5" s="85"/>
+      <c r="FI5" s="85"/>
+      <c r="FJ5" s="85"/>
+      <c r="FK5" s="85"/>
+      <c r="FL5" s="86"/>
+      <c r="FM5" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="FN5" s="104" t="s">
+      <c r="FN5" s="24" t="s">
         <v>27</v>
       </c>
-      <c r="FO5" s="95" t="s">
+      <c r="FO5" s="45" t="s">
         <v>28</v>
       </c>
-      <c r="FP5" s="96"/>
-      <c r="FQ5" s="96"/>
-      <c r="FR5" s="97"/>
-      <c r="FS5" s="74" t="s">
+      <c r="FP5" s="46"/>
+      <c r="FQ5" s="46"/>
+      <c r="FR5" s="47"/>
+      <c r="FS5" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="FT5" s="75"/>
-      <c r="FU5" s="75"/>
-      <c r="FV5" s="75"/>
-      <c r="FW5" s="75"/>
-      <c r="FX5" s="75"/>
-      <c r="FY5" s="75"/>
-      <c r="FZ5" s="75"/>
-      <c r="GA5" s="75"/>
-      <c r="GB5" s="75"/>
-      <c r="GC5" s="75"/>
-      <c r="GD5" s="75"/>
-      <c r="GE5" s="75"/>
-      <c r="GF5" s="75"/>
-      <c r="GG5" s="75"/>
-      <c r="GH5" s="75"/>
-      <c r="GI5" s="75"/>
-      <c r="GJ5" s="75"/>
-      <c r="GK5" s="112"/>
-      <c r="GL5" s="80"/>
-      <c r="GM5" s="84"/>
-      <c r="GN5" s="84"/>
-      <c r="GO5" s="84"/>
-      <c r="GP5" s="84"/>
-      <c r="GQ5" s="84"/>
-      <c r="GR5" s="84"/>
-      <c r="GS5" s="84"/>
-      <c r="GT5" s="84"/>
-      <c r="GU5" s="84"/>
-      <c r="GV5" s="84"/>
-      <c r="GW5" s="84"/>
-      <c r="GX5" s="84"/>
-      <c r="GY5" s="84"/>
-      <c r="GZ5" s="84"/>
-      <c r="HA5" s="84"/>
-      <c r="HB5" s="84"/>
+      <c r="FT5" s="27"/>
+      <c r="FU5" s="27"/>
+      <c r="FV5" s="27"/>
+      <c r="FW5" s="27"/>
+      <c r="FX5" s="27"/>
+      <c r="FY5" s="27"/>
+      <c r="FZ5" s="27"/>
+      <c r="GA5" s="27"/>
+      <c r="GB5" s="27"/>
+      <c r="GC5" s="27"/>
+      <c r="GD5" s="27"/>
+      <c r="GE5" s="27"/>
+      <c r="GF5" s="27"/>
+      <c r="GG5" s="27"/>
+      <c r="GH5" s="27"/>
+      <c r="GI5" s="27"/>
+      <c r="GJ5" s="27"/>
+      <c r="GK5" s="89"/>
+      <c r="GL5" s="33"/>
+      <c r="GM5" s="34"/>
+      <c r="GN5" s="34"/>
+      <c r="GO5" s="34"/>
+      <c r="GP5" s="34"/>
+      <c r="GQ5" s="34"/>
+      <c r="GR5" s="34"/>
+      <c r="GS5" s="34"/>
+      <c r="GT5" s="34"/>
+      <c r="GU5" s="34"/>
+      <c r="GV5" s="34"/>
+      <c r="GW5" s="34"/>
+      <c r="GX5" s="34"/>
+      <c r="GY5" s="34"/>
+      <c r="GZ5" s="34"/>
+      <c r="HA5" s="34"/>
+      <c r="HB5" s="34"/>
     </row>
     <row r="6" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
+      <c r="A6" s="38"/>
+      <c r="B6" s="38"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
       <c r="E6" s="12"/>
-      <c r="F6" s="43"/>
+      <c r="F6" s="38"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="37" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="53" t="s">
+      <c r="I6" s="112" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="54"/>
-      <c r="K6" s="54"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="74" t="s">
+      <c r="J6" s="113"/>
+      <c r="K6" s="113"/>
+      <c r="L6" s="114"/>
+      <c r="M6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="N6" s="75"/>
-      <c r="O6" s="76"/>
-      <c r="P6" s="74" t="s">
+      <c r="N6" s="27"/>
+      <c r="O6" s="28"/>
+      <c r="P6" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="Q6" s="75"/>
-      <c r="R6" s="76"/>
-      <c r="S6" s="77" t="s">
+      <c r="Q6" s="27"/>
+      <c r="R6" s="28"/>
+      <c r="S6" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="T6" s="78"/>
-      <c r="U6" s="79"/>
-      <c r="V6" s="77" t="s">
+      <c r="T6" s="52"/>
+      <c r="U6" s="53"/>
+      <c r="V6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="W6" s="78"/>
-      <c r="X6" s="79"/>
-      <c r="Y6" s="62"/>
-      <c r="Z6" s="63"/>
-      <c r="AA6" s="72"/>
-      <c r="AB6" s="62"/>
-      <c r="AC6" s="63"/>
-      <c r="AD6" s="72"/>
-      <c r="AE6" s="80" t="s">
+      <c r="W6" s="52"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="61"/>
+      <c r="Z6" s="62"/>
+      <c r="AA6" s="73"/>
+      <c r="AB6" s="61"/>
+      <c r="AC6" s="62"/>
+      <c r="AD6" s="73"/>
+      <c r="AE6" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="AF6" s="80"/>
-      <c r="AG6" s="80"/>
-      <c r="AH6" s="84" t="s">
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="33"/>
+      <c r="AH6" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="AI6" s="84"/>
-      <c r="AJ6" s="84"/>
-      <c r="AK6" s="80" t="s">
+      <c r="AI6" s="34"/>
+      <c r="AJ6" s="34"/>
+      <c r="AK6" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="AL6" s="80"/>
-      <c r="AM6" s="80"/>
-      <c r="AN6" s="84" t="s">
+      <c r="AL6" s="33"/>
+      <c r="AM6" s="33"/>
+      <c r="AN6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="AO6" s="84"/>
-      <c r="AP6" s="84"/>
-      <c r="AQ6" s="84" t="s">
+      <c r="AO6" s="34"/>
+      <c r="AP6" s="34"/>
+      <c r="AQ6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="AR6" s="84"/>
-      <c r="AS6" s="84"/>
-      <c r="AT6" s="62"/>
-      <c r="AU6" s="63"/>
-      <c r="AV6" s="64"/>
-      <c r="AW6" s="75" t="s">
+      <c r="AR6" s="34"/>
+      <c r="AS6" s="34"/>
+      <c r="AT6" s="61"/>
+      <c r="AU6" s="62"/>
+      <c r="AV6" s="63"/>
+      <c r="AW6" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="AX6" s="75"/>
-      <c r="AY6" s="76"/>
-      <c r="AZ6" s="74" t="s">
+      <c r="AX6" s="27"/>
+      <c r="AY6" s="28"/>
+      <c r="AZ6" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="BA6" s="75"/>
-      <c r="BB6" s="76"/>
-      <c r="BC6" s="77" t="s">
+      <c r="BA6" s="27"/>
+      <c r="BB6" s="28"/>
+      <c r="BC6" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="BD6" s="78"/>
-      <c r="BE6" s="79"/>
-      <c r="BF6" s="77" t="s">
+      <c r="BD6" s="52"/>
+      <c r="BE6" s="53"/>
+      <c r="BF6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="BG6" s="78"/>
-      <c r="BH6" s="79"/>
-      <c r="BI6" s="62"/>
-      <c r="BJ6" s="63"/>
-      <c r="BK6" s="72"/>
-      <c r="BL6" s="62"/>
-      <c r="BM6" s="63"/>
-      <c r="BN6" s="72"/>
-      <c r="BO6" s="80" t="s">
+      <c r="BG6" s="52"/>
+      <c r="BH6" s="53"/>
+      <c r="BI6" s="61"/>
+      <c r="BJ6" s="62"/>
+      <c r="BK6" s="73"/>
+      <c r="BL6" s="61"/>
+      <c r="BM6" s="62"/>
+      <c r="BN6" s="73"/>
+      <c r="BO6" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="BP6" s="80"/>
-      <c r="BQ6" s="80"/>
-      <c r="BR6" s="84" t="s">
+      <c r="BP6" s="33"/>
+      <c r="BQ6" s="33"/>
+      <c r="BR6" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="BS6" s="84"/>
-      <c r="BT6" s="84"/>
-      <c r="BU6" s="80" t="s">
+      <c r="BS6" s="34"/>
+      <c r="BT6" s="34"/>
+      <c r="BU6" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="BV6" s="80"/>
-      <c r="BW6" s="80"/>
-      <c r="BX6" s="84" t="s">
+      <c r="BV6" s="33"/>
+      <c r="BW6" s="33"/>
+      <c r="BX6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="BY6" s="84"/>
-      <c r="BZ6" s="84"/>
-      <c r="CA6" s="84" t="s">
+      <c r="BY6" s="34"/>
+      <c r="BZ6" s="34"/>
+      <c r="CA6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="CB6" s="84"/>
-      <c r="CC6" s="84"/>
-      <c r="CD6" s="62"/>
-      <c r="CE6" s="63"/>
-      <c r="CF6" s="64"/>
-      <c r="CG6" s="74" t="s">
+      <c r="CB6" s="34"/>
+      <c r="CC6" s="34"/>
+      <c r="CD6" s="61"/>
+      <c r="CE6" s="62"/>
+      <c r="CF6" s="63"/>
+      <c r="CG6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="CH6" s="75"/>
-      <c r="CI6" s="76"/>
-      <c r="CJ6" s="74" t="s">
+      <c r="CH6" s="27"/>
+      <c r="CI6" s="28"/>
+      <c r="CJ6" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="CK6" s="75"/>
-      <c r="CL6" s="76"/>
-      <c r="CM6" s="77" t="s">
+      <c r="CK6" s="27"/>
+      <c r="CL6" s="28"/>
+      <c r="CM6" s="51" t="s">
         <v>33</v>
       </c>
-      <c r="CN6" s="78"/>
-      <c r="CO6" s="79"/>
-      <c r="CP6" s="77" t="s">
+      <c r="CN6" s="52"/>
+      <c r="CO6" s="53"/>
+      <c r="CP6" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="CQ6" s="78"/>
-      <c r="CR6" s="79"/>
-      <c r="CS6" s="62"/>
-      <c r="CT6" s="63"/>
-      <c r="CU6" s="72"/>
-      <c r="CV6" s="62"/>
-      <c r="CW6" s="63"/>
-      <c r="CX6" s="72"/>
-      <c r="CY6" s="80" t="s">
+      <c r="CQ6" s="52"/>
+      <c r="CR6" s="53"/>
+      <c r="CS6" s="61"/>
+      <c r="CT6" s="62"/>
+      <c r="CU6" s="73"/>
+      <c r="CV6" s="61"/>
+      <c r="CW6" s="62"/>
+      <c r="CX6" s="73"/>
+      <c r="CY6" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="CZ6" s="80"/>
-      <c r="DA6" s="80"/>
-      <c r="DB6" s="84" t="s">
+      <c r="CZ6" s="33"/>
+      <c r="DA6" s="33"/>
+      <c r="DB6" s="34" t="s">
         <v>36</v>
       </c>
-      <c r="DC6" s="84"/>
-      <c r="DD6" s="84"/>
-      <c r="DE6" s="80" t="s">
+      <c r="DC6" s="34"/>
+      <c r="DD6" s="34"/>
+      <c r="DE6" s="33" t="s">
         <v>37</v>
       </c>
-      <c r="DF6" s="80"/>
-      <c r="DG6" s="80"/>
-      <c r="DH6" s="84" t="s">
+      <c r="DF6" s="33"/>
+      <c r="DG6" s="33"/>
+      <c r="DH6" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="DI6" s="84"/>
-      <c r="DJ6" s="84"/>
-      <c r="DK6" s="84" t="s">
+      <c r="DI6" s="34"/>
+      <c r="DJ6" s="34"/>
+      <c r="DK6" s="34" t="s">
         <v>20</v>
       </c>
-      <c r="DL6" s="84"/>
-      <c r="DM6" s="84"/>
-      <c r="DN6" s="62"/>
-      <c r="DO6" s="63"/>
-      <c r="DP6" s="64"/>
-      <c r="DQ6" s="106"/>
-      <c r="DR6" s="103"/>
-      <c r="DS6" s="98"/>
-      <c r="DT6" s="99"/>
-      <c r="DU6" s="99"/>
-      <c r="DV6" s="100"/>
-      <c r="DW6" s="74" t="s">
+      <c r="DL6" s="34"/>
+      <c r="DM6" s="34"/>
+      <c r="DN6" s="61"/>
+      <c r="DO6" s="62"/>
+      <c r="DP6" s="63"/>
+      <c r="DQ6" s="77"/>
+      <c r="DR6" s="32"/>
+      <c r="DS6" s="48"/>
+      <c r="DT6" s="49"/>
+      <c r="DU6" s="49"/>
+      <c r="DV6" s="50"/>
+      <c r="DW6" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="DX6" s="75"/>
-      <c r="DY6" s="75"/>
-      <c r="DZ6" s="75"/>
-      <c r="EA6" s="75"/>
-      <c r="EB6" s="76"/>
-      <c r="EC6" s="74" t="s">
+      <c r="DX6" s="27"/>
+      <c r="DY6" s="27"/>
+      <c r="DZ6" s="27"/>
+      <c r="EA6" s="27"/>
+      <c r="EB6" s="28"/>
+      <c r="EC6" s="26" t="s">
         <v>32</v>
       </c>
-      <c r="ED6" s="75"/>
-      <c r="EE6" s="75"/>
-      <c r="EF6" s="75"/>
-      <c r="EG6" s="75"/>
-      <c r="EH6" s="76"/>
-      <c r="EI6" s="103"/>
-      <c r="EJ6" s="103"/>
-      <c r="EK6" s="98"/>
-      <c r="EL6" s="99"/>
-      <c r="EM6" s="99"/>
-      <c r="EN6" s="100"/>
-      <c r="EO6" s="95" t="s">
+      <c r="ED6" s="27"/>
+      <c r="EE6" s="27"/>
+      <c r="EF6" s="27"/>
+      <c r="EG6" s="27"/>
+      <c r="EH6" s="28"/>
+      <c r="EI6" s="32"/>
+      <c r="EJ6" s="32"/>
+      <c r="EK6" s="48"/>
+      <c r="EL6" s="49"/>
+      <c r="EM6" s="49"/>
+      <c r="EN6" s="50"/>
+      <c r="EO6" s="45" t="s">
         <v>33</v>
       </c>
-      <c r="EP6" s="96"/>
-      <c r="EQ6" s="96"/>
-      <c r="ER6" s="96"/>
-      <c r="ES6" s="96"/>
-      <c r="ET6" s="97"/>
-      <c r="EU6" s="84" t="s">
+      <c r="EP6" s="46"/>
+      <c r="EQ6" s="46"/>
+      <c r="ER6" s="46"/>
+      <c r="ES6" s="46"/>
+      <c r="ET6" s="47"/>
+      <c r="EU6" s="34" t="s">
         <v>34</v>
       </c>
-      <c r="EV6" s="84"/>
-      <c r="EW6" s="84"/>
-      <c r="EX6" s="84"/>
-      <c r="EY6" s="84"/>
-      <c r="EZ6" s="84"/>
-      <c r="FA6" s="80" t="s">
+      <c r="EV6" s="34"/>
+      <c r="EW6" s="34"/>
+      <c r="EX6" s="34"/>
+      <c r="EY6" s="34"/>
+      <c r="EZ6" s="34"/>
+      <c r="FA6" s="33" t="s">
         <v>38</v>
       </c>
-      <c r="FB6" s="80"/>
-      <c r="FC6" s="84" t="s">
+      <c r="FB6" s="33"/>
+      <c r="FC6" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="FD6" s="84"/>
-      <c r="FE6" s="84"/>
-      <c r="FF6" s="84"/>
-      <c r="FG6" s="80" t="s">
+      <c r="FD6" s="34"/>
+      <c r="FE6" s="34"/>
+      <c r="FF6" s="34"/>
+      <c r="FG6" s="33" t="s">
         <v>40</v>
       </c>
-      <c r="FH6" s="80"/>
-      <c r="FI6" s="84" t="s">
+      <c r="FH6" s="33"/>
+      <c r="FI6" s="34" t="s">
         <v>39</v>
       </c>
-      <c r="FJ6" s="84"/>
-      <c r="FK6" s="84"/>
-      <c r="FL6" s="84"/>
-      <c r="FM6" s="114"/>
-      <c r="FN6" s="114"/>
-      <c r="FO6" s="98"/>
-      <c r="FP6" s="99"/>
-      <c r="FQ6" s="99"/>
-      <c r="FR6" s="100"/>
-      <c r="FS6" s="74" t="s">
+      <c r="FJ6" s="34"/>
+      <c r="FK6" s="34"/>
+      <c r="FL6" s="34"/>
+      <c r="FM6" s="25"/>
+      <c r="FN6" s="25"/>
+      <c r="FO6" s="48"/>
+      <c r="FP6" s="49"/>
+      <c r="FQ6" s="49"/>
+      <c r="FR6" s="50"/>
+      <c r="FS6" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="FT6" s="75"/>
-      <c r="FU6" s="75"/>
-      <c r="FV6" s="75"/>
-      <c r="FW6" s="75"/>
-      <c r="FX6" s="76"/>
-      <c r="FY6" s="74" t="s">
+      <c r="FT6" s="27"/>
+      <c r="FU6" s="27"/>
+      <c r="FV6" s="27"/>
+      <c r="FW6" s="27"/>
+      <c r="FX6" s="28"/>
+      <c r="FY6" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="FZ6" s="75"/>
-      <c r="GA6" s="75"/>
-      <c r="GB6" s="75"/>
-      <c r="GC6" s="75"/>
-      <c r="GD6" s="76"/>
-      <c r="GE6" s="74" t="s">
+      <c r="FZ6" s="27"/>
+      <c r="GA6" s="27"/>
+      <c r="GB6" s="27"/>
+      <c r="GC6" s="27"/>
+      <c r="GD6" s="28"/>
+      <c r="GE6" s="26" t="s">
         <v>37</v>
       </c>
-      <c r="GF6" s="75"/>
-      <c r="GG6" s="75"/>
-      <c r="GH6" s="75"/>
-      <c r="GI6" s="75"/>
-      <c r="GJ6" s="75"/>
-      <c r="GK6" s="112"/>
-      <c r="GL6" s="80"/>
-      <c r="GM6" s="84"/>
-      <c r="GN6" s="84"/>
-      <c r="GO6" s="84"/>
-      <c r="GP6" s="84"/>
-      <c r="GQ6" s="84"/>
-      <c r="GR6" s="84"/>
-      <c r="GS6" s="84"/>
-      <c r="GT6" s="84"/>
-      <c r="GU6" s="84"/>
-      <c r="GV6" s="84"/>
-      <c r="GW6" s="84"/>
-      <c r="GX6" s="84"/>
-      <c r="GY6" s="84"/>
-      <c r="GZ6" s="84"/>
-      <c r="HA6" s="84"/>
-      <c r="HB6" s="84"/>
+      <c r="GF6" s="27"/>
+      <c r="GG6" s="27"/>
+      <c r="GH6" s="27"/>
+      <c r="GI6" s="27"/>
+      <c r="GJ6" s="27"/>
+      <c r="GK6" s="89"/>
+      <c r="GL6" s="33"/>
+      <c r="GM6" s="34"/>
+      <c r="GN6" s="34"/>
+      <c r="GO6" s="34"/>
+      <c r="GP6" s="34"/>
+      <c r="GQ6" s="34"/>
+      <c r="GR6" s="34"/>
+      <c r="GS6" s="34"/>
+      <c r="GT6" s="34"/>
+      <c r="GU6" s="34"/>
+      <c r="GV6" s="34"/>
+      <c r="GW6" s="34"/>
+      <c r="GX6" s="34"/>
+      <c r="GY6" s="34"/>
+      <c r="GZ6" s="34"/>
+      <c r="HA6" s="34"/>
+      <c r="HB6" s="34"/>
     </row>
     <row r="7" spans="1:210" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="43"/>
-      <c r="B7" s="43"/>
-      <c r="C7" s="43"/>
-      <c r="D7" s="43"/>
+      <c r="A7" s="38"/>
+      <c r="B7" s="38"/>
+      <c r="C7" s="38"/>
+      <c r="D7" s="38"/>
       <c r="E7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="43"/>
+      <c r="F7" s="38"/>
       <c r="G7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="43"/>
-      <c r="I7" s="42" t="s">
+      <c r="H7" s="38"/>
+      <c r="I7" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="119" t="s">
+      <c r="J7" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="120"/>
-      <c r="L7" s="121"/>
-      <c r="M7" s="80" t="s">
+      <c r="K7" s="43"/>
+      <c r="L7" s="44"/>
+      <c r="M7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="N7" s="84" t="s">
+      <c r="N7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="O7" s="102" t="s">
+      <c r="O7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="80" t="s">
+      <c r="P7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="84" t="s">
+      <c r="Q7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="R7" s="102" t="s">
+      <c r="R7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="S7" s="80" t="s">
+      <c r="S7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="T7" s="84" t="s">
+      <c r="T7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="U7" s="102" t="s">
+      <c r="U7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="V7" s="80" t="s">
+      <c r="V7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="W7" s="84" t="s">
+      <c r="W7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="X7" s="102" t="s">
+      <c r="X7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="Y7" s="80" t="s">
+      <c r="Y7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="Z7" s="84" t="s">
+      <c r="Z7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AA7" s="102" t="s">
+      <c r="AA7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AB7" s="80" t="s">
+      <c r="AB7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AC7" s="84" t="s">
+      <c r="AC7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AD7" s="102" t="s">
+      <c r="AD7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AE7" s="80" t="s">
+      <c r="AE7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AF7" s="84" t="s">
+      <c r="AF7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AG7" s="102" t="s">
+      <c r="AG7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AH7" s="80" t="s">
+      <c r="AH7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AI7" s="84" t="s">
+      <c r="AI7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AJ7" s="102" t="s">
+      <c r="AJ7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AK7" s="80" t="s">
+      <c r="AK7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AL7" s="84" t="s">
+      <c r="AL7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AM7" s="102" t="s">
+      <c r="AM7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AN7" s="80" t="s">
+      <c r="AN7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AO7" s="84" t="s">
+      <c r="AO7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AP7" s="102" t="s">
+      <c r="AP7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AQ7" s="80" t="s">
+      <c r="AQ7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="AR7" s="84" t="s">
+      <c r="AR7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AS7" s="102" t="s">
+      <c r="AS7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AT7" s="84" t="s">
+      <c r="AT7" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="AU7" s="84" t="s">
+      <c r="AU7" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="AV7" s="122" t="s">
+      <c r="AV7" s="40" t="s">
         <v>46</v>
       </c>
-      <c r="AW7" s="116" t="s">
+      <c r="AW7" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="AX7" s="84" t="s">
+      <c r="AX7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="AY7" s="102" t="s">
+      <c r="AY7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="AZ7" s="80" t="s">
+      <c r="AZ7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BA7" s="84" t="s">
+      <c r="BA7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BB7" s="102" t="s">
+      <c r="BB7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BC7" s="80" t="s">
+      <c r="BC7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BD7" s="84" t="s">
+      <c r="BD7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BE7" s="102" t="s">
+      <c r="BE7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BF7" s="80" t="s">
+      <c r="BF7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BG7" s="84" t="s">
+      <c r="BG7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BH7" s="102" t="s">
+      <c r="BH7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BI7" s="80" t="s">
+      <c r="BI7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BJ7" s="84" t="s">
+      <c r="BJ7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BK7" s="102" t="s">
+      <c r="BK7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BL7" s="80" t="s">
+      <c r="BL7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BM7" s="84" t="s">
+      <c r="BM7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BN7" s="102" t="s">
+      <c r="BN7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BO7" s="80" t="s">
+      <c r="BO7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BP7" s="84" t="s">
+      <c r="BP7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BQ7" s="102" t="s">
+      <c r="BQ7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BR7" s="80" t="s">
+      <c r="BR7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BS7" s="84" t="s">
+      <c r="BS7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BT7" s="102" t="s">
+      <c r="BT7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BU7" s="80" t="s">
+      <c r="BU7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BV7" s="84" t="s">
+      <c r="BV7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BW7" s="102" t="s">
+      <c r="BW7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="BX7" s="80" t="s">
+      <c r="BX7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="BY7" s="84" t="s">
+      <c r="BY7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="BZ7" s="102" t="s">
+      <c r="BZ7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CA7" s="80" t="s">
+      <c r="CA7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="CB7" s="84" t="s">
+      <c r="CB7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="CC7" s="102" t="s">
+      <c r="CC7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CD7" s="84" t="s">
+      <c r="CD7" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="CE7" s="84" t="s">
+      <c r="CE7" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="CF7" s="117" t="s">
+      <c r="CF7" s="74" t="s">
         <v>46</v>
       </c>
-      <c r="CG7" s="116" t="s">
+      <c r="CG7" s="36" t="s">
         <v>45</v>
       </c>
-      <c r="CH7" s="84" t="s">
+      <c r="CH7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="CI7" s="102" t="s">
+      <c r="CI7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CJ7" s="80" t="s">
+      <c r="CJ7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="CK7" s="84" t="s">
+      <c r="CK7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="CL7" s="102" t="s">
+      <c r="CL7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CM7" s="80" t="s">
+      <c r="CM7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="CN7" s="84" t="s">
+      <c r="CN7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="CO7" s="102" t="s">
+      <c r="CO7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CP7" s="80" t="s">
+      <c r="CP7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="CQ7" s="84" t="s">
+      <c r="CQ7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="CR7" s="102" t="s">
+      <c r="CR7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CS7" s="80" t="s">
+      <c r="CS7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="CT7" s="84" t="s">
+      <c r="CT7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="CU7" s="102" t="s">
+      <c r="CU7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CV7" s="80" t="s">
+      <c r="CV7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="CW7" s="84" t="s">
+      <c r="CW7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="CX7" s="102" t="s">
+      <c r="CX7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="CY7" s="80" t="s">
+      <c r="CY7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="CZ7" s="84" t="s">
+      <c r="CZ7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="DA7" s="102" t="s">
+      <c r="DA7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="DB7" s="80" t="s">
+      <c r="DB7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="DC7" s="84" t="s">
+      <c r="DC7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="DD7" s="102" t="s">
+      <c r="DD7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="DE7" s="80" t="s">
+      <c r="DE7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="DF7" s="84" t="s">
+      <c r="DF7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="DG7" s="102" t="s">
+      <c r="DG7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="DH7" s="80" t="s">
+      <c r="DH7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="DI7" s="84" t="s">
+      <c r="DI7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="DJ7" s="102" t="s">
+      <c r="DJ7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="DK7" s="80" t="s">
+      <c r="DK7" s="33" t="s">
         <v>45</v>
       </c>
-      <c r="DL7" s="84" t="s">
+      <c r="DL7" s="34" t="s">
         <v>481</v>
       </c>
-      <c r="DM7" s="102" t="s">
+      <c r="DM7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="DN7" s="84" t="s">
+      <c r="DN7" s="34" t="s">
         <v>47</v>
       </c>
-      <c r="DO7" s="84" t="s">
+      <c r="DO7" s="34" t="s">
         <v>482</v>
       </c>
-      <c r="DP7" s="102" t="s">
+      <c r="DP7" s="31" t="s">
         <v>46</v>
       </c>
-      <c r="DQ7" s="106"/>
-      <c r="DR7" s="103"/>
-      <c r="DS7" s="77"/>
-      <c r="DT7" s="78"/>
-      <c r="DU7" s="78"/>
-      <c r="DV7" s="79"/>
-      <c r="DW7" s="74" t="s">
+      <c r="DQ7" s="77"/>
+      <c r="DR7" s="32"/>
+      <c r="DS7" s="51"/>
+      <c r="DT7" s="52"/>
+      <c r="DU7" s="52"/>
+      <c r="DV7" s="53"/>
+      <c r="DW7" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="DX7" s="76"/>
-      <c r="DY7" s="74" t="s">
+      <c r="DX7" s="28"/>
+      <c r="DY7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="DZ7" s="75"/>
-      <c r="EA7" s="75"/>
-      <c r="EB7" s="76"/>
-      <c r="EC7" s="74" t="s">
+      <c r="DZ7" s="27"/>
+      <c r="EA7" s="27"/>
+      <c r="EB7" s="28"/>
+      <c r="EC7" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="ED7" s="76"/>
-      <c r="EE7" s="74" t="s">
+      <c r="ED7" s="28"/>
+      <c r="EE7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="EF7" s="75"/>
-      <c r="EG7" s="75"/>
-      <c r="EH7" s="76"/>
-      <c r="EI7" s="103"/>
-      <c r="EJ7" s="103"/>
-      <c r="EK7" s="77"/>
-      <c r="EL7" s="78"/>
-      <c r="EM7" s="78"/>
-      <c r="EN7" s="79"/>
-      <c r="EO7" s="74" t="s">
+      <c r="EF7" s="27"/>
+      <c r="EG7" s="27"/>
+      <c r="EH7" s="28"/>
+      <c r="EI7" s="32"/>
+      <c r="EJ7" s="32"/>
+      <c r="EK7" s="51"/>
+      <c r="EL7" s="52"/>
+      <c r="EM7" s="52"/>
+      <c r="EN7" s="53"/>
+      <c r="EO7" s="26" t="s">
         <v>50</v>
       </c>
-      <c r="EP7" s="76"/>
-      <c r="EQ7" s="74" t="s">
+      <c r="EP7" s="28"/>
+      <c r="EQ7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="ER7" s="75"/>
-      <c r="ES7" s="75"/>
-      <c r="ET7" s="76"/>
-      <c r="EU7" s="84" t="s">
+      <c r="ER7" s="27"/>
+      <c r="ES7" s="27"/>
+      <c r="ET7" s="28"/>
+      <c r="EU7" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="EV7" s="84"/>
-      <c r="EW7" s="74" t="s">
+      <c r="EV7" s="34"/>
+      <c r="EW7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="EX7" s="75"/>
-      <c r="EY7" s="75"/>
-      <c r="EZ7" s="76"/>
-      <c r="FA7" s="80"/>
-      <c r="FB7" s="80"/>
-      <c r="FC7" s="84"/>
-      <c r="FD7" s="84"/>
-      <c r="FE7" s="84"/>
-      <c r="FF7" s="84"/>
-      <c r="FG7" s="80"/>
-      <c r="FH7" s="80"/>
-      <c r="FI7" s="84"/>
-      <c r="FJ7" s="84"/>
-      <c r="FK7" s="84"/>
-      <c r="FL7" s="84"/>
-      <c r="FM7" s="114"/>
-      <c r="FN7" s="114"/>
-      <c r="FO7" s="77"/>
-      <c r="FP7" s="78"/>
-      <c r="FQ7" s="78"/>
-      <c r="FR7" s="79"/>
-      <c r="FS7" s="115" t="s">
+      <c r="EX7" s="27"/>
+      <c r="EY7" s="27"/>
+      <c r="EZ7" s="28"/>
+      <c r="FA7" s="33"/>
+      <c r="FB7" s="33"/>
+      <c r="FC7" s="34"/>
+      <c r="FD7" s="34"/>
+      <c r="FE7" s="34"/>
+      <c r="FF7" s="34"/>
+      <c r="FG7" s="33"/>
+      <c r="FH7" s="33"/>
+      <c r="FI7" s="34"/>
+      <c r="FJ7" s="34"/>
+      <c r="FK7" s="34"/>
+      <c r="FL7" s="34"/>
+      <c r="FM7" s="25"/>
+      <c r="FN7" s="25"/>
+      <c r="FO7" s="51"/>
+      <c r="FP7" s="52"/>
+      <c r="FQ7" s="52"/>
+      <c r="FR7" s="53"/>
+      <c r="FS7" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="FT7" s="116"/>
-      <c r="FU7" s="74" t="s">
+      <c r="FT7" s="36"/>
+      <c r="FU7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="FV7" s="75"/>
-      <c r="FW7" s="75"/>
-      <c r="FX7" s="76"/>
-      <c r="FY7" s="115" t="s">
+      <c r="FV7" s="27"/>
+      <c r="FW7" s="27"/>
+      <c r="FX7" s="28"/>
+      <c r="FY7" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="FZ7" s="116"/>
-      <c r="GA7" s="74" t="s">
+      <c r="FZ7" s="36"/>
+      <c r="GA7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="GB7" s="75"/>
-      <c r="GC7" s="75"/>
-      <c r="GD7" s="76"/>
-      <c r="GE7" s="115" t="s">
+      <c r="GB7" s="27"/>
+      <c r="GC7" s="27"/>
+      <c r="GD7" s="28"/>
+      <c r="GE7" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="GF7" s="116"/>
-      <c r="GG7" s="74" t="s">
+      <c r="GF7" s="36"/>
+      <c r="GG7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="GH7" s="75"/>
-      <c r="GI7" s="75"/>
-      <c r="GJ7" s="75"/>
-      <c r="GK7" s="112"/>
-      <c r="GL7" s="80"/>
-      <c r="GM7" s="84"/>
-      <c r="GN7" s="84"/>
-      <c r="GO7" s="84"/>
-      <c r="GP7" s="84"/>
-      <c r="GQ7" s="125" t="s">
+      <c r="GH7" s="27"/>
+      <c r="GI7" s="27"/>
+      <c r="GJ7" s="27"/>
+      <c r="GK7" s="89"/>
+      <c r="GL7" s="33"/>
+      <c r="GM7" s="34"/>
+      <c r="GN7" s="34"/>
+      <c r="GO7" s="34"/>
+      <c r="GP7" s="34"/>
+      <c r="GQ7" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="GR7" s="116"/>
-      <c r="GS7" s="74" t="s">
+      <c r="GR7" s="36"/>
+      <c r="GS7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="GT7" s="75"/>
-      <c r="GU7" s="75"/>
-      <c r="GV7" s="76"/>
-      <c r="GW7" s="115" t="s">
+      <c r="GT7" s="27"/>
+      <c r="GU7" s="27"/>
+      <c r="GV7" s="28"/>
+      <c r="GW7" s="35" t="s">
         <v>50</v>
       </c>
-      <c r="GX7" s="116"/>
-      <c r="GY7" s="74" t="s">
+      <c r="GX7" s="36"/>
+      <c r="GY7" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="GZ7" s="75"/>
-      <c r="HA7" s="75"/>
-      <c r="HB7" s="76"/>
+      <c r="GZ7" s="27"/>
+      <c r="HA7" s="27"/>
+      <c r="HB7" s="28"/>
     </row>
     <row r="8" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="43"/>
-      <c r="B8" s="43"/>
-      <c r="C8" s="43"/>
-      <c r="D8" s="43"/>
+      <c r="A8" s="38"/>
+      <c r="B8" s="38"/>
+      <c r="C8" s="38"/>
+      <c r="D8" s="38"/>
       <c r="E8" s="12"/>
-      <c r="F8" s="43"/>
+      <c r="F8" s="38"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="43"/>
-      <c r="I8" s="43"/>
-      <c r="J8" s="42" t="s">
+      <c r="H8" s="38"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="42" t="s">
+      <c r="K8" s="37" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="42" t="s">
+      <c r="L8" s="37" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="80"/>
-      <c r="N8" s="84"/>
-      <c r="O8" s="103"/>
-      <c r="P8" s="80"/>
-      <c r="Q8" s="84"/>
-      <c r="R8" s="103"/>
-      <c r="S8" s="80"/>
-      <c r="T8" s="84"/>
-      <c r="U8" s="103"/>
-      <c r="V8" s="80"/>
-      <c r="W8" s="84"/>
-      <c r="X8" s="103"/>
-      <c r="Y8" s="80"/>
-      <c r="Z8" s="84"/>
-      <c r="AA8" s="103"/>
-      <c r="AB8" s="80"/>
-      <c r="AC8" s="84"/>
-      <c r="AD8" s="103"/>
-      <c r="AE8" s="80"/>
-      <c r="AF8" s="84"/>
-      <c r="AG8" s="103"/>
-      <c r="AH8" s="80"/>
-      <c r="AI8" s="84"/>
-      <c r="AJ8" s="103"/>
-      <c r="AK8" s="80"/>
-      <c r="AL8" s="84"/>
-      <c r="AM8" s="103"/>
-      <c r="AN8" s="80"/>
-      <c r="AO8" s="84"/>
-      <c r="AP8" s="103"/>
-      <c r="AQ8" s="80"/>
-      <c r="AR8" s="84"/>
-      <c r="AS8" s="103"/>
-      <c r="AT8" s="84"/>
-      <c r="AU8" s="84"/>
-      <c r="AV8" s="123"/>
-      <c r="AW8" s="116"/>
-      <c r="AX8" s="84"/>
-      <c r="AY8" s="103"/>
-      <c r="AZ8" s="80"/>
-      <c r="BA8" s="84"/>
-      <c r="BB8" s="103"/>
-      <c r="BC8" s="80"/>
-      <c r="BD8" s="84"/>
-      <c r="BE8" s="103"/>
-      <c r="BF8" s="80"/>
-      <c r="BG8" s="84"/>
-      <c r="BH8" s="103"/>
-      <c r="BI8" s="80"/>
-      <c r="BJ8" s="84"/>
-      <c r="BK8" s="103"/>
-      <c r="BL8" s="80"/>
-      <c r="BM8" s="84"/>
-      <c r="BN8" s="103"/>
-      <c r="BO8" s="80"/>
-      <c r="BP8" s="84"/>
-      <c r="BQ8" s="103"/>
-      <c r="BR8" s="80"/>
-      <c r="BS8" s="84"/>
-      <c r="BT8" s="103"/>
-      <c r="BU8" s="80"/>
-      <c r="BV8" s="84"/>
-      <c r="BW8" s="103"/>
-      <c r="BX8" s="80"/>
-      <c r="BY8" s="84"/>
-      <c r="BZ8" s="103"/>
-      <c r="CA8" s="80"/>
-      <c r="CB8" s="84"/>
-      <c r="CC8" s="103"/>
-      <c r="CD8" s="84"/>
-      <c r="CE8" s="84"/>
-      <c r="CF8" s="118"/>
-      <c r="CG8" s="116"/>
-      <c r="CH8" s="84"/>
-      <c r="CI8" s="103"/>
-      <c r="CJ8" s="80"/>
-      <c r="CK8" s="84"/>
-      <c r="CL8" s="103"/>
-      <c r="CM8" s="80"/>
-      <c r="CN8" s="84"/>
-      <c r="CO8" s="103"/>
-      <c r="CP8" s="80"/>
-      <c r="CQ8" s="84"/>
-      <c r="CR8" s="103"/>
-      <c r="CS8" s="80"/>
-      <c r="CT8" s="84"/>
-      <c r="CU8" s="103"/>
-      <c r="CV8" s="80"/>
-      <c r="CW8" s="84"/>
-      <c r="CX8" s="103"/>
-      <c r="CY8" s="80"/>
-      <c r="CZ8" s="84"/>
-      <c r="DA8" s="103"/>
-      <c r="DB8" s="80"/>
-      <c r="DC8" s="84"/>
-      <c r="DD8" s="103"/>
-      <c r="DE8" s="80"/>
-      <c r="DF8" s="84"/>
-      <c r="DG8" s="103"/>
-      <c r="DH8" s="80"/>
-      <c r="DI8" s="84"/>
-      <c r="DJ8" s="103"/>
-      <c r="DK8" s="80"/>
-      <c r="DL8" s="84"/>
-      <c r="DM8" s="103"/>
-      <c r="DN8" s="84"/>
-      <c r="DO8" s="84"/>
-      <c r="DP8" s="103"/>
-      <c r="DQ8" s="106"/>
-      <c r="DR8" s="103"/>
-      <c r="DS8" s="104" t="s">
+      <c r="M8" s="33"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="33"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="33"/>
+      <c r="W8" s="34"/>
+      <c r="X8" s="32"/>
+      <c r="Y8" s="33"/>
+      <c r="Z8" s="34"/>
+      <c r="AA8" s="32"/>
+      <c r="AB8" s="33"/>
+      <c r="AC8" s="34"/>
+      <c r="AD8" s="32"/>
+      <c r="AE8" s="33"/>
+      <c r="AF8" s="34"/>
+      <c r="AG8" s="32"/>
+      <c r="AH8" s="33"/>
+      <c r="AI8" s="34"/>
+      <c r="AJ8" s="32"/>
+      <c r="AK8" s="33"/>
+      <c r="AL8" s="34"/>
+      <c r="AM8" s="32"/>
+      <c r="AN8" s="33"/>
+      <c r="AO8" s="34"/>
+      <c r="AP8" s="32"/>
+      <c r="AQ8" s="33"/>
+      <c r="AR8" s="34"/>
+      <c r="AS8" s="32"/>
+      <c r="AT8" s="34"/>
+      <c r="AU8" s="34"/>
+      <c r="AV8" s="41"/>
+      <c r="AW8" s="36"/>
+      <c r="AX8" s="34"/>
+      <c r="AY8" s="32"/>
+      <c r="AZ8" s="33"/>
+      <c r="BA8" s="34"/>
+      <c r="BB8" s="32"/>
+      <c r="BC8" s="33"/>
+      <c r="BD8" s="34"/>
+      <c r="BE8" s="32"/>
+      <c r="BF8" s="33"/>
+      <c r="BG8" s="34"/>
+      <c r="BH8" s="32"/>
+      <c r="BI8" s="33"/>
+      <c r="BJ8" s="34"/>
+      <c r="BK8" s="32"/>
+      <c r="BL8" s="33"/>
+      <c r="BM8" s="34"/>
+      <c r="BN8" s="32"/>
+      <c r="BO8" s="33"/>
+      <c r="BP8" s="34"/>
+      <c r="BQ8" s="32"/>
+      <c r="BR8" s="33"/>
+      <c r="BS8" s="34"/>
+      <c r="BT8" s="32"/>
+      <c r="BU8" s="33"/>
+      <c r="BV8" s="34"/>
+      <c r="BW8" s="32"/>
+      <c r="BX8" s="33"/>
+      <c r="BY8" s="34"/>
+      <c r="BZ8" s="32"/>
+      <c r="CA8" s="33"/>
+      <c r="CB8" s="34"/>
+      <c r="CC8" s="32"/>
+      <c r="CD8" s="34"/>
+      <c r="CE8" s="34"/>
+      <c r="CF8" s="75"/>
+      <c r="CG8" s="36"/>
+      <c r="CH8" s="34"/>
+      <c r="CI8" s="32"/>
+      <c r="CJ8" s="33"/>
+      <c r="CK8" s="34"/>
+      <c r="CL8" s="32"/>
+      <c r="CM8" s="33"/>
+      <c r="CN8" s="34"/>
+      <c r="CO8" s="32"/>
+      <c r="CP8" s="33"/>
+      <c r="CQ8" s="34"/>
+      <c r="CR8" s="32"/>
+      <c r="CS8" s="33"/>
+      <c r="CT8" s="34"/>
+      <c r="CU8" s="32"/>
+      <c r="CV8" s="33"/>
+      <c r="CW8" s="34"/>
+      <c r="CX8" s="32"/>
+      <c r="CY8" s="33"/>
+      <c r="CZ8" s="34"/>
+      <c r="DA8" s="32"/>
+      <c r="DB8" s="33"/>
+      <c r="DC8" s="34"/>
+      <c r="DD8" s="32"/>
+      <c r="DE8" s="33"/>
+      <c r="DF8" s="34"/>
+      <c r="DG8" s="32"/>
+      <c r="DH8" s="33"/>
+      <c r="DI8" s="34"/>
+      <c r="DJ8" s="32"/>
+      <c r="DK8" s="33"/>
+      <c r="DL8" s="34"/>
+      <c r="DM8" s="32"/>
+      <c r="DN8" s="34"/>
+      <c r="DO8" s="34"/>
+      <c r="DP8" s="32"/>
+      <c r="DQ8" s="77"/>
+      <c r="DR8" s="32"/>
+      <c r="DS8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="DT8" s="74" t="s">
+      <c r="DT8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="DU8" s="75"/>
-      <c r="DV8" s="76"/>
-      <c r="DW8" s="102" t="s">
+      <c r="DU8" s="27"/>
+      <c r="DV8" s="28"/>
+      <c r="DW8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="DX8" s="102" t="s">
+      <c r="DX8" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="DY8" s="104" t="s">
+      <c r="DY8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="DZ8" s="74" t="s">
+      <c r="DZ8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="EA8" s="75"/>
-      <c r="EB8" s="76"/>
-      <c r="EC8" s="102" t="s">
+      <c r="EA8" s="27"/>
+      <c r="EB8" s="28"/>
+      <c r="EC8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="ED8" s="102" t="s">
+      <c r="ED8" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="EE8" s="104" t="s">
+      <c r="EE8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="EF8" s="74" t="s">
+      <c r="EF8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="EG8" s="75"/>
-      <c r="EH8" s="76"/>
-      <c r="EI8" s="103"/>
-      <c r="EJ8" s="103"/>
-      <c r="EK8" s="104" t="s">
+      <c r="EG8" s="27"/>
+      <c r="EH8" s="28"/>
+      <c r="EI8" s="32"/>
+      <c r="EJ8" s="32"/>
+      <c r="EK8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="EL8" s="74" t="s">
+      <c r="EL8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="EM8" s="75"/>
-      <c r="EN8" s="76"/>
-      <c r="EO8" s="102" t="s">
+      <c r="EM8" s="27"/>
+      <c r="EN8" s="28"/>
+      <c r="EO8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="EP8" s="102" t="s">
+      <c r="EP8" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="EQ8" s="104" t="s">
+      <c r="EQ8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="ER8" s="74" t="s">
+      <c r="ER8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="ES8" s="75"/>
-      <c r="ET8" s="76"/>
-      <c r="EU8" s="102" t="s">
+      <c r="ES8" s="27"/>
+      <c r="ET8" s="28"/>
+      <c r="EU8" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="EV8" s="102" t="s">
+      <c r="EV8" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="EW8" s="104" t="s">
+      <c r="EW8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="EX8" s="74" t="s">
+      <c r="EX8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="EY8" s="75"/>
-      <c r="EZ8" s="76"/>
-      <c r="FA8" s="104" t="s">
+      <c r="EY8" s="27"/>
+      <c r="EZ8" s="28"/>
+      <c r="FA8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FB8" s="104" t="s">
+      <c r="FB8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="FC8" s="104" t="s">
+      <c r="FC8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FD8" s="74" t="s">
+      <c r="FD8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="FE8" s="75"/>
-      <c r="FF8" s="76"/>
-      <c r="FG8" s="104" t="s">
+      <c r="FE8" s="27"/>
+      <c r="FF8" s="28"/>
+      <c r="FG8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FH8" s="104" t="s">
+      <c r="FH8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="FI8" s="104" t="s">
+      <c r="FI8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FJ8" s="74" t="s">
+      <c r="FJ8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="FK8" s="75"/>
-      <c r="FL8" s="76"/>
-      <c r="FM8" s="114"/>
-      <c r="FN8" s="114"/>
-      <c r="FO8" s="104" t="s">
+      <c r="FK8" s="27"/>
+      <c r="FL8" s="28"/>
+      <c r="FM8" s="25"/>
+      <c r="FN8" s="25"/>
+      <c r="FO8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FP8" s="74" t="s">
+      <c r="FP8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="FQ8" s="75"/>
-      <c r="FR8" s="76"/>
-      <c r="FS8" s="104" t="s">
+      <c r="FQ8" s="27"/>
+      <c r="FR8" s="28"/>
+      <c r="FS8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FT8" s="104" t="s">
+      <c r="FT8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="FU8" s="104" t="s">
+      <c r="FU8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FV8" s="74" t="s">
+      <c r="FV8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="FW8" s="75"/>
-      <c r="FX8" s="76"/>
-      <c r="FY8" s="104" t="s">
+      <c r="FW8" s="27"/>
+      <c r="FX8" s="28"/>
+      <c r="FY8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="FZ8" s="104" t="s">
+      <c r="FZ8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="GA8" s="104" t="s">
+      <c r="GA8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="GB8" s="74" t="s">
+      <c r="GB8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="GC8" s="75"/>
-      <c r="GD8" s="76"/>
-      <c r="GE8" s="104" t="s">
+      <c r="GC8" s="27"/>
+      <c r="GD8" s="28"/>
+      <c r="GE8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="GF8" s="104" t="s">
+      <c r="GF8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="GG8" s="104" t="s">
+      <c r="GG8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="GH8" s="74" t="s">
+      <c r="GH8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="GI8" s="75"/>
-      <c r="GJ8" s="75"/>
-      <c r="GK8" s="112"/>
-      <c r="GL8" s="80"/>
-      <c r="GM8" s="124" t="s">
+      <c r="GI8" s="27"/>
+      <c r="GJ8" s="27"/>
+      <c r="GK8" s="89"/>
+      <c r="GL8" s="33"/>
+      <c r="GM8" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="GN8" s="74" t="s">
+      <c r="GN8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="GO8" s="75"/>
-      <c r="GP8" s="76"/>
-      <c r="GQ8" s="104" t="s">
+      <c r="GO8" s="27"/>
+      <c r="GP8" s="28"/>
+      <c r="GQ8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="GR8" s="104" t="s">
+      <c r="GR8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="GS8" s="104" t="s">
+      <c r="GS8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="GT8" s="74" t="s">
+      <c r="GT8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="GU8" s="75"/>
-      <c r="GV8" s="76"/>
-      <c r="GW8" s="104" t="s">
+      <c r="GU8" s="27"/>
+      <c r="GV8" s="28"/>
+      <c r="GW8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="GX8" s="104" t="s">
+      <c r="GX8" s="24" t="s">
         <v>55</v>
       </c>
-      <c r="GY8" s="104" t="s">
+      <c r="GY8" s="24" t="s">
         <v>54</v>
       </c>
-      <c r="GZ8" s="74" t="s">
+      <c r="GZ8" s="26" t="s">
         <v>21</v>
       </c>
-      <c r="HA8" s="75"/>
-      <c r="HB8" s="76"/>
+      <c r="HA8" s="27"/>
+      <c r="HB8" s="28"/>
     </row>
     <row r="9" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="43"/>
-      <c r="B9" s="43"/>
-      <c r="C9" s="43"/>
-      <c r="D9" s="43"/>
+      <c r="A9" s="38"/>
+      <c r="B9" s="38"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
       <c r="E9" s="14"/>
-      <c r="F9" s="43"/>
+      <c r="F9" s="38"/>
       <c r="G9" s="14"/>
-      <c r="H9" s="43"/>
-      <c r="I9" s="43"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="43"/>
-      <c r="L9" s="43"/>
-      <c r="M9" s="104"/>
-      <c r="N9" s="102"/>
-      <c r="O9" s="103"/>
-      <c r="P9" s="104"/>
-      <c r="Q9" s="102"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="104"/>
-      <c r="T9" s="102"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="104"/>
-      <c r="W9" s="102"/>
-      <c r="X9" s="103"/>
-      <c r="Y9" s="104"/>
-      <c r="Z9" s="102"/>
-      <c r="AA9" s="103"/>
-      <c r="AB9" s="104"/>
-      <c r="AC9" s="102"/>
-      <c r="AD9" s="103"/>
-      <c r="AE9" s="104"/>
-      <c r="AF9" s="102"/>
-      <c r="AG9" s="103"/>
-      <c r="AH9" s="104"/>
-      <c r="AI9" s="102"/>
-      <c r="AJ9" s="103"/>
-      <c r="AK9" s="104"/>
-      <c r="AL9" s="102"/>
-      <c r="AM9" s="103"/>
-      <c r="AN9" s="104"/>
-      <c r="AO9" s="102"/>
-      <c r="AP9" s="103"/>
-      <c r="AQ9" s="104"/>
-      <c r="AR9" s="102"/>
-      <c r="AS9" s="103"/>
-      <c r="AT9" s="102"/>
-      <c r="AU9" s="102"/>
-      <c r="AV9" s="123"/>
-      <c r="AW9" s="124"/>
-      <c r="AX9" s="102"/>
-      <c r="AY9" s="103"/>
-      <c r="AZ9" s="104"/>
-      <c r="BA9" s="102"/>
-      <c r="BB9" s="103"/>
-      <c r="BC9" s="104"/>
-      <c r="BD9" s="102"/>
-      <c r="BE9" s="103"/>
-      <c r="BF9" s="104"/>
-      <c r="BG9" s="102"/>
-      <c r="BH9" s="103"/>
-      <c r="BI9" s="104"/>
-      <c r="BJ9" s="102"/>
-      <c r="BK9" s="103"/>
-      <c r="BL9" s="104"/>
-      <c r="BM9" s="102"/>
-      <c r="BN9" s="103"/>
-      <c r="BO9" s="104"/>
-      <c r="BP9" s="102"/>
-      <c r="BQ9" s="103"/>
-      <c r="BR9" s="104"/>
-      <c r="BS9" s="102"/>
-      <c r="BT9" s="103"/>
-      <c r="BU9" s="104"/>
-      <c r="BV9" s="102"/>
-      <c r="BW9" s="103"/>
-      <c r="BX9" s="104"/>
-      <c r="BY9" s="102"/>
-      <c r="BZ9" s="103"/>
-      <c r="CA9" s="104"/>
-      <c r="CB9" s="102"/>
-      <c r="CC9" s="103"/>
-      <c r="CD9" s="102"/>
-      <c r="CE9" s="102"/>
-      <c r="CF9" s="118"/>
-      <c r="CG9" s="124"/>
-      <c r="CH9" s="102"/>
-      <c r="CI9" s="103"/>
-      <c r="CJ9" s="104"/>
-      <c r="CK9" s="102"/>
-      <c r="CL9" s="103"/>
-      <c r="CM9" s="104"/>
-      <c r="CN9" s="102"/>
-      <c r="CO9" s="103"/>
-      <c r="CP9" s="104"/>
-      <c r="CQ9" s="102"/>
-      <c r="CR9" s="103"/>
-      <c r="CS9" s="104"/>
-      <c r="CT9" s="102"/>
-      <c r="CU9" s="103"/>
-      <c r="CV9" s="104"/>
-      <c r="CW9" s="102"/>
-      <c r="CX9" s="103"/>
-      <c r="CY9" s="104"/>
-      <c r="CZ9" s="102"/>
-      <c r="DA9" s="103"/>
-      <c r="DB9" s="104"/>
-      <c r="DC9" s="102"/>
-      <c r="DD9" s="103"/>
-      <c r="DE9" s="104"/>
-      <c r="DF9" s="102"/>
-      <c r="DG9" s="103"/>
-      <c r="DH9" s="104"/>
-      <c r="DI9" s="102"/>
-      <c r="DJ9" s="103"/>
-      <c r="DK9" s="104"/>
-      <c r="DL9" s="102"/>
-      <c r="DM9" s="103"/>
-      <c r="DN9" s="102"/>
-      <c r="DO9" s="102"/>
-      <c r="DP9" s="103"/>
-      <c r="DQ9" s="106"/>
-      <c r="DR9" s="103"/>
-      <c r="DS9" s="114"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="32"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="32"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="32"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="32"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="32"/>
+      <c r="AH9" s="24"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="32"/>
+      <c r="AK9" s="24"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="32"/>
+      <c r="AN9" s="24"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="32"/>
+      <c r="AQ9" s="24"/>
+      <c r="AR9" s="31"/>
+      <c r="AS9" s="32"/>
+      <c r="AT9" s="31"/>
+      <c r="AU9" s="31"/>
+      <c r="AV9" s="41"/>
+      <c r="AW9" s="29"/>
+      <c r="AX9" s="31"/>
+      <c r="AY9" s="32"/>
+      <c r="AZ9" s="24"/>
+      <c r="BA9" s="31"/>
+      <c r="BB9" s="32"/>
+      <c r="BC9" s="24"/>
+      <c r="BD9" s="31"/>
+      <c r="BE9" s="32"/>
+      <c r="BF9" s="24"/>
+      <c r="BG9" s="31"/>
+      <c r="BH9" s="32"/>
+      <c r="BI9" s="24"/>
+      <c r="BJ9" s="31"/>
+      <c r="BK9" s="32"/>
+      <c r="BL9" s="24"/>
+      <c r="BM9" s="31"/>
+      <c r="BN9" s="32"/>
+      <c r="BO9" s="24"/>
+      <c r="BP9" s="31"/>
+      <c r="BQ9" s="32"/>
+      <c r="BR9" s="24"/>
+      <c r="BS9" s="31"/>
+      <c r="BT9" s="32"/>
+      <c r="BU9" s="24"/>
+      <c r="BV9" s="31"/>
+      <c r="BW9" s="32"/>
+      <c r="BX9" s="24"/>
+      <c r="BY9" s="31"/>
+      <c r="BZ9" s="32"/>
+      <c r="CA9" s="24"/>
+      <c r="CB9" s="31"/>
+      <c r="CC9" s="32"/>
+      <c r="CD9" s="31"/>
+      <c r="CE9" s="31"/>
+      <c r="CF9" s="75"/>
+      <c r="CG9" s="29"/>
+      <c r="CH9" s="31"/>
+      <c r="CI9" s="32"/>
+      <c r="CJ9" s="24"/>
+      <c r="CK9" s="31"/>
+      <c r="CL9" s="32"/>
+      <c r="CM9" s="24"/>
+      <c r="CN9" s="31"/>
+      <c r="CO9" s="32"/>
+      <c r="CP9" s="24"/>
+      <c r="CQ9" s="31"/>
+      <c r="CR9" s="32"/>
+      <c r="CS9" s="24"/>
+      <c r="CT9" s="31"/>
+      <c r="CU9" s="32"/>
+      <c r="CV9" s="24"/>
+      <c r="CW9" s="31"/>
+      <c r="CX9" s="32"/>
+      <c r="CY9" s="24"/>
+      <c r="CZ9" s="31"/>
+      <c r="DA9" s="32"/>
+      <c r="DB9" s="24"/>
+      <c r="DC9" s="31"/>
+      <c r="DD9" s="32"/>
+      <c r="DE9" s="24"/>
+      <c r="DF9" s="31"/>
+      <c r="DG9" s="32"/>
+      <c r="DH9" s="24"/>
+      <c r="DI9" s="31"/>
+      <c r="DJ9" s="32"/>
+      <c r="DK9" s="24"/>
+      <c r="DL9" s="31"/>
+      <c r="DM9" s="32"/>
+      <c r="DN9" s="31"/>
+      <c r="DO9" s="31"/>
+      <c r="DP9" s="32"/>
+      <c r="DQ9" s="77"/>
+      <c r="DR9" s="32"/>
+      <c r="DS9" s="25"/>
       <c r="DT9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5226,9 +5227,9 @@
       <c r="DV9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="DW9" s="103"/>
-      <c r="DX9" s="103"/>
-      <c r="DY9" s="114"/>
+      <c r="DW9" s="32"/>
+      <c r="DX9" s="32"/>
+      <c r="DY9" s="25"/>
       <c r="DZ9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5238,9 +5239,9 @@
       <c r="EB9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EC9" s="103"/>
-      <c r="ED9" s="103"/>
-      <c r="EE9" s="114"/>
+      <c r="EC9" s="32"/>
+      <c r="ED9" s="32"/>
+      <c r="EE9" s="25"/>
       <c r="EF9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5250,9 +5251,9 @@
       <c r="EH9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EI9" s="103"/>
-      <c r="EJ9" s="103"/>
-      <c r="EK9" s="114"/>
+      <c r="EI9" s="32"/>
+      <c r="EJ9" s="32"/>
+      <c r="EK9" s="25"/>
       <c r="EL9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5262,9 +5263,9 @@
       <c r="EN9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EO9" s="103"/>
-      <c r="EP9" s="103"/>
-      <c r="EQ9" s="114"/>
+      <c r="EO9" s="32"/>
+      <c r="EP9" s="32"/>
+      <c r="EQ9" s="25"/>
       <c r="ER9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5274,9 +5275,9 @@
       <c r="ET9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EU9" s="103"/>
-      <c r="EV9" s="103"/>
-      <c r="EW9" s="114"/>
+      <c r="EU9" s="32"/>
+      <c r="EV9" s="32"/>
+      <c r="EW9" s="25"/>
       <c r="EX9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5286,9 +5287,9 @@
       <c r="EZ9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FA9" s="114"/>
-      <c r="FB9" s="114"/>
-      <c r="FC9" s="114"/>
+      <c r="FA9" s="25"/>
+      <c r="FB9" s="25"/>
+      <c r="FC9" s="25"/>
       <c r="FD9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5298,9 +5299,9 @@
       <c r="FF9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FG9" s="114"/>
-      <c r="FH9" s="114"/>
-      <c r="FI9" s="114"/>
+      <c r="FG9" s="25"/>
+      <c r="FH9" s="25"/>
+      <c r="FI9" s="25"/>
       <c r="FJ9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5310,9 +5311,9 @@
       <c r="FL9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FM9" s="114"/>
-      <c r="FN9" s="114"/>
-      <c r="FO9" s="114"/>
+      <c r="FM9" s="25"/>
+      <c r="FN9" s="25"/>
+      <c r="FO9" s="25"/>
       <c r="FP9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5322,9 +5323,9 @@
       <c r="FR9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FS9" s="114"/>
-      <c r="FT9" s="114"/>
-      <c r="FU9" s="114"/>
+      <c r="FS9" s="25"/>
+      <c r="FT9" s="25"/>
+      <c r="FU9" s="25"/>
       <c r="FV9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5334,9 +5335,9 @@
       <c r="FX9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FY9" s="114"/>
-      <c r="FZ9" s="114"/>
-      <c r="GA9" s="114"/>
+      <c r="FY9" s="25"/>
+      <c r="FZ9" s="25"/>
+      <c r="GA9" s="25"/>
       <c r="GB9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5346,9 +5347,9 @@
       <c r="GD9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="GE9" s="114"/>
-      <c r="GF9" s="114"/>
-      <c r="GG9" s="114"/>
+      <c r="GE9" s="25"/>
+      <c r="GF9" s="25"/>
+      <c r="GG9" s="25"/>
       <c r="GH9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5358,9 +5359,9 @@
       <c r="GJ9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="GK9" s="113"/>
-      <c r="GL9" s="104"/>
-      <c r="GM9" s="126"/>
+      <c r="GK9" s="90"/>
+      <c r="GL9" s="24"/>
+      <c r="GM9" s="30"/>
       <c r="GN9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5370,9 +5371,9 @@
       <c r="GP9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="GQ9" s="114"/>
-      <c r="GR9" s="114"/>
-      <c r="GS9" s="114"/>
+      <c r="GQ9" s="25"/>
+      <c r="GR9" s="25"/>
+      <c r="GS9" s="25"/>
       <c r="GT9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5382,9 +5383,9 @@
       <c r="GV9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="GW9" s="114"/>
-      <c r="GX9" s="114"/>
-      <c r="GY9" s="114"/>
+      <c r="GW9" s="25"/>
+      <c r="GX9" s="25"/>
+      <c r="GY9" s="25"/>
       <c r="GZ9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5395,1313 +5396,1473 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:210" s="23" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="32"/>
-      <c r="B10" s="33" t="s">
+    <row r="10" spans="1:210" s="19" customFormat="1" ht="24.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="20"/>
+      <c r="B10" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="C10" s="33"/>
-      <c r="D10" s="19" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="115" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="19" t="s">
+      <c r="E10" s="115" t="s">
         <v>438</v>
       </c>
-      <c r="F10" s="19" t="s">
+      <c r="F10" s="115" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G10" s="115" t="s">
         <v>439</v>
       </c>
-      <c r="H10" s="19" t="s">
+      <c r="H10" s="115" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="19" t="s">
+      <c r="I10" s="115" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="19" t="s">
+      <c r="J10" s="115" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="19" t="s">
+      <c r="K10" s="115" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="19" t="s">
+      <c r="L10" s="115" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="20" t="s">
+      <c r="M10" s="116" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="20" t="s">
+      <c r="N10" s="116" t="s">
         <v>67</v>
       </c>
-      <c r="O10" s="21" t="s">
+      <c r="O10" s="117" t="s">
         <v>440</v>
       </c>
-      <c r="P10" s="20" t="s">
+      <c r="P10" s="116" t="s">
         <v>68</v>
       </c>
-      <c r="Q10" s="20" t="s">
+      <c r="Q10" s="116" t="s">
         <v>69</v>
       </c>
-      <c r="R10" s="21" t="s">
+      <c r="R10" s="117" t="s">
         <v>441</v>
       </c>
-      <c r="S10" s="20" t="s">
+      <c r="S10" s="116" t="s">
         <v>70</v>
       </c>
-      <c r="T10" s="20" t="s">
+      <c r="T10" s="116" t="s">
         <v>71</v>
       </c>
-      <c r="U10" s="21" t="s">
+      <c r="U10" s="117" t="s">
         <v>442</v>
       </c>
-      <c r="V10" s="20" t="s">
+      <c r="V10" s="116" t="s">
         <v>72</v>
       </c>
-      <c r="W10" s="20" t="s">
+      <c r="W10" s="116" t="s">
         <v>73</v>
       </c>
-      <c r="X10" s="21" t="s">
+      <c r="X10" s="117" t="s">
         <v>443</v>
       </c>
-      <c r="Y10" s="20" t="s">
+      <c r="Y10" s="116" t="s">
         <v>74</v>
       </c>
-      <c r="Z10" s="20" t="s">
+      <c r="Z10" s="116" t="s">
         <v>75</v>
       </c>
-      <c r="AA10" s="21" t="s">
+      <c r="AA10" s="117" t="s">
         <v>444</v>
       </c>
-      <c r="AB10" s="20" t="s">
+      <c r="AB10" s="116" t="s">
         <v>76</v>
       </c>
-      <c r="AC10" s="20" t="s">
+      <c r="AC10" s="116" t="s">
         <v>77</v>
       </c>
-      <c r="AD10" s="21" t="s">
+      <c r="AD10" s="117" t="s">
         <v>445</v>
       </c>
-      <c r="AE10" s="20" t="s">
+      <c r="AE10" s="116" t="s">
         <v>78</v>
       </c>
-      <c r="AF10" s="20" t="s">
+      <c r="AF10" s="116" t="s">
         <v>79</v>
       </c>
-      <c r="AG10" s="21" t="s">
+      <c r="AG10" s="117" t="s">
         <v>446</v>
       </c>
-      <c r="AH10" s="20" t="s">
+      <c r="AH10" s="116" t="s">
         <v>80</v>
       </c>
-      <c r="AI10" s="20" t="s">
+      <c r="AI10" s="116" t="s">
         <v>81</v>
       </c>
-      <c r="AJ10" s="21" t="s">
+      <c r="AJ10" s="117" t="s">
         <v>447</v>
       </c>
-      <c r="AK10" s="20" t="s">
+      <c r="AK10" s="116" t="s">
         <v>82</v>
       </c>
-      <c r="AL10" s="20" t="s">
+      <c r="AL10" s="116" t="s">
         <v>83</v>
       </c>
-      <c r="AM10" s="21" t="s">
+      <c r="AM10" s="117" t="s">
         <v>448</v>
       </c>
-      <c r="AN10" s="20" t="s">
+      <c r="AN10" s="116" t="s">
         <v>84</v>
       </c>
-      <c r="AO10" s="20" t="s">
+      <c r="AO10" s="116" t="s">
         <v>85</v>
       </c>
-      <c r="AP10" s="21" t="s">
+      <c r="AP10" s="117" t="s">
         <v>449</v>
       </c>
-      <c r="AQ10" s="20" t="s">
+      <c r="AQ10" s="116" t="s">
         <v>86</v>
       </c>
-      <c r="AR10" s="20" t="s">
+      <c r="AR10" s="116" t="s">
         <v>87</v>
       </c>
-      <c r="AS10" s="21" t="s">
+      <c r="AS10" s="117" t="s">
         <v>450</v>
       </c>
-      <c r="AT10" s="21" t="s">
+      <c r="AT10" s="117" t="s">
         <v>88</v>
       </c>
-      <c r="AU10" s="21" t="s">
+      <c r="AU10" s="117" t="s">
         <v>89</v>
       </c>
-      <c r="AV10" s="21" t="s">
+      <c r="AV10" s="117" t="s">
         <v>451</v>
       </c>
-      <c r="AW10" s="20" t="s">
+      <c r="AW10" s="116" t="s">
         <v>90</v>
       </c>
-      <c r="AX10" s="20" t="s">
+      <c r="AX10" s="116" t="s">
         <v>91</v>
       </c>
-      <c r="AY10" s="21" t="s">
+      <c r="AY10" s="117" t="s">
         <v>452</v>
       </c>
-      <c r="AZ10" s="20" t="s">
+      <c r="AZ10" s="116" t="s">
         <v>92</v>
       </c>
-      <c r="BA10" s="20" t="s">
+      <c r="BA10" s="116" t="s">
         <v>93</v>
       </c>
-      <c r="BB10" s="21" t="s">
+      <c r="BB10" s="117" t="s">
         <v>453</v>
       </c>
-      <c r="BC10" s="20" t="s">
+      <c r="BC10" s="116" t="s">
         <v>94</v>
       </c>
-      <c r="BD10" s="20" t="s">
+      <c r="BD10" s="116" t="s">
         <v>95</v>
       </c>
-      <c r="BE10" s="21" t="s">
+      <c r="BE10" s="117" t="s">
         <v>454</v>
       </c>
-      <c r="BF10" s="20" t="s">
+      <c r="BF10" s="116" t="s">
         <v>96</v>
       </c>
-      <c r="BG10" s="20" t="s">
+      <c r="BG10" s="116" t="s">
         <v>97</v>
       </c>
-      <c r="BH10" s="21" t="s">
+      <c r="BH10" s="117" t="s">
         <v>455</v>
       </c>
-      <c r="BI10" s="20" t="s">
+      <c r="BI10" s="116" t="s">
         <v>98</v>
       </c>
-      <c r="BJ10" s="20" t="s">
+      <c r="BJ10" s="116" t="s">
         <v>99</v>
       </c>
-      <c r="BK10" s="21" t="s">
+      <c r="BK10" s="117" t="s">
         <v>456</v>
       </c>
-      <c r="BL10" s="20" t="s">
+      <c r="BL10" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="BM10" s="20" t="s">
+      <c r="BM10" s="116" t="s">
         <v>101</v>
       </c>
-      <c r="BN10" s="21" t="s">
+      <c r="BN10" s="117" t="s">
         <v>457</v>
       </c>
-      <c r="BO10" s="20" t="s">
+      <c r="BO10" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="BP10" s="20" t="s">
+      <c r="BP10" s="116" t="s">
         <v>103</v>
       </c>
-      <c r="BQ10" s="21" t="s">
+      <c r="BQ10" s="117" t="s">
         <v>458</v>
       </c>
-      <c r="BR10" s="20" t="s">
+      <c r="BR10" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="BS10" s="20" t="s">
+      <c r="BS10" s="116" t="s">
         <v>105</v>
       </c>
-      <c r="BT10" s="21" t="s">
+      <c r="BT10" s="117" t="s">
         <v>459</v>
       </c>
-      <c r="BU10" s="20" t="s">
+      <c r="BU10" s="116" t="s">
         <v>106</v>
       </c>
-      <c r="BV10" s="20" t="s">
+      <c r="BV10" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="BW10" s="21" t="s">
+      <c r="BW10" s="117" t="s">
         <v>460</v>
       </c>
-      <c r="BX10" s="20" t="s">
+      <c r="BX10" s="116" t="s">
         <v>108</v>
       </c>
-      <c r="BY10" s="20" t="s">
+      <c r="BY10" s="116" t="s">
         <v>109</v>
       </c>
-      <c r="BZ10" s="21" t="s">
+      <c r="BZ10" s="117" t="s">
         <v>461</v>
       </c>
-      <c r="CA10" s="20" t="s">
+      <c r="CA10" s="116" t="s">
         <v>110</v>
       </c>
-      <c r="CB10" s="20" t="s">
+      <c r="CB10" s="116" t="s">
         <v>111</v>
       </c>
-      <c r="CC10" s="21" t="s">
+      <c r="CC10" s="117" t="s">
         <v>462</v>
       </c>
-      <c r="CD10" s="21" t="s">
+      <c r="CD10" s="117" t="s">
         <v>112</v>
       </c>
-      <c r="CE10" s="21" t="s">
+      <c r="CE10" s="117" t="s">
         <v>113</v>
       </c>
-      <c r="CF10" s="21" t="s">
+      <c r="CF10" s="117" t="s">
         <v>463</v>
       </c>
-      <c r="CG10" s="20" t="s">
+      <c r="CG10" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="CH10" s="20" t="s">
+      <c r="CH10" s="116" t="s">
         <v>115</v>
       </c>
-      <c r="CI10" s="21" t="s">
+      <c r="CI10" s="117" t="s">
         <v>464</v>
       </c>
-      <c r="CJ10" s="20" t="s">
+      <c r="CJ10" s="116" t="s">
         <v>116</v>
       </c>
-      <c r="CK10" s="20" t="s">
+      <c r="CK10" s="116" t="s">
         <v>117</v>
       </c>
-      <c r="CL10" s="21" t="s">
+      <c r="CL10" s="117" t="s">
         <v>465</v>
       </c>
-      <c r="CM10" s="20" t="s">
+      <c r="CM10" s="116" t="s">
         <v>118</v>
       </c>
-      <c r="CN10" s="20" t="s">
+      <c r="CN10" s="116" t="s">
         <v>119</v>
       </c>
-      <c r="CO10" s="21" t="s">
+      <c r="CO10" s="117" t="s">
         <v>466</v>
       </c>
-      <c r="CP10" s="20" t="s">
+      <c r="CP10" s="116" t="s">
         <v>120</v>
       </c>
-      <c r="CQ10" s="20" t="s">
+      <c r="CQ10" s="116" t="s">
         <v>121</v>
       </c>
-      <c r="CR10" s="21" t="s">
+      <c r="CR10" s="117" t="s">
         <v>467</v>
       </c>
-      <c r="CS10" s="20" t="s">
+      <c r="CS10" s="116" t="s">
         <v>122</v>
       </c>
-      <c r="CT10" s="20" t="s">
+      <c r="CT10" s="116" t="s">
         <v>123</v>
       </c>
-      <c r="CU10" s="21" t="s">
+      <c r="CU10" s="117" t="s">
         <v>468</v>
       </c>
-      <c r="CV10" s="20" t="s">
+      <c r="CV10" s="116" t="s">
         <v>124</v>
       </c>
-      <c r="CW10" s="20" t="s">
+      <c r="CW10" s="116" t="s">
         <v>125</v>
       </c>
-      <c r="CX10" s="21" t="s">
+      <c r="CX10" s="117" t="s">
         <v>469</v>
       </c>
-      <c r="CY10" s="20" t="s">
+      <c r="CY10" s="116" t="s">
         <v>126</v>
       </c>
-      <c r="CZ10" s="20" t="s">
+      <c r="CZ10" s="116" t="s">
         <v>127</v>
       </c>
-      <c r="DA10" s="21" t="s">
+      <c r="DA10" s="117" t="s">
         <v>470</v>
       </c>
-      <c r="DB10" s="20" t="s">
+      <c r="DB10" s="116" t="s">
         <v>128</v>
       </c>
-      <c r="DC10" s="20" t="s">
+      <c r="DC10" s="116" t="s">
         <v>129</v>
       </c>
-      <c r="DD10" s="21" t="s">
+      <c r="DD10" s="117" t="s">
         <v>471</v>
       </c>
-      <c r="DE10" s="20" t="s">
+      <c r="DE10" s="116" t="s">
         <v>130</v>
       </c>
-      <c r="DF10" s="20" t="s">
+      <c r="DF10" s="116" t="s">
         <v>131</v>
       </c>
-      <c r="DG10" s="21" t="s">
+      <c r="DG10" s="117" t="s">
         <v>472</v>
       </c>
-      <c r="DH10" s="20" t="s">
+      <c r="DH10" s="116" t="s">
         <v>132</v>
       </c>
-      <c r="DI10" s="20" t="s">
+      <c r="DI10" s="116" t="s">
         <v>133</v>
       </c>
-      <c r="DJ10" s="21" t="s">
+      <c r="DJ10" s="117" t="s">
         <v>473</v>
       </c>
-      <c r="DK10" s="20" t="s">
+      <c r="DK10" s="116" t="s">
         <v>134</v>
       </c>
-      <c r="DL10" s="20" t="s">
+      <c r="DL10" s="116" t="s">
         <v>135</v>
       </c>
-      <c r="DM10" s="21" t="s">
+      <c r="DM10" s="117" t="s">
         <v>474</v>
       </c>
-      <c r="DN10" s="21" t="s">
+      <c r="DN10" s="117" t="s">
         <v>136</v>
       </c>
-      <c r="DO10" s="21" t="s">
+      <c r="DO10" s="117" t="s">
         <v>137</v>
       </c>
-      <c r="DP10" s="21" t="s">
+      <c r="DP10" s="117" t="s">
         <v>475</v>
       </c>
-      <c r="DQ10" s="20" t="s">
+      <c r="DQ10" s="116" t="s">
         <v>138</v>
       </c>
-      <c r="DR10" s="21" t="s">
+      <c r="DR10" s="117" t="s">
         <v>139</v>
       </c>
-      <c r="DS10" s="21" t="s">
+      <c r="DS10" s="117" t="s">
         <v>140</v>
       </c>
-      <c r="DT10" s="21" t="s">
+      <c r="DT10" s="117" t="s">
         <v>141</v>
       </c>
-      <c r="DU10" s="21" t="s">
+      <c r="DU10" s="117" t="s">
         <v>142</v>
       </c>
-      <c r="DV10" s="21" t="s">
+      <c r="DV10" s="117" t="s">
         <v>143</v>
       </c>
-      <c r="DW10" s="20" t="s">
+      <c r="DW10" s="116" t="s">
         <v>144</v>
       </c>
-      <c r="DX10" s="20" t="s">
+      <c r="DX10" s="116" t="s">
         <v>145</v>
       </c>
-      <c r="DY10" s="21" t="s">
+      <c r="DY10" s="117" t="s">
         <v>146</v>
       </c>
-      <c r="DZ10" s="21" t="s">
+      <c r="DZ10" s="117" t="s">
         <v>147</v>
       </c>
-      <c r="EA10" s="21" t="s">
+      <c r="EA10" s="117" t="s">
         <v>148</v>
       </c>
-      <c r="EB10" s="21" t="s">
+      <c r="EB10" s="117" t="s">
         <v>149</v>
       </c>
-      <c r="EC10" s="20" t="s">
+      <c r="EC10" s="116" t="s">
         <v>150</v>
       </c>
-      <c r="ED10" s="20" t="s">
+      <c r="ED10" s="116" t="s">
         <v>151</v>
       </c>
-      <c r="EE10" s="21" t="s">
+      <c r="EE10" s="117" t="s">
         <v>152</v>
       </c>
-      <c r="EF10" s="21" t="s">
+      <c r="EF10" s="117" t="s">
         <v>153</v>
       </c>
-      <c r="EG10" s="21" t="s">
+      <c r="EG10" s="117" t="s">
         <v>154</v>
       </c>
-      <c r="EH10" s="21" t="s">
+      <c r="EH10" s="117" t="s">
         <v>155</v>
       </c>
-      <c r="EI10" s="21" t="s">
+      <c r="EI10" s="117" t="s">
         <v>156</v>
       </c>
-      <c r="EJ10" s="21" t="s">
+      <c r="EJ10" s="117" t="s">
         <v>157</v>
       </c>
-      <c r="EK10" s="21" t="s">
+      <c r="EK10" s="117" t="s">
         <v>158</v>
       </c>
-      <c r="EL10" s="21" t="s">
+      <c r="EL10" s="117" t="s">
         <v>159</v>
       </c>
-      <c r="EM10" s="21" t="s">
+      <c r="EM10" s="117" t="s">
         <v>160</v>
       </c>
-      <c r="EN10" s="21" t="s">
+      <c r="EN10" s="117" t="s">
         <v>161</v>
       </c>
-      <c r="EO10" s="20" t="s">
+      <c r="EO10" s="116" t="s">
         <v>162</v>
       </c>
-      <c r="EP10" s="20" t="s">
+      <c r="EP10" s="116" t="s">
         <v>163</v>
       </c>
-      <c r="EQ10" s="21" t="s">
+      <c r="EQ10" s="117" t="s">
         <v>164</v>
       </c>
-      <c r="ER10" s="21" t="s">
+      <c r="ER10" s="117" t="s">
         <v>165</v>
       </c>
-      <c r="ES10" s="21" t="s">
+      <c r="ES10" s="117" t="s">
         <v>166</v>
       </c>
-      <c r="ET10" s="21" t="s">
+      <c r="ET10" s="117" t="s">
         <v>167</v>
       </c>
-      <c r="EU10" s="20" t="s">
+      <c r="EU10" s="116" t="s">
         <v>168</v>
       </c>
-      <c r="EV10" s="20" t="s">
+      <c r="EV10" s="116" t="s">
         <v>169</v>
       </c>
-      <c r="EW10" s="21" t="s">
+      <c r="EW10" s="117" t="s">
         <v>170</v>
       </c>
-      <c r="EX10" s="21" t="s">
+      <c r="EX10" s="117" t="s">
         <v>171</v>
       </c>
-      <c r="EY10" s="21" t="s">
+      <c r="EY10" s="117" t="s">
         <v>172</v>
       </c>
-      <c r="EZ10" s="21" t="s">
+      <c r="EZ10" s="117" t="s">
         <v>173</v>
       </c>
-      <c r="FA10" s="20" t="s">
+      <c r="FA10" s="116" t="s">
         <v>174</v>
       </c>
-      <c r="FB10" s="20" t="s">
+      <c r="FB10" s="116" t="s">
         <v>175</v>
       </c>
-      <c r="FC10" s="21" t="s">
+      <c r="FC10" s="117" t="s">
         <v>176</v>
       </c>
-      <c r="FD10" s="21" t="s">
+      <c r="FD10" s="117" t="s">
         <v>177</v>
       </c>
-      <c r="FE10" s="21" t="s">
+      <c r="FE10" s="117" t="s">
         <v>178</v>
       </c>
-      <c r="FF10" s="21" t="s">
+      <c r="FF10" s="117" t="s">
         <v>179</v>
       </c>
-      <c r="FG10" s="20" t="s">
+      <c r="FG10" s="116" t="s">
         <v>180</v>
       </c>
-      <c r="FH10" s="20" t="s">
+      <c r="FH10" s="116" t="s">
         <v>181</v>
       </c>
-      <c r="FI10" s="21" t="s">
+      <c r="FI10" s="117" t="s">
         <v>182</v>
       </c>
-      <c r="FJ10" s="21" t="s">
+      <c r="FJ10" s="117" t="s">
         <v>183</v>
       </c>
-      <c r="FK10" s="21" t="s">
+      <c r="FK10" s="117" t="s">
         <v>184</v>
       </c>
-      <c r="FL10" s="21" t="s">
+      <c r="FL10" s="117" t="s">
         <v>185</v>
       </c>
-      <c r="FM10" s="21" t="s">
+      <c r="FM10" s="117" t="s">
         <v>186</v>
       </c>
-      <c r="FN10" s="21" t="s">
+      <c r="FN10" s="117" t="s">
         <v>187</v>
       </c>
-      <c r="FO10" s="21" t="s">
+      <c r="FO10" s="117" t="s">
         <v>188</v>
       </c>
-      <c r="FP10" s="21" t="s">
+      <c r="FP10" s="117" t="s">
         <v>189</v>
       </c>
-      <c r="FQ10" s="21" t="s">
+      <c r="FQ10" s="117" t="s">
         <v>190</v>
       </c>
-      <c r="FR10" s="21" t="s">
+      <c r="FR10" s="117" t="s">
         <v>191</v>
       </c>
-      <c r="FS10" s="20" t="s">
+      <c r="FS10" s="116" t="s">
         <v>192</v>
       </c>
-      <c r="FT10" s="20" t="s">
+      <c r="FT10" s="116" t="s">
         <v>193</v>
       </c>
-      <c r="FU10" s="21" t="s">
+      <c r="FU10" s="117" t="s">
         <v>194</v>
       </c>
-      <c r="FV10" s="21" t="s">
+      <c r="FV10" s="117" t="s">
         <v>195</v>
       </c>
-      <c r="FW10" s="21" t="s">
+      <c r="FW10" s="117" t="s">
         <v>196</v>
       </c>
-      <c r="FX10" s="21" t="s">
+      <c r="FX10" s="117" t="s">
         <v>197</v>
       </c>
-      <c r="FY10" s="20" t="s">
+      <c r="FY10" s="116" t="s">
         <v>198</v>
       </c>
-      <c r="FZ10" s="20" t="s">
+      <c r="FZ10" s="116" t="s">
         <v>199</v>
       </c>
-      <c r="GA10" s="21" t="s">
+      <c r="GA10" s="117" t="s">
         <v>200</v>
       </c>
-      <c r="GB10" s="21" t="s">
+      <c r="GB10" s="117" t="s">
         <v>201</v>
       </c>
-      <c r="GC10" s="21" t="s">
+      <c r="GC10" s="117" t="s">
         <v>202</v>
       </c>
-      <c r="GD10" s="21" t="s">
+      <c r="GD10" s="117" t="s">
         <v>203</v>
       </c>
-      <c r="GE10" s="20" t="s">
+      <c r="GE10" s="116" t="s">
         <v>204</v>
       </c>
-      <c r="GF10" s="20" t="s">
+      <c r="GF10" s="116" t="s">
         <v>205</v>
       </c>
-      <c r="GG10" s="21" t="s">
+      <c r="GG10" s="117" t="s">
         <v>206</v>
       </c>
-      <c r="GH10" s="21" t="s">
+      <c r="GH10" s="117" t="s">
         <v>207</v>
       </c>
-      <c r="GI10" s="21" t="s">
+      <c r="GI10" s="117" t="s">
         <v>208</v>
       </c>
-      <c r="GJ10" s="21" t="s">
+      <c r="GJ10" s="117" t="s">
         <v>209</v>
       </c>
-      <c r="GK10" s="21" t="s">
+      <c r="GK10" s="117" t="s">
         <v>210</v>
       </c>
-      <c r="GL10" s="21" t="s">
+      <c r="GL10" s="117" t="s">
         <v>211</v>
       </c>
-      <c r="GM10" s="21" t="s">
+      <c r="GM10" s="117" t="s">
         <v>212</v>
       </c>
-      <c r="GN10" s="21" t="s">
+      <c r="GN10" s="117" t="s">
         <v>213</v>
       </c>
-      <c r="GO10" s="21" t="s">
+      <c r="GO10" s="117" t="s">
         <v>214</v>
       </c>
-      <c r="GP10" s="21" t="s">
+      <c r="GP10" s="117" t="s">
         <v>215</v>
       </c>
-      <c r="GQ10" s="20" t="s">
+      <c r="GQ10" s="116" t="s">
         <v>216</v>
       </c>
-      <c r="GR10" s="20" t="s">
+      <c r="GR10" s="116" t="s">
         <v>217</v>
       </c>
-      <c r="GS10" s="21" t="s">
+      <c r="GS10" s="117" t="s">
         <v>218</v>
       </c>
-      <c r="GT10" s="21" t="s">
+      <c r="GT10" s="117" t="s">
         <v>219</v>
       </c>
-      <c r="GU10" s="21" t="s">
+      <c r="GU10" s="117" t="s">
         <v>220</v>
       </c>
-      <c r="GV10" s="21" t="s">
+      <c r="GV10" s="117" t="s">
         <v>221</v>
       </c>
-      <c r="GW10" s="20" t="s">
+      <c r="GW10" s="116" t="s">
         <v>222</v>
       </c>
-      <c r="GX10" s="20" t="s">
+      <c r="GX10" s="116" t="s">
         <v>223</v>
       </c>
-      <c r="GY10" s="21" t="s">
+      <c r="GY10" s="117" t="s">
         <v>224</v>
       </c>
-      <c r="GZ10" s="21" t="s">
+      <c r="GZ10" s="117" t="s">
         <v>225</v>
       </c>
-      <c r="HA10" s="21" t="s">
+      <c r="HA10" s="117" t="s">
         <v>226</v>
       </c>
-      <c r="HB10" s="22" t="s">
+      <c r="HB10" s="118" t="s">
         <v>227</v>
       </c>
     </row>
-    <row r="11" spans="1:210" s="23" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="34"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="35" t="s">
+    <row r="11" spans="1:210" s="19" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="119" t="s">
         <v>230</v>
       </c>
-      <c r="E11" s="25" t="s">
+      <c r="E11" s="120" t="s">
         <v>231</v>
       </c>
-      <c r="F11" s="24" t="s">
+      <c r="F11" s="119" t="s">
         <v>232</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="120" t="s">
         <v>233</v>
       </c>
-      <c r="H11" s="24" t="s">
+      <c r="H11" s="119" t="s">
         <v>234</v>
       </c>
-      <c r="I11" s="24" t="s">
+      <c r="I11" s="119" t="s">
         <v>235</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="119" t="s">
         <v>236</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="119" t="s">
         <v>237</v>
       </c>
-      <c r="L11" s="24" t="s">
+      <c r="L11" s="119" t="s">
         <v>238</v>
       </c>
-      <c r="M11" s="26" t="s">
+      <c r="M11" s="121" t="s">
         <v>239</v>
       </c>
-      <c r="N11" s="26" t="s">
+      <c r="N11" s="121" t="s">
         <v>240</v>
       </c>
-      <c r="O11" s="24" t="s">
+      <c r="O11" s="119" t="s">
         <v>241</v>
       </c>
-      <c r="P11" s="26" t="s">
+      <c r="P11" s="121" t="s">
         <v>242</v>
       </c>
-      <c r="Q11" s="26" t="s">
+      <c r="Q11" s="121" t="s">
         <v>243</v>
       </c>
-      <c r="R11" s="24" t="s">
+      <c r="R11" s="119" t="s">
         <v>244</v>
       </c>
-      <c r="S11" s="26" t="s">
+      <c r="S11" s="121" t="s">
         <v>245</v>
       </c>
-      <c r="T11" s="26" t="s">
+      <c r="T11" s="121" t="s">
         <v>246</v>
       </c>
-      <c r="U11" s="24" t="s">
+      <c r="U11" s="119" t="s">
         <v>247</v>
       </c>
-      <c r="V11" s="26" t="s">
+      <c r="V11" s="121" t="s">
         <v>248</v>
       </c>
-      <c r="W11" s="26" t="s">
+      <c r="W11" s="121" t="s">
         <v>249</v>
       </c>
-      <c r="X11" s="24" t="s">
+      <c r="X11" s="119" t="s">
         <v>250</v>
       </c>
-      <c r="Y11" s="26" t="s">
+      <c r="Y11" s="121" t="s">
         <v>251</v>
       </c>
-      <c r="Z11" s="26" t="s">
+      <c r="Z11" s="121" t="s">
         <v>252</v>
       </c>
-      <c r="AA11" s="24" t="s">
+      <c r="AA11" s="119" t="s">
         <v>253</v>
       </c>
-      <c r="AB11" s="26" t="s">
+      <c r="AB11" s="121" t="s">
         <v>254</v>
       </c>
-      <c r="AC11" s="26" t="s">
+      <c r="AC11" s="121" t="s">
         <v>255</v>
       </c>
-      <c r="AD11" s="24" t="s">
+      <c r="AD11" s="119" t="s">
         <v>256</v>
       </c>
-      <c r="AE11" s="26" t="s">
+      <c r="AE11" s="121" t="s">
         <v>257</v>
       </c>
-      <c r="AF11" s="26" t="s">
+      <c r="AF11" s="121" t="s">
         <v>258</v>
       </c>
-      <c r="AG11" s="24" t="s">
+      <c r="AG11" s="119" t="s">
         <v>259</v>
       </c>
-      <c r="AH11" s="26" t="s">
+      <c r="AH11" s="121" t="s">
         <v>260</v>
       </c>
-      <c r="AI11" s="26" t="s">
+      <c r="AI11" s="121" t="s">
         <v>261</v>
       </c>
-      <c r="AJ11" s="24" t="s">
+      <c r="AJ11" s="119" t="s">
         <v>262</v>
       </c>
-      <c r="AK11" s="26" t="s">
+      <c r="AK11" s="121" t="s">
         <v>263</v>
       </c>
-      <c r="AL11" s="26" t="s">
+      <c r="AL11" s="121" t="s">
         <v>264</v>
       </c>
-      <c r="AM11" s="24" t="s">
+      <c r="AM11" s="119" t="s">
         <v>265</v>
       </c>
-      <c r="AN11" s="26" t="s">
+      <c r="AN11" s="121" t="s">
         <v>266</v>
       </c>
-      <c r="AO11" s="26" t="s">
+      <c r="AO11" s="121" t="s">
         <v>267</v>
       </c>
-      <c r="AP11" s="24" t="s">
+      <c r="AP11" s="119" t="s">
         <v>268</v>
       </c>
-      <c r="AQ11" s="26" t="s">
+      <c r="AQ11" s="121" t="s">
         <v>269</v>
       </c>
-      <c r="AR11" s="26" t="s">
+      <c r="AR11" s="121" t="s">
         <v>270</v>
       </c>
-      <c r="AS11" s="24" t="s">
+      <c r="AS11" s="119" t="s">
         <v>271</v>
       </c>
-      <c r="AT11" s="24" t="s">
+      <c r="AT11" s="119" t="s">
         <v>272</v>
       </c>
-      <c r="AU11" s="24" t="s">
+      <c r="AU11" s="119" t="s">
         <v>273</v>
       </c>
-      <c r="AV11" s="27" t="s">
+      <c r="AV11" s="122" t="s">
         <v>274</v>
       </c>
-      <c r="AW11" s="28" t="s">
+      <c r="AW11" s="123" t="s">
         <v>275</v>
       </c>
-      <c r="AX11" s="26" t="s">
+      <c r="AX11" s="121" t="s">
         <v>276</v>
       </c>
-      <c r="AY11" s="24" t="s">
+      <c r="AY11" s="119" t="s">
         <v>277</v>
       </c>
-      <c r="AZ11" s="26" t="s">
+      <c r="AZ11" s="121" t="s">
         <v>278</v>
       </c>
-      <c r="BA11" s="26" t="s">
+      <c r="BA11" s="121" t="s">
         <v>279</v>
       </c>
-      <c r="BB11" s="24" t="s">
+      <c r="BB11" s="119" t="s">
         <v>280</v>
       </c>
-      <c r="BC11" s="26" t="s">
+      <c r="BC11" s="121" t="s">
         <v>281</v>
       </c>
-      <c r="BD11" s="26" t="s">
+      <c r="BD11" s="121" t="s">
         <v>282</v>
       </c>
-      <c r="BE11" s="24" t="s">
+      <c r="BE11" s="119" t="s">
         <v>283</v>
       </c>
-      <c r="BF11" s="26" t="s">
+      <c r="BF11" s="121" t="s">
         <v>284</v>
       </c>
-      <c r="BG11" s="26" t="s">
+      <c r="BG11" s="121" t="s">
         <v>285</v>
       </c>
-      <c r="BH11" s="24" t="s">
+      <c r="BH11" s="119" t="s">
         <v>286</v>
       </c>
-      <c r="BI11" s="26" t="s">
+      <c r="BI11" s="121" t="s">
         <v>287</v>
       </c>
-      <c r="BJ11" s="26" t="s">
+      <c r="BJ11" s="121" t="s">
         <v>288</v>
       </c>
-      <c r="BK11" s="24" t="s">
+      <c r="BK11" s="119" t="s">
         <v>289</v>
       </c>
-      <c r="BL11" s="26" t="s">
+      <c r="BL11" s="121" t="s">
         <v>290</v>
       </c>
-      <c r="BM11" s="26" t="s">
+      <c r="BM11" s="121" t="s">
         <v>291</v>
       </c>
-      <c r="BN11" s="24" t="s">
+      <c r="BN11" s="119" t="s">
         <v>292</v>
       </c>
-      <c r="BO11" s="26" t="s">
+      <c r="BO11" s="121" t="s">
         <v>293</v>
       </c>
-      <c r="BP11" s="26" t="s">
+      <c r="BP11" s="121" t="s">
         <v>294</v>
       </c>
-      <c r="BQ11" s="24" t="s">
+      <c r="BQ11" s="119" t="s">
         <v>295</v>
       </c>
-      <c r="BR11" s="26" t="s">
+      <c r="BR11" s="121" t="s">
         <v>296</v>
       </c>
-      <c r="BS11" s="26" t="s">
+      <c r="BS11" s="121" t="s">
         <v>297</v>
       </c>
-      <c r="BT11" s="24" t="s">
+      <c r="BT11" s="119" t="s">
         <v>298</v>
       </c>
-      <c r="BU11" s="26" t="s">
+      <c r="BU11" s="121" t="s">
         <v>299</v>
       </c>
-      <c r="BV11" s="26" t="s">
+      <c r="BV11" s="121" t="s">
         <v>300</v>
       </c>
-      <c r="BW11" s="24" t="s">
+      <c r="BW11" s="119" t="s">
         <v>301</v>
       </c>
-      <c r="BX11" s="26" t="s">
+      <c r="BX11" s="121" t="s">
         <v>302</v>
       </c>
-      <c r="BY11" s="26" t="s">
+      <c r="BY11" s="121" t="s">
         <v>303</v>
       </c>
-      <c r="BZ11" s="24" t="s">
+      <c r="BZ11" s="119" t="s">
         <v>304</v>
       </c>
-      <c r="CA11" s="26" t="s">
+      <c r="CA11" s="121" t="s">
         <v>305</v>
       </c>
-      <c r="CB11" s="26" t="s">
+      <c r="CB11" s="121" t="s">
         <v>306</v>
       </c>
-      <c r="CC11" s="24" t="s">
+      <c r="CC11" s="119" t="s">
         <v>307</v>
       </c>
-      <c r="CD11" s="24" t="s">
+      <c r="CD11" s="119" t="s">
         <v>308</v>
       </c>
-      <c r="CE11" s="24" t="s">
+      <c r="CE11" s="119" t="s">
         <v>309</v>
       </c>
-      <c r="CF11" s="27" t="s">
+      <c r="CF11" s="122" t="s">
         <v>310</v>
       </c>
-      <c r="CG11" s="28" t="s">
+      <c r="CG11" s="123" t="s">
         <v>311</v>
       </c>
-      <c r="CH11" s="26" t="s">
+      <c r="CH11" s="121" t="s">
         <v>312</v>
       </c>
-      <c r="CI11" s="24" t="s">
+      <c r="CI11" s="119" t="s">
         <v>313</v>
       </c>
-      <c r="CJ11" s="26" t="s">
+      <c r="CJ11" s="121" t="s">
         <v>314</v>
       </c>
-      <c r="CK11" s="26" t="s">
+      <c r="CK11" s="121" t="s">
         <v>315</v>
       </c>
-      <c r="CL11" s="24" t="s">
+      <c r="CL11" s="119" t="s">
         <v>316</v>
       </c>
-      <c r="CM11" s="26" t="s">
+      <c r="CM11" s="121" t="s">
         <v>317</v>
       </c>
-      <c r="CN11" s="26" t="s">
+      <c r="CN11" s="121" t="s">
         <v>318</v>
       </c>
-      <c r="CO11" s="24" t="s">
+      <c r="CO11" s="119" t="s">
         <v>319</v>
       </c>
-      <c r="CP11" s="26" t="s">
+      <c r="CP11" s="121" t="s">
         <v>320</v>
       </c>
-      <c r="CQ11" s="26" t="s">
+      <c r="CQ11" s="121" t="s">
         <v>321</v>
       </c>
-      <c r="CR11" s="24" t="s">
+      <c r="CR11" s="119" t="s">
         <v>322</v>
       </c>
-      <c r="CS11" s="26" t="s">
+      <c r="CS11" s="121" t="s">
         <v>323</v>
       </c>
-      <c r="CT11" s="26" t="s">
+      <c r="CT11" s="121" t="s">
         <v>324</v>
       </c>
-      <c r="CU11" s="24" t="s">
+      <c r="CU11" s="119" t="s">
         <v>325</v>
       </c>
-      <c r="CV11" s="26" t="s">
+      <c r="CV11" s="121" t="s">
         <v>326</v>
       </c>
-      <c r="CW11" s="26" t="s">
+      <c r="CW11" s="121" t="s">
         <v>327</v>
       </c>
-      <c r="CX11" s="24" t="s">
+      <c r="CX11" s="119" t="s">
         <v>328</v>
       </c>
-      <c r="CY11" s="26" t="s">
+      <c r="CY11" s="121" t="s">
         <v>329</v>
       </c>
-      <c r="CZ11" s="26" t="s">
+      <c r="CZ11" s="121" t="s">
         <v>330</v>
       </c>
-      <c r="DA11" s="24" t="s">
+      <c r="DA11" s="119" t="s">
         <v>331</v>
       </c>
-      <c r="DB11" s="26" t="s">
+      <c r="DB11" s="121" t="s">
         <v>332</v>
       </c>
-      <c r="DC11" s="26" t="s">
+      <c r="DC11" s="121" t="s">
         <v>333</v>
       </c>
-      <c r="DD11" s="24" t="s">
+      <c r="DD11" s="119" t="s">
         <v>334</v>
       </c>
-      <c r="DE11" s="26" t="s">
+      <c r="DE11" s="121" t="s">
         <v>335</v>
       </c>
-      <c r="DF11" s="26" t="s">
+      <c r="DF11" s="121" t="s">
         <v>336</v>
       </c>
-      <c r="DG11" s="24" t="s">
+      <c r="DG11" s="119" t="s">
         <v>337</v>
       </c>
-      <c r="DH11" s="26" t="s">
+      <c r="DH11" s="121" t="s">
         <v>338</v>
       </c>
-      <c r="DI11" s="26" t="s">
+      <c r="DI11" s="121" t="s">
         <v>339</v>
       </c>
-      <c r="DJ11" s="24" t="s">
+      <c r="DJ11" s="119" t="s">
         <v>340</v>
       </c>
-      <c r="DK11" s="26" t="s">
+      <c r="DK11" s="121" t="s">
         <v>341</v>
       </c>
-      <c r="DL11" s="26" t="s">
+      <c r="DL11" s="121" t="s">
         <v>342</v>
       </c>
-      <c r="DM11" s="24" t="s">
+      <c r="DM11" s="119" t="s">
         <v>343</v>
       </c>
-      <c r="DN11" s="24" t="s">
+      <c r="DN11" s="119" t="s">
         <v>344</v>
       </c>
-      <c r="DO11" s="24" t="s">
+      <c r="DO11" s="119" t="s">
         <v>345</v>
       </c>
-      <c r="DP11" s="24" t="s">
+      <c r="DP11" s="119" t="s">
         <v>346</v>
       </c>
-      <c r="DQ11" s="29" t="s">
+      <c r="DQ11" s="124" t="s">
         <v>347</v>
       </c>
-      <c r="DR11" s="24" t="s">
+      <c r="DR11" s="119" t="s">
         <v>348</v>
       </c>
-      <c r="DS11" s="24" t="s">
+      <c r="DS11" s="119" t="s">
         <v>349</v>
       </c>
-      <c r="DT11" s="24" t="s">
+      <c r="DT11" s="119" t="s">
         <v>350</v>
       </c>
-      <c r="DU11" s="24" t="s">
+      <c r="DU11" s="119" t="s">
         <v>351</v>
       </c>
-      <c r="DV11" s="24" t="s">
+      <c r="DV11" s="119" t="s">
         <v>352</v>
       </c>
-      <c r="DW11" s="26" t="s">
+      <c r="DW11" s="121" t="s">
         <v>353</v>
       </c>
-      <c r="DX11" s="26" t="s">
+      <c r="DX11" s="121" t="s">
         <v>354</v>
       </c>
-      <c r="DY11" s="24" t="s">
+      <c r="DY11" s="119" t="s">
         <v>355</v>
       </c>
-      <c r="DZ11" s="24" t="s">
+      <c r="DZ11" s="119" t="s">
         <v>356</v>
       </c>
-      <c r="EA11" s="24" t="s">
+      <c r="EA11" s="119" t="s">
         <v>357</v>
       </c>
-      <c r="EB11" s="24" t="s">
+      <c r="EB11" s="119" t="s">
         <v>358</v>
       </c>
-      <c r="EC11" s="26" t="s">
+      <c r="EC11" s="121" t="s">
         <v>359</v>
       </c>
-      <c r="ED11" s="26" t="s">
+      <c r="ED11" s="121" t="s">
         <v>360</v>
       </c>
-      <c r="EE11" s="24" t="s">
+      <c r="EE11" s="119" t="s">
         <v>361</v>
       </c>
-      <c r="EF11" s="24" t="s">
+      <c r="EF11" s="119" t="s">
         <v>362</v>
       </c>
-      <c r="EG11" s="24" t="s">
+      <c r="EG11" s="119" t="s">
         <v>363</v>
       </c>
-      <c r="EH11" s="24" t="s">
+      <c r="EH11" s="119" t="s">
         <v>364</v>
       </c>
-      <c r="EI11" s="24" t="s">
+      <c r="EI11" s="119" t="s">
         <v>365</v>
       </c>
-      <c r="EJ11" s="24" t="s">
+      <c r="EJ11" s="119" t="s">
         <v>366</v>
       </c>
-      <c r="EK11" s="24" t="s">
+      <c r="EK11" s="119" t="s">
         <v>367</v>
       </c>
-      <c r="EL11" s="24" t="s">
+      <c r="EL11" s="119" t="s">
         <v>368</v>
       </c>
-      <c r="EM11" s="24" t="s">
+      <c r="EM11" s="119" t="s">
         <v>369</v>
       </c>
-      <c r="EN11" s="24" t="s">
+      <c r="EN11" s="119" t="s">
         <v>370</v>
       </c>
-      <c r="EO11" s="26" t="s">
+      <c r="EO11" s="121" t="s">
         <v>371</v>
       </c>
-      <c r="EP11" s="26" t="s">
+      <c r="EP11" s="121" t="s">
         <v>372</v>
       </c>
-      <c r="EQ11" s="24" t="s">
+      <c r="EQ11" s="119" t="s">
         <v>373</v>
       </c>
-      <c r="ER11" s="24" t="s">
+      <c r="ER11" s="119" t="s">
         <v>374</v>
       </c>
-      <c r="ES11" s="24" t="s">
+      <c r="ES11" s="119" t="s">
         <v>375</v>
       </c>
-      <c r="ET11" s="24" t="s">
+      <c r="ET11" s="119" t="s">
         <v>376</v>
       </c>
-      <c r="EU11" s="26" t="s">
+      <c r="EU11" s="121" t="s">
         <v>377</v>
       </c>
-      <c r="EV11" s="26" t="s">
+      <c r="EV11" s="121" t="s">
         <v>378</v>
       </c>
-      <c r="EW11" s="24" t="s">
+      <c r="EW11" s="119" t="s">
         <v>379</v>
       </c>
-      <c r="EX11" s="24" t="s">
+      <c r="EX11" s="119" t="s">
         <v>380</v>
       </c>
-      <c r="EY11" s="24" t="s">
+      <c r="EY11" s="119" t="s">
         <v>381</v>
       </c>
-      <c r="EZ11" s="24" t="s">
+      <c r="EZ11" s="119" t="s">
         <v>382</v>
       </c>
-      <c r="FA11" s="26" t="s">
+      <c r="FA11" s="121" t="s">
         <v>383</v>
       </c>
-      <c r="FB11" s="26" t="s">
+      <c r="FB11" s="121" t="s">
         <v>384</v>
       </c>
-      <c r="FC11" s="24" t="s">
+      <c r="FC11" s="119" t="s">
         <v>385</v>
       </c>
-      <c r="FD11" s="24" t="s">
+      <c r="FD11" s="119" t="s">
         <v>386</v>
       </c>
-      <c r="FE11" s="24" t="s">
+      <c r="FE11" s="119" t="s">
         <v>387</v>
       </c>
-      <c r="FF11" s="24" t="s">
+      <c r="FF11" s="119" t="s">
         <v>388</v>
       </c>
-      <c r="FG11" s="26" t="s">
+      <c r="FG11" s="121" t="s">
         <v>389</v>
       </c>
-      <c r="FH11" s="26" t="s">
+      <c r="FH11" s="121" t="s">
         <v>390</v>
       </c>
-      <c r="FI11" s="24" t="s">
+      <c r="FI11" s="119" t="s">
         <v>391</v>
       </c>
-      <c r="FJ11" s="24" t="s">
+      <c r="FJ11" s="119" t="s">
         <v>392</v>
       </c>
-      <c r="FK11" s="24" t="s">
+      <c r="FK11" s="119" t="s">
         <v>393</v>
       </c>
-      <c r="FL11" s="24" t="s">
+      <c r="FL11" s="119" t="s">
         <v>394</v>
       </c>
-      <c r="FM11" s="24" t="s">
+      <c r="FM11" s="119" t="s">
         <v>395</v>
       </c>
-      <c r="FN11" s="24" t="s">
+      <c r="FN11" s="119" t="s">
         <v>396</v>
       </c>
-      <c r="FO11" s="24" t="s">
+      <c r="FO11" s="119" t="s">
         <v>397</v>
       </c>
-      <c r="FP11" s="24" t="s">
+      <c r="FP11" s="119" t="s">
         <v>398</v>
       </c>
-      <c r="FQ11" s="24" t="s">
+      <c r="FQ11" s="119" t="s">
         <v>399</v>
       </c>
-      <c r="FR11" s="24" t="s">
+      <c r="FR11" s="119" t="s">
         <v>400</v>
       </c>
-      <c r="FS11" s="26" t="s">
+      <c r="FS11" s="121" t="s">
         <v>401</v>
       </c>
-      <c r="FT11" s="26" t="s">
+      <c r="FT11" s="121" t="s">
         <v>402</v>
       </c>
-      <c r="FU11" s="24" t="s">
+      <c r="FU11" s="119" t="s">
         <v>403</v>
       </c>
-      <c r="FV11" s="24" t="s">
+      <c r="FV11" s="119" t="s">
         <v>404</v>
       </c>
-      <c r="FW11" s="24" t="s">
+      <c r="FW11" s="119" t="s">
         <v>405</v>
       </c>
-      <c r="FX11" s="24" t="s">
+      <c r="FX11" s="119" t="s">
         <v>406</v>
       </c>
-      <c r="FY11" s="26" t="s">
+      <c r="FY11" s="121" t="s">
         <v>407</v>
       </c>
-      <c r="FZ11" s="26" t="s">
+      <c r="FZ11" s="121" t="s">
         <v>408</v>
       </c>
-      <c r="GA11" s="24" t="s">
+      <c r="GA11" s="119" t="s">
         <v>409</v>
       </c>
-      <c r="GB11" s="24" t="s">
+      <c r="GB11" s="119" t="s">
         <v>410</v>
       </c>
-      <c r="GC11" s="24" t="s">
+      <c r="GC11" s="119" t="s">
         <v>411</v>
       </c>
-      <c r="GD11" s="24" t="s">
+      <c r="GD11" s="119" t="s">
         <v>412</v>
       </c>
-      <c r="GE11" s="26" t="s">
+      <c r="GE11" s="121" t="s">
         <v>413</v>
       </c>
-      <c r="GF11" s="26" t="s">
+      <c r="GF11" s="121" t="s">
         <v>414</v>
       </c>
-      <c r="GG11" s="24" t="s">
+      <c r="GG11" s="119" t="s">
         <v>415</v>
       </c>
-      <c r="GH11" s="24" t="s">
+      <c r="GH11" s="119" t="s">
         <v>416</v>
       </c>
-      <c r="GI11" s="24" t="s">
+      <c r="GI11" s="119" t="s">
         <v>417</v>
       </c>
-      <c r="GJ11" s="30" t="s">
+      <c r="GJ11" s="125" t="s">
         <v>418</v>
       </c>
-      <c r="GK11" s="31" t="s">
+      <c r="GK11" s="126" t="s">
         <v>419</v>
       </c>
-      <c r="GL11" s="24" t="s">
+      <c r="GL11" s="119" t="s">
         <v>420</v>
       </c>
-      <c r="GM11" s="24" t="s">
+      <c r="GM11" s="119" t="s">
         <v>421</v>
       </c>
-      <c r="GN11" s="24" t="s">
+      <c r="GN11" s="119" t="s">
         <v>422</v>
       </c>
-      <c r="GO11" s="24" t="s">
+      <c r="GO11" s="119" t="s">
         <v>423</v>
       </c>
-      <c r="GP11" s="24" t="s">
+      <c r="GP11" s="119" t="s">
         <v>424</v>
       </c>
-      <c r="GQ11" s="26" t="s">
+      <c r="GQ11" s="121" t="s">
         <v>425</v>
       </c>
-      <c r="GR11" s="26" t="s">
+      <c r="GR11" s="121" t="s">
         <v>426</v>
       </c>
-      <c r="GS11" s="24" t="s">
+      <c r="GS11" s="119" t="s">
         <v>427</v>
       </c>
-      <c r="GT11" s="24" t="s">
+      <c r="GT11" s="119" t="s">
         <v>428</v>
       </c>
-      <c r="GU11" s="24" t="s">
+      <c r="GU11" s="119" t="s">
         <v>429</v>
       </c>
-      <c r="GV11" s="30" t="s">
+      <c r="GV11" s="125" t="s">
         <v>430</v>
       </c>
-      <c r="GW11" s="26" t="s">
+      <c r="GW11" s="121" t="s">
         <v>431</v>
       </c>
-      <c r="GX11" s="26" t="s">
+      <c r="GX11" s="121" t="s">
         <v>432</v>
       </c>
-      <c r="GY11" s="24" t="s">
+      <c r="GY11" s="119" t="s">
         <v>433</v>
       </c>
-      <c r="GZ11" s="24" t="s">
+      <c r="GZ11" s="119" t="s">
         <v>434</v>
       </c>
-      <c r="HA11" s="24" t="s">
+      <c r="HA11" s="119" t="s">
         <v>435</v>
       </c>
-      <c r="HB11" s="24" t="s">
+      <c r="HB11" s="119" t="s">
         <v>436</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="282">
-    <mergeCell ref="FZ8:FZ9"/>
-    <mergeCell ref="GA8:GA9"/>
-    <mergeCell ref="GB8:GD8"/>
-    <mergeCell ref="GE8:GE9"/>
-    <mergeCell ref="GF8:GF9"/>
-    <mergeCell ref="GG8:GG9"/>
-    <mergeCell ref="FP8:FR8"/>
-    <mergeCell ref="FS8:FS9"/>
-    <mergeCell ref="FT8:FT9"/>
-    <mergeCell ref="FU8:FU9"/>
-    <mergeCell ref="FV8:FX8"/>
-    <mergeCell ref="FY8:FY9"/>
-    <mergeCell ref="GT8:GV8"/>
-    <mergeCell ref="GW8:GW9"/>
-    <mergeCell ref="GX8:GX9"/>
-    <mergeCell ref="GY8:GY9"/>
-    <mergeCell ref="GZ8:HB8"/>
-    <mergeCell ref="GH8:GJ8"/>
-    <mergeCell ref="GM8:GM9"/>
-    <mergeCell ref="GN8:GP8"/>
-    <mergeCell ref="GQ8:GQ9"/>
-    <mergeCell ref="GR8:GR9"/>
-    <mergeCell ref="GS8:GS9"/>
-    <mergeCell ref="FD8:FF8"/>
-    <mergeCell ref="FG8:FG9"/>
-    <mergeCell ref="FH8:FH9"/>
-    <mergeCell ref="FI8:FI9"/>
-    <mergeCell ref="FJ8:FL8"/>
-    <mergeCell ref="FO8:FO9"/>
-    <mergeCell ref="EV8:EV9"/>
-    <mergeCell ref="EW8:EW9"/>
-    <mergeCell ref="EX8:EZ8"/>
-    <mergeCell ref="FA8:FA9"/>
-    <mergeCell ref="FB8:FB9"/>
-    <mergeCell ref="FC8:FC9"/>
-    <mergeCell ref="DK7:DK9"/>
-    <mergeCell ref="DL7:DL9"/>
-    <mergeCell ref="EL8:EN8"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EP8:EP9"/>
-    <mergeCell ref="EQ8:EQ9"/>
-    <mergeCell ref="ER8:ET8"/>
-    <mergeCell ref="EU8:EU9"/>
-    <mergeCell ref="DZ8:EB8"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="EF8:EH8"/>
-    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="AW3:CF3"/>
+    <mergeCell ref="CG3:DP3"/>
+    <mergeCell ref="DQ3:FL3"/>
+    <mergeCell ref="FM3:GJ3"/>
+    <mergeCell ref="GK3:HB3"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="D3:D9"/>
+    <mergeCell ref="F3:F9"/>
+    <mergeCell ref="H3:L5"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="AT4:AV6"/>
+    <mergeCell ref="AW4:BB5"/>
+    <mergeCell ref="BC4:BH5"/>
+    <mergeCell ref="BI4:BK6"/>
+    <mergeCell ref="BL4:BN6"/>
+    <mergeCell ref="BO4:BW4"/>
+    <mergeCell ref="AZ6:BB6"/>
+    <mergeCell ref="BC6:BE6"/>
+    <mergeCell ref="BF6:BH6"/>
+    <mergeCell ref="BO6:BQ6"/>
+    <mergeCell ref="CY4:DG4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="Y4:AA6"/>
+    <mergeCell ref="AB4:AD6"/>
+    <mergeCell ref="AE4:AM4"/>
+    <mergeCell ref="AN4:AS5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="S6:U6"/>
+    <mergeCell ref="V6:X6"/>
+    <mergeCell ref="AE6:AG6"/>
+    <mergeCell ref="AH6:AJ6"/>
+    <mergeCell ref="AK6:AM6"/>
+    <mergeCell ref="AN6:AP6"/>
+    <mergeCell ref="AQ6:AS6"/>
+    <mergeCell ref="M3:AR3"/>
+    <mergeCell ref="DH4:DM5"/>
+    <mergeCell ref="DN4:DP6"/>
+    <mergeCell ref="DQ4:EH4"/>
+    <mergeCell ref="EI4:EZ4"/>
+    <mergeCell ref="FA4:FF5"/>
+    <mergeCell ref="EK5:EN7"/>
+    <mergeCell ref="EO5:EZ5"/>
+    <mergeCell ref="CY6:DA6"/>
+    <mergeCell ref="DB6:DD6"/>
+    <mergeCell ref="DW6:EB6"/>
+    <mergeCell ref="EC6:EH6"/>
+    <mergeCell ref="EO6:ET6"/>
+    <mergeCell ref="DA7:DA9"/>
+    <mergeCell ref="DB7:DB9"/>
+    <mergeCell ref="DC7:DC9"/>
+    <mergeCell ref="DD7:DD9"/>
+    <mergeCell ref="DM7:DM9"/>
+    <mergeCell ref="DN7:DN9"/>
+    <mergeCell ref="DO7:DO9"/>
+    <mergeCell ref="DP7:DP9"/>
+    <mergeCell ref="DE7:DE9"/>
+    <mergeCell ref="DF7:DF9"/>
+    <mergeCell ref="DG7:DG9"/>
+    <mergeCell ref="DH7:DH9"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="GW4:HB6"/>
+    <mergeCell ref="AE5:AM5"/>
+    <mergeCell ref="BO5:BW5"/>
+    <mergeCell ref="CY5:DG5"/>
+    <mergeCell ref="DQ5:DQ9"/>
+    <mergeCell ref="DR5:DR9"/>
+    <mergeCell ref="DS5:DV7"/>
+    <mergeCell ref="DW5:EH5"/>
+    <mergeCell ref="EI5:EI9"/>
+    <mergeCell ref="EJ5:EJ9"/>
+    <mergeCell ref="FG4:FL5"/>
+    <mergeCell ref="FM4:GJ4"/>
+    <mergeCell ref="GK4:GK9"/>
+    <mergeCell ref="GL4:GL9"/>
+    <mergeCell ref="GM4:GP7"/>
+    <mergeCell ref="GQ4:GV6"/>
+    <mergeCell ref="FM5:FM9"/>
+    <mergeCell ref="FN5:FN9"/>
+    <mergeCell ref="FS7:FT7"/>
+    <mergeCell ref="FU7:FX7"/>
+    <mergeCell ref="DE6:DG6"/>
+    <mergeCell ref="DH6:DJ6"/>
+    <mergeCell ref="DK6:DM6"/>
+    <mergeCell ref="BR6:BT6"/>
+    <mergeCell ref="BU6:BW6"/>
+    <mergeCell ref="BX6:BZ6"/>
+    <mergeCell ref="CA6:CC6"/>
+    <mergeCell ref="CG6:CI6"/>
+    <mergeCell ref="CJ6:CL6"/>
+    <mergeCell ref="FO5:FR7"/>
+    <mergeCell ref="FS5:GJ5"/>
+    <mergeCell ref="BX4:CC5"/>
+    <mergeCell ref="CD4:CF6"/>
+    <mergeCell ref="CG4:CL5"/>
+    <mergeCell ref="CM4:CR5"/>
+    <mergeCell ref="CS4:CU6"/>
+    <mergeCell ref="CV4:CX6"/>
+    <mergeCell ref="CM6:CO6"/>
+    <mergeCell ref="CP6:CR6"/>
+    <mergeCell ref="CA7:CA9"/>
+    <mergeCell ref="CB7:CB9"/>
+    <mergeCell ref="CC7:CC9"/>
+    <mergeCell ref="CD7:CD9"/>
+    <mergeCell ref="CE7:CE9"/>
+    <mergeCell ref="CF7:CF9"/>
+    <mergeCell ref="BU7:BU9"/>
+    <mergeCell ref="BV7:BV9"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="FY6:GD6"/>
+    <mergeCell ref="GE6:GJ6"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:Q9"/>
+    <mergeCell ref="R7:R9"/>
+    <mergeCell ref="EU6:EZ6"/>
+    <mergeCell ref="FA6:FB7"/>
+    <mergeCell ref="FC6:FF7"/>
+    <mergeCell ref="FG6:FH7"/>
+    <mergeCell ref="FI6:FL7"/>
+    <mergeCell ref="FS6:FX6"/>
+    <mergeCell ref="EU7:EV7"/>
+    <mergeCell ref="EW7:EZ7"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AQ7:AQ9"/>
+    <mergeCell ref="AR7:AR9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AT7:AT9"/>
+    <mergeCell ref="AU7:AU9"/>
+    <mergeCell ref="AV7:AV9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AP7:AP9"/>
+    <mergeCell ref="BC7:BC9"/>
+    <mergeCell ref="BD7:BD9"/>
+    <mergeCell ref="BE7:BE9"/>
+    <mergeCell ref="BF7:BF9"/>
+    <mergeCell ref="BG7:BG9"/>
+    <mergeCell ref="BH7:BH9"/>
+    <mergeCell ref="AW7:AW9"/>
+    <mergeCell ref="AX7:AX9"/>
+    <mergeCell ref="AY7:AY9"/>
+    <mergeCell ref="AZ7:AZ9"/>
+    <mergeCell ref="BA7:BA9"/>
+    <mergeCell ref="BB7:BB9"/>
+    <mergeCell ref="BO7:BO9"/>
+    <mergeCell ref="BP7:BP9"/>
+    <mergeCell ref="BQ7:BQ9"/>
+    <mergeCell ref="BR7:BR9"/>
+    <mergeCell ref="BS7:BS9"/>
+    <mergeCell ref="BT7:BT9"/>
+    <mergeCell ref="BI7:BI9"/>
+    <mergeCell ref="BJ7:BJ9"/>
+    <mergeCell ref="BK7:BK9"/>
+    <mergeCell ref="BL7:BL9"/>
+    <mergeCell ref="BM7:BM9"/>
+    <mergeCell ref="BN7:BN9"/>
+    <mergeCell ref="BW7:BW9"/>
+    <mergeCell ref="BX7:BX9"/>
+    <mergeCell ref="BY7:BY9"/>
+    <mergeCell ref="BZ7:BZ9"/>
+    <mergeCell ref="CM7:CM9"/>
+    <mergeCell ref="CN7:CN9"/>
+    <mergeCell ref="CO7:CO9"/>
+    <mergeCell ref="CP7:CP9"/>
+    <mergeCell ref="CQ7:CQ9"/>
+    <mergeCell ref="CR7:CR9"/>
+    <mergeCell ref="CG7:CG9"/>
+    <mergeCell ref="CH7:CH9"/>
+    <mergeCell ref="CI7:CI9"/>
+    <mergeCell ref="CJ7:CJ9"/>
+    <mergeCell ref="CK7:CK9"/>
+    <mergeCell ref="CL7:CL9"/>
+    <mergeCell ref="CY7:CY9"/>
+    <mergeCell ref="CZ7:CZ9"/>
+    <mergeCell ref="CS7:CS9"/>
+    <mergeCell ref="CT7:CT9"/>
+    <mergeCell ref="CU7:CU9"/>
+    <mergeCell ref="CV7:CV9"/>
+    <mergeCell ref="CW7:CW9"/>
+    <mergeCell ref="CX7:CX9"/>
     <mergeCell ref="DI7:DI9"/>
     <mergeCell ref="DJ7:DJ9"/>
     <mergeCell ref="GW7:GX7"/>
@@ -6726,215 +6887,55 @@
     <mergeCell ref="EE7:EH7"/>
     <mergeCell ref="EO7:EP7"/>
     <mergeCell ref="EQ7:ET7"/>
-    <mergeCell ref="CR7:CR9"/>
-    <mergeCell ref="CG7:CG9"/>
-    <mergeCell ref="CH7:CH9"/>
-    <mergeCell ref="CI7:CI9"/>
-    <mergeCell ref="CJ7:CJ9"/>
-    <mergeCell ref="CK7:CK9"/>
-    <mergeCell ref="CL7:CL9"/>
-    <mergeCell ref="CY7:CY9"/>
-    <mergeCell ref="CZ7:CZ9"/>
-    <mergeCell ref="CS7:CS9"/>
-    <mergeCell ref="CT7:CT9"/>
-    <mergeCell ref="CU7:CU9"/>
-    <mergeCell ref="CV7:CV9"/>
-    <mergeCell ref="CW7:CW9"/>
-    <mergeCell ref="CX7:CX9"/>
-    <mergeCell ref="BW7:BW9"/>
-    <mergeCell ref="BX7:BX9"/>
-    <mergeCell ref="BY7:BY9"/>
-    <mergeCell ref="BZ7:BZ9"/>
-    <mergeCell ref="CM7:CM9"/>
-    <mergeCell ref="CN7:CN9"/>
-    <mergeCell ref="CO7:CO9"/>
-    <mergeCell ref="CP7:CP9"/>
-    <mergeCell ref="CQ7:CQ9"/>
-    <mergeCell ref="BO7:BO9"/>
-    <mergeCell ref="BP7:BP9"/>
-    <mergeCell ref="BQ7:BQ9"/>
-    <mergeCell ref="BR7:BR9"/>
-    <mergeCell ref="BS7:BS9"/>
-    <mergeCell ref="BT7:BT9"/>
-    <mergeCell ref="BI7:BI9"/>
-    <mergeCell ref="BJ7:BJ9"/>
-    <mergeCell ref="BK7:BK9"/>
-    <mergeCell ref="BL7:BL9"/>
-    <mergeCell ref="BM7:BM9"/>
-    <mergeCell ref="BN7:BN9"/>
-    <mergeCell ref="BC7:BC9"/>
-    <mergeCell ref="BD7:BD9"/>
-    <mergeCell ref="BE7:BE9"/>
-    <mergeCell ref="BF7:BF9"/>
-    <mergeCell ref="BG7:BG9"/>
-    <mergeCell ref="BH7:BH9"/>
-    <mergeCell ref="AW7:AW9"/>
-    <mergeCell ref="AX7:AX9"/>
-    <mergeCell ref="AY7:AY9"/>
-    <mergeCell ref="AZ7:AZ9"/>
-    <mergeCell ref="BA7:BA9"/>
-    <mergeCell ref="BB7:BB9"/>
-    <mergeCell ref="AQ7:AQ9"/>
-    <mergeCell ref="AR7:AR9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AT7:AT9"/>
-    <mergeCell ref="AU7:AU9"/>
-    <mergeCell ref="AV7:AV9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AP7:AP9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="T7:T9"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="FY6:GD6"/>
-    <mergeCell ref="GE6:GJ6"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="Q7:Q9"/>
-    <mergeCell ref="R7:R9"/>
-    <mergeCell ref="EU6:EZ6"/>
-    <mergeCell ref="FA6:FB7"/>
-    <mergeCell ref="FC6:FF7"/>
-    <mergeCell ref="FG6:FH7"/>
-    <mergeCell ref="FI6:FL7"/>
-    <mergeCell ref="FS6:FX6"/>
-    <mergeCell ref="EU7:EV7"/>
-    <mergeCell ref="EW7:EZ7"/>
-    <mergeCell ref="BR6:BT6"/>
-    <mergeCell ref="BU6:BW6"/>
-    <mergeCell ref="BX6:BZ6"/>
-    <mergeCell ref="CA6:CC6"/>
-    <mergeCell ref="CG6:CI6"/>
-    <mergeCell ref="CJ6:CL6"/>
-    <mergeCell ref="FO5:FR7"/>
-    <mergeCell ref="FS5:GJ5"/>
-    <mergeCell ref="BX4:CC5"/>
-    <mergeCell ref="CD4:CF6"/>
-    <mergeCell ref="CG4:CL5"/>
-    <mergeCell ref="CM4:CR5"/>
-    <mergeCell ref="CS4:CU6"/>
-    <mergeCell ref="CV4:CX6"/>
-    <mergeCell ref="CM6:CO6"/>
-    <mergeCell ref="CP6:CR6"/>
-    <mergeCell ref="CA7:CA9"/>
-    <mergeCell ref="CB7:CB9"/>
-    <mergeCell ref="CC7:CC9"/>
-    <mergeCell ref="CD7:CD9"/>
-    <mergeCell ref="CE7:CE9"/>
-    <mergeCell ref="CF7:CF9"/>
-    <mergeCell ref="BU7:BU9"/>
-    <mergeCell ref="BV7:BV9"/>
-    <mergeCell ref="AW6:AY6"/>
-    <mergeCell ref="GW4:HB6"/>
-    <mergeCell ref="AE5:AM5"/>
-    <mergeCell ref="BO5:BW5"/>
-    <mergeCell ref="CY5:DG5"/>
-    <mergeCell ref="DQ5:DQ9"/>
-    <mergeCell ref="DR5:DR9"/>
-    <mergeCell ref="DS5:DV7"/>
-    <mergeCell ref="DW5:EH5"/>
-    <mergeCell ref="EI5:EI9"/>
-    <mergeCell ref="EJ5:EJ9"/>
-    <mergeCell ref="FG4:FL5"/>
-    <mergeCell ref="FM4:GJ4"/>
-    <mergeCell ref="GK4:GK9"/>
-    <mergeCell ref="GL4:GL9"/>
-    <mergeCell ref="GM4:GP7"/>
-    <mergeCell ref="GQ4:GV6"/>
-    <mergeCell ref="FM5:FM9"/>
-    <mergeCell ref="FN5:FN9"/>
-    <mergeCell ref="FS7:FT7"/>
-    <mergeCell ref="FU7:FX7"/>
-    <mergeCell ref="DE6:DG6"/>
-    <mergeCell ref="DH6:DJ6"/>
-    <mergeCell ref="DK6:DM6"/>
-    <mergeCell ref="DH4:DM5"/>
-    <mergeCell ref="DN4:DP6"/>
-    <mergeCell ref="DQ4:EH4"/>
-    <mergeCell ref="EI4:EZ4"/>
-    <mergeCell ref="FA4:FF5"/>
-    <mergeCell ref="EK5:EN7"/>
-    <mergeCell ref="EO5:EZ5"/>
-    <mergeCell ref="CY6:DA6"/>
-    <mergeCell ref="DB6:DD6"/>
-    <mergeCell ref="DW6:EB6"/>
-    <mergeCell ref="EC6:EH6"/>
-    <mergeCell ref="EO6:ET6"/>
-    <mergeCell ref="DA7:DA9"/>
-    <mergeCell ref="DB7:DB9"/>
-    <mergeCell ref="DC7:DC9"/>
-    <mergeCell ref="DD7:DD9"/>
-    <mergeCell ref="DM7:DM9"/>
-    <mergeCell ref="DN7:DN9"/>
-    <mergeCell ref="DO7:DO9"/>
-    <mergeCell ref="DP7:DP9"/>
-    <mergeCell ref="DE7:DE9"/>
-    <mergeCell ref="DF7:DF9"/>
-    <mergeCell ref="DG7:DG9"/>
-    <mergeCell ref="DH7:DH9"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="S4:X5"/>
-    <mergeCell ref="Y4:AA6"/>
-    <mergeCell ref="AB4:AD6"/>
-    <mergeCell ref="AE4:AM4"/>
-    <mergeCell ref="AN4:AS5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:U6"/>
-    <mergeCell ref="V6:X6"/>
-    <mergeCell ref="AE6:AG6"/>
-    <mergeCell ref="AH6:AJ6"/>
-    <mergeCell ref="AK6:AM6"/>
-    <mergeCell ref="AN6:AP6"/>
-    <mergeCell ref="AQ6:AS6"/>
-    <mergeCell ref="M3:AR3"/>
-    <mergeCell ref="AW3:CF3"/>
-    <mergeCell ref="CG3:DP3"/>
-    <mergeCell ref="DQ3:FL3"/>
-    <mergeCell ref="FM3:GJ3"/>
-    <mergeCell ref="GK3:HB3"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="D3:D9"/>
-    <mergeCell ref="F3:F9"/>
-    <mergeCell ref="H3:L5"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="AT4:AV6"/>
-    <mergeCell ref="AW4:BB5"/>
-    <mergeCell ref="BC4:BH5"/>
-    <mergeCell ref="BI4:BK6"/>
-    <mergeCell ref="BL4:BN6"/>
-    <mergeCell ref="BO4:BW4"/>
-    <mergeCell ref="AZ6:BB6"/>
-    <mergeCell ref="BC6:BE6"/>
-    <mergeCell ref="BF6:BH6"/>
-    <mergeCell ref="BO6:BQ6"/>
-    <mergeCell ref="CY4:DG4"/>
+    <mergeCell ref="DK7:DK9"/>
+    <mergeCell ref="DL7:DL9"/>
+    <mergeCell ref="EL8:EN8"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EP8:EP9"/>
+    <mergeCell ref="EQ8:EQ9"/>
+    <mergeCell ref="ER8:ET8"/>
+    <mergeCell ref="EU8:EU9"/>
+    <mergeCell ref="DZ8:EB8"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="EF8:EH8"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="FD8:FF8"/>
+    <mergeCell ref="FG8:FG9"/>
+    <mergeCell ref="FH8:FH9"/>
+    <mergeCell ref="FI8:FI9"/>
+    <mergeCell ref="FJ8:FL8"/>
+    <mergeCell ref="FO8:FO9"/>
+    <mergeCell ref="EV8:EV9"/>
+    <mergeCell ref="EW8:EW9"/>
+    <mergeCell ref="EX8:EZ8"/>
+    <mergeCell ref="FA8:FA9"/>
+    <mergeCell ref="FB8:FB9"/>
+    <mergeCell ref="FC8:FC9"/>
+    <mergeCell ref="GT8:GV8"/>
+    <mergeCell ref="GW8:GW9"/>
+    <mergeCell ref="GX8:GX9"/>
+    <mergeCell ref="GY8:GY9"/>
+    <mergeCell ref="GZ8:HB8"/>
+    <mergeCell ref="GH8:GJ8"/>
+    <mergeCell ref="GM8:GM9"/>
+    <mergeCell ref="GN8:GP8"/>
+    <mergeCell ref="GQ8:GQ9"/>
+    <mergeCell ref="GR8:GR9"/>
+    <mergeCell ref="GS8:GS9"/>
+    <mergeCell ref="FZ8:FZ9"/>
+    <mergeCell ref="GA8:GA9"/>
+    <mergeCell ref="GB8:GD8"/>
+    <mergeCell ref="GE8:GE9"/>
+    <mergeCell ref="GF8:GF9"/>
+    <mergeCell ref="GG8:GG9"/>
+    <mergeCell ref="FP8:FR8"/>
+    <mergeCell ref="FS8:FS9"/>
+    <mergeCell ref="FT8:FT9"/>
+    <mergeCell ref="FU8:FU9"/>
+    <mergeCell ref="FV8:FX8"/>
+    <mergeCell ref="FY8:FY9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/templates/summaryReportForm5.xlsx
+++ b/src/main/resources/templates/summaryReportForm5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD654E5D-A0A3-4FDF-8E7B-11F759315ECF}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42E54488-EF10-4DE0-BEC9-CA9914410EA7}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2222,10 +2222,158 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2237,304 +2385,156 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="32" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="33" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="3" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="27" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="2" borderId="28" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="3" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2829,14 +2829,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:210" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="95" t="s">
+      <c r="A1" s="81" t="s">
         <v>437</v>
       </c>
-      <c r="B1" s="95"/>
-      <c r="C1" s="95"/>
-      <c r="D1" s="95"/>
-      <c r="E1" s="95"/>
-      <c r="F1" s="95"/>
+      <c r="B1" s="81"/>
+      <c r="C1" s="81"/>
+      <c r="D1" s="81"/>
+      <c r="E1" s="81"/>
+      <c r="F1" s="81"/>
       <c r="G1" s="18" t="s">
         <v>483</v>
       </c>
@@ -3257,255 +3257,255 @@
       <c r="HB2" s="7"/>
     </row>
     <row r="3" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="37" t="s">
+      <c r="A3" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="37" t="s">
+      <c r="B3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="37" t="s">
+      <c r="C3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="42" t="s">
         <v>476</v>
       </c>
       <c r="E3" s="9"/>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="42" t="s">
         <v>477</v>
       </c>
       <c r="G3" s="10"/>
-      <c r="H3" s="103" t="s">
+      <c r="H3" s="44" t="s">
         <v>478</v>
       </c>
-      <c r="I3" s="104"/>
-      <c r="J3" s="104"/>
-      <c r="K3" s="104"/>
-      <c r="L3" s="105"/>
-      <c r="M3" s="96" t="s">
+      <c r="I3" s="45"/>
+      <c r="J3" s="45"/>
+      <c r="K3" s="45"/>
+      <c r="L3" s="46"/>
+      <c r="M3" s="37" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="96"/>
-      <c r="O3" s="96"/>
-      <c r="P3" s="96"/>
-      <c r="Q3" s="96"/>
-      <c r="R3" s="96"/>
-      <c r="S3" s="96"/>
-      <c r="T3" s="96"/>
-      <c r="U3" s="96"/>
-      <c r="V3" s="96"/>
-      <c r="W3" s="96"/>
-      <c r="X3" s="96"/>
-      <c r="Y3" s="96"/>
-      <c r="Z3" s="96"/>
-      <c r="AA3" s="96"/>
-      <c r="AB3" s="96"/>
-      <c r="AC3" s="96"/>
-      <c r="AD3" s="97"/>
-      <c r="AE3" s="97"/>
-      <c r="AF3" s="97"/>
-      <c r="AG3" s="97"/>
-      <c r="AH3" s="97"/>
-      <c r="AI3" s="97"/>
-      <c r="AJ3" s="97"/>
-      <c r="AK3" s="97"/>
-      <c r="AL3" s="97"/>
-      <c r="AM3" s="97"/>
-      <c r="AN3" s="96"/>
-      <c r="AO3" s="96"/>
-      <c r="AP3" s="96"/>
-      <c r="AQ3" s="96"/>
-      <c r="AR3" s="96"/>
+      <c r="N3" s="37"/>
+      <c r="O3" s="37"/>
+      <c r="P3" s="37"/>
+      <c r="Q3" s="37"/>
+      <c r="R3" s="37"/>
+      <c r="S3" s="37"/>
+      <c r="T3" s="37"/>
+      <c r="U3" s="37"/>
+      <c r="V3" s="37"/>
+      <c r="W3" s="37"/>
+      <c r="X3" s="37"/>
+      <c r="Y3" s="37"/>
+      <c r="Z3" s="37"/>
+      <c r="AA3" s="37"/>
+      <c r="AB3" s="37"/>
+      <c r="AC3" s="37"/>
+      <c r="AD3" s="85"/>
+      <c r="AE3" s="85"/>
+      <c r="AF3" s="85"/>
+      <c r="AG3" s="85"/>
+      <c r="AH3" s="85"/>
+      <c r="AI3" s="85"/>
+      <c r="AJ3" s="85"/>
+      <c r="AK3" s="85"/>
+      <c r="AL3" s="85"/>
+      <c r="AM3" s="85"/>
+      <c r="AN3" s="37"/>
+      <c r="AO3" s="37"/>
+      <c r="AP3" s="37"/>
+      <c r="AQ3" s="37"/>
+      <c r="AR3" s="37"/>
       <c r="AS3" s="11"/>
       <c r="AT3" s="11"/>
       <c r="AU3" s="11"/>
       <c r="AV3" s="11"/>
-      <c r="AW3" s="98" t="s">
+      <c r="AW3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="AX3" s="96"/>
-      <c r="AY3" s="96"/>
-      <c r="AZ3" s="96"/>
-      <c r="BA3" s="96"/>
-      <c r="BB3" s="96"/>
-      <c r="BC3" s="96"/>
-      <c r="BD3" s="96"/>
-      <c r="BE3" s="96"/>
-      <c r="BF3" s="96"/>
-      <c r="BG3" s="96"/>
-      <c r="BH3" s="96"/>
-      <c r="BI3" s="96"/>
-      <c r="BJ3" s="96"/>
-      <c r="BK3" s="96"/>
-      <c r="BL3" s="96"/>
-      <c r="BM3" s="96"/>
-      <c r="BN3" s="96"/>
-      <c r="BO3" s="96"/>
-      <c r="BP3" s="96"/>
-      <c r="BQ3" s="96"/>
-      <c r="BR3" s="96"/>
-      <c r="BS3" s="96"/>
-      <c r="BT3" s="96"/>
-      <c r="BU3" s="96"/>
-      <c r="BV3" s="96"/>
-      <c r="BW3" s="96"/>
-      <c r="BX3" s="96"/>
-      <c r="BY3" s="96"/>
-      <c r="BZ3" s="96"/>
-      <c r="CA3" s="96"/>
-      <c r="CB3" s="96"/>
-      <c r="CC3" s="96"/>
-      <c r="CD3" s="96"/>
-      <c r="CE3" s="96"/>
-      <c r="CF3" s="99"/>
-      <c r="CG3" s="98" t="s">
+      <c r="AX3" s="37"/>
+      <c r="AY3" s="37"/>
+      <c r="AZ3" s="37"/>
+      <c r="BA3" s="37"/>
+      <c r="BB3" s="37"/>
+      <c r="BC3" s="37"/>
+      <c r="BD3" s="37"/>
+      <c r="BE3" s="37"/>
+      <c r="BF3" s="37"/>
+      <c r="BG3" s="37"/>
+      <c r="BH3" s="37"/>
+      <c r="BI3" s="37"/>
+      <c r="BJ3" s="37"/>
+      <c r="BK3" s="37"/>
+      <c r="BL3" s="37"/>
+      <c r="BM3" s="37"/>
+      <c r="BN3" s="37"/>
+      <c r="BO3" s="37"/>
+      <c r="BP3" s="37"/>
+      <c r="BQ3" s="37"/>
+      <c r="BR3" s="37"/>
+      <c r="BS3" s="37"/>
+      <c r="BT3" s="37"/>
+      <c r="BU3" s="37"/>
+      <c r="BV3" s="37"/>
+      <c r="BW3" s="37"/>
+      <c r="BX3" s="37"/>
+      <c r="BY3" s="37"/>
+      <c r="BZ3" s="37"/>
+      <c r="CA3" s="37"/>
+      <c r="CB3" s="37"/>
+      <c r="CC3" s="37"/>
+      <c r="CD3" s="37"/>
+      <c r="CE3" s="37"/>
+      <c r="CF3" s="38"/>
+      <c r="CG3" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="CH3" s="96"/>
-      <c r="CI3" s="96"/>
-      <c r="CJ3" s="96"/>
-      <c r="CK3" s="96"/>
-      <c r="CL3" s="96"/>
-      <c r="CM3" s="96"/>
-      <c r="CN3" s="96"/>
-      <c r="CO3" s="96"/>
-      <c r="CP3" s="96"/>
-      <c r="CQ3" s="96"/>
-      <c r="CR3" s="96"/>
-      <c r="CS3" s="96"/>
-      <c r="CT3" s="96"/>
-      <c r="CU3" s="96"/>
-      <c r="CV3" s="96"/>
-      <c r="CW3" s="96"/>
-      <c r="CX3" s="96"/>
-      <c r="CY3" s="96"/>
-      <c r="CZ3" s="96"/>
-      <c r="DA3" s="96"/>
-      <c r="DB3" s="96"/>
-      <c r="DC3" s="96"/>
-      <c r="DD3" s="96"/>
-      <c r="DE3" s="96"/>
-      <c r="DF3" s="96"/>
-      <c r="DG3" s="96"/>
-      <c r="DH3" s="96"/>
-      <c r="DI3" s="96"/>
-      <c r="DJ3" s="96"/>
-      <c r="DK3" s="96"/>
-      <c r="DL3" s="96"/>
-      <c r="DM3" s="96"/>
-      <c r="DN3" s="96"/>
-      <c r="DO3" s="96"/>
-      <c r="DP3" s="99"/>
-      <c r="DQ3" s="98" t="s">
+      <c r="CH3" s="37"/>
+      <c r="CI3" s="37"/>
+      <c r="CJ3" s="37"/>
+      <c r="CK3" s="37"/>
+      <c r="CL3" s="37"/>
+      <c r="CM3" s="37"/>
+      <c r="CN3" s="37"/>
+      <c r="CO3" s="37"/>
+      <c r="CP3" s="37"/>
+      <c r="CQ3" s="37"/>
+      <c r="CR3" s="37"/>
+      <c r="CS3" s="37"/>
+      <c r="CT3" s="37"/>
+      <c r="CU3" s="37"/>
+      <c r="CV3" s="37"/>
+      <c r="CW3" s="37"/>
+      <c r="CX3" s="37"/>
+      <c r="CY3" s="37"/>
+      <c r="CZ3" s="37"/>
+      <c r="DA3" s="37"/>
+      <c r="DB3" s="37"/>
+      <c r="DC3" s="37"/>
+      <c r="DD3" s="37"/>
+      <c r="DE3" s="37"/>
+      <c r="DF3" s="37"/>
+      <c r="DG3" s="37"/>
+      <c r="DH3" s="37"/>
+      <c r="DI3" s="37"/>
+      <c r="DJ3" s="37"/>
+      <c r="DK3" s="37"/>
+      <c r="DL3" s="37"/>
+      <c r="DM3" s="37"/>
+      <c r="DN3" s="37"/>
+      <c r="DO3" s="37"/>
+      <c r="DP3" s="38"/>
+      <c r="DQ3" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="DR3" s="96"/>
-      <c r="DS3" s="96"/>
-      <c r="DT3" s="96"/>
-      <c r="DU3" s="96"/>
-      <c r="DV3" s="96"/>
-      <c r="DW3" s="96"/>
-      <c r="DX3" s="96"/>
-      <c r="DY3" s="96"/>
-      <c r="DZ3" s="96"/>
-      <c r="EA3" s="96"/>
-      <c r="EB3" s="96"/>
-      <c r="EC3" s="96"/>
-      <c r="ED3" s="96"/>
-      <c r="EE3" s="96"/>
-      <c r="EF3" s="96"/>
-      <c r="EG3" s="96"/>
-      <c r="EH3" s="96"/>
-      <c r="EI3" s="96"/>
-      <c r="EJ3" s="96"/>
-      <c r="EK3" s="96"/>
-      <c r="EL3" s="96"/>
-      <c r="EM3" s="96"/>
-      <c r="EN3" s="96"/>
-      <c r="EO3" s="96"/>
-      <c r="EP3" s="96"/>
-      <c r="EQ3" s="96"/>
-      <c r="ER3" s="96"/>
-      <c r="ES3" s="96"/>
-      <c r="ET3" s="96"/>
-      <c r="EU3" s="96"/>
-      <c r="EV3" s="96"/>
-      <c r="EW3" s="96"/>
-      <c r="EX3" s="96"/>
-      <c r="EY3" s="96"/>
-      <c r="EZ3" s="96"/>
-      <c r="FA3" s="96"/>
-      <c r="FB3" s="96"/>
-      <c r="FC3" s="96"/>
-      <c r="FD3" s="96"/>
-      <c r="FE3" s="96"/>
-      <c r="FF3" s="96"/>
-      <c r="FG3" s="96"/>
-      <c r="FH3" s="96"/>
-      <c r="FI3" s="96"/>
-      <c r="FJ3" s="96"/>
-      <c r="FK3" s="96"/>
-      <c r="FL3" s="100"/>
-      <c r="FM3" s="101" t="s">
+      <c r="DR3" s="37"/>
+      <c r="DS3" s="37"/>
+      <c r="DT3" s="37"/>
+      <c r="DU3" s="37"/>
+      <c r="DV3" s="37"/>
+      <c r="DW3" s="37"/>
+      <c r="DX3" s="37"/>
+      <c r="DY3" s="37"/>
+      <c r="DZ3" s="37"/>
+      <c r="EA3" s="37"/>
+      <c r="EB3" s="37"/>
+      <c r="EC3" s="37"/>
+      <c r="ED3" s="37"/>
+      <c r="EE3" s="37"/>
+      <c r="EF3" s="37"/>
+      <c r="EG3" s="37"/>
+      <c r="EH3" s="37"/>
+      <c r="EI3" s="37"/>
+      <c r="EJ3" s="37"/>
+      <c r="EK3" s="37"/>
+      <c r="EL3" s="37"/>
+      <c r="EM3" s="37"/>
+      <c r="EN3" s="37"/>
+      <c r="EO3" s="37"/>
+      <c r="EP3" s="37"/>
+      <c r="EQ3" s="37"/>
+      <c r="ER3" s="37"/>
+      <c r="ES3" s="37"/>
+      <c r="ET3" s="37"/>
+      <c r="EU3" s="37"/>
+      <c r="EV3" s="37"/>
+      <c r="EW3" s="37"/>
+      <c r="EX3" s="37"/>
+      <c r="EY3" s="37"/>
+      <c r="EZ3" s="37"/>
+      <c r="FA3" s="37"/>
+      <c r="FB3" s="37"/>
+      <c r="FC3" s="37"/>
+      <c r="FD3" s="37"/>
+      <c r="FE3" s="37"/>
+      <c r="FF3" s="37"/>
+      <c r="FG3" s="37"/>
+      <c r="FH3" s="37"/>
+      <c r="FI3" s="37"/>
+      <c r="FJ3" s="37"/>
+      <c r="FK3" s="37"/>
+      <c r="FL3" s="39"/>
+      <c r="FM3" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="FN3" s="96"/>
-      <c r="FO3" s="96"/>
-      <c r="FP3" s="96"/>
-      <c r="FQ3" s="96"/>
-      <c r="FR3" s="96"/>
-      <c r="FS3" s="96"/>
-      <c r="FT3" s="96"/>
-      <c r="FU3" s="96"/>
-      <c r="FV3" s="96"/>
-      <c r="FW3" s="96"/>
-      <c r="FX3" s="96"/>
-      <c r="FY3" s="96"/>
-      <c r="FZ3" s="96"/>
-      <c r="GA3" s="96"/>
-      <c r="GB3" s="96"/>
-      <c r="GC3" s="96"/>
-      <c r="GD3" s="96"/>
-      <c r="GE3" s="96"/>
-      <c r="GF3" s="96"/>
-      <c r="GG3" s="96"/>
-      <c r="GH3" s="96"/>
-      <c r="GI3" s="96"/>
-      <c r="GJ3" s="96"/>
-      <c r="GK3" s="102" t="s">
+      <c r="FN3" s="37"/>
+      <c r="FO3" s="37"/>
+      <c r="FP3" s="37"/>
+      <c r="FQ3" s="37"/>
+      <c r="FR3" s="37"/>
+      <c r="FS3" s="37"/>
+      <c r="FT3" s="37"/>
+      <c r="FU3" s="37"/>
+      <c r="FV3" s="37"/>
+      <c r="FW3" s="37"/>
+      <c r="FX3" s="37"/>
+      <c r="FY3" s="37"/>
+      <c r="FZ3" s="37"/>
+      <c r="GA3" s="37"/>
+      <c r="GB3" s="37"/>
+      <c r="GC3" s="37"/>
+      <c r="GD3" s="37"/>
+      <c r="GE3" s="37"/>
+      <c r="GF3" s="37"/>
+      <c r="GG3" s="37"/>
+      <c r="GH3" s="37"/>
+      <c r="GI3" s="37"/>
+      <c r="GJ3" s="37"/>
+      <c r="GK3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="GL3" s="96"/>
-      <c r="GM3" s="96"/>
-      <c r="GN3" s="96"/>
-      <c r="GO3" s="96"/>
-      <c r="GP3" s="96"/>
-      <c r="GQ3" s="96"/>
-      <c r="GR3" s="96"/>
-      <c r="GS3" s="96"/>
-      <c r="GT3" s="96"/>
-      <c r="GU3" s="96"/>
-      <c r="GV3" s="96"/>
-      <c r="GW3" s="96"/>
-      <c r="GX3" s="96"/>
-      <c r="GY3" s="96"/>
-      <c r="GZ3" s="96"/>
-      <c r="HA3" s="96"/>
-      <c r="HB3" s="100"/>
+      <c r="GL3" s="37"/>
+      <c r="GM3" s="37"/>
+      <c r="GN3" s="37"/>
+      <c r="GO3" s="37"/>
+      <c r="GP3" s="37"/>
+      <c r="GQ3" s="37"/>
+      <c r="GR3" s="37"/>
+      <c r="GS3" s="37"/>
+      <c r="GT3" s="37"/>
+      <c r="GU3" s="37"/>
+      <c r="GV3" s="37"/>
+      <c r="GW3" s="37"/>
+      <c r="GX3" s="37"/>
+      <c r="GY3" s="37"/>
+      <c r="GZ3" s="37"/>
+      <c r="HA3" s="37"/>
+      <c r="HB3" s="39"/>
     </row>
     <row r="4" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="38"/>
-      <c r="B4" s="38"/>
-      <c r="C4" s="38"/>
-      <c r="D4" s="38"/>
+      <c r="A4" s="43"/>
+      <c r="B4" s="43"/>
+      <c r="C4" s="43"/>
+      <c r="D4" s="43"/>
       <c r="E4" s="12"/>
-      <c r="F4" s="38"/>
+      <c r="F4" s="43"/>
       <c r="G4" s="13"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="107"/>
-      <c r="J4" s="107"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="64" t="s">
+      <c r="H4" s="47"/>
+      <c r="I4" s="48"/>
+      <c r="J4" s="48"/>
+      <c r="K4" s="48"/>
+      <c r="L4" s="49"/>
+      <c r="M4" s="82" t="s">
         <v>9</v>
       </c>
       <c r="N4" s="65"/>
@@ -3513,48 +3513,48 @@
       <c r="P4" s="65"/>
       <c r="Q4" s="65"/>
       <c r="R4" s="66"/>
-      <c r="S4" s="70" t="s">
+      <c r="S4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="T4" s="70"/>
-      <c r="U4" s="70"/>
-      <c r="V4" s="70"/>
-      <c r="W4" s="70"/>
-      <c r="X4" s="70"/>
-      <c r="Y4" s="55" t="s">
+      <c r="T4" s="69"/>
+      <c r="U4" s="69"/>
+      <c r="V4" s="69"/>
+      <c r="W4" s="69"/>
+      <c r="X4" s="69"/>
+      <c r="Y4" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="Z4" s="56"/>
-      <c r="AA4" s="71"/>
-      <c r="AB4" s="55" t="s">
+      <c r="Z4" s="57"/>
+      <c r="AA4" s="70"/>
+      <c r="AB4" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="AC4" s="56"/>
-      <c r="AD4" s="71"/>
-      <c r="AE4" s="54" t="s">
+      <c r="AC4" s="57"/>
+      <c r="AD4" s="70"/>
+      <c r="AE4" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="AF4" s="54"/>
-      <c r="AG4" s="54"/>
-      <c r="AH4" s="54"/>
-      <c r="AI4" s="54"/>
-      <c r="AJ4" s="54"/>
-      <c r="AK4" s="54"/>
-      <c r="AL4" s="54"/>
-      <c r="AM4" s="54"/>
-      <c r="AN4" s="54" t="s">
+      <c r="AF4" s="73"/>
+      <c r="AG4" s="73"/>
+      <c r="AH4" s="73"/>
+      <c r="AI4" s="73"/>
+      <c r="AJ4" s="73"/>
+      <c r="AK4" s="73"/>
+      <c r="AL4" s="73"/>
+      <c r="AM4" s="73"/>
+      <c r="AN4" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="AO4" s="54"/>
-      <c r="AP4" s="54"/>
-      <c r="AQ4" s="54"/>
-      <c r="AR4" s="54"/>
-      <c r="AS4" s="54"/>
-      <c r="AT4" s="55" t="s">
+      <c r="AO4" s="73"/>
+      <c r="AP4" s="73"/>
+      <c r="AQ4" s="73"/>
+      <c r="AR4" s="73"/>
+      <c r="AS4" s="73"/>
+      <c r="AT4" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="AU4" s="56"/>
-      <c r="AV4" s="57"/>
+      <c r="AU4" s="57"/>
+      <c r="AV4" s="58"/>
       <c r="AW4" s="65" t="s">
         <v>9</v>
       </c>
@@ -3563,49 +3563,49 @@
       <c r="AZ4" s="65"/>
       <c r="BA4" s="65"/>
       <c r="BB4" s="66"/>
-      <c r="BC4" s="70" t="s">
+      <c r="BC4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="BD4" s="70"/>
-      <c r="BE4" s="70"/>
-      <c r="BF4" s="70"/>
-      <c r="BG4" s="70"/>
-      <c r="BH4" s="70"/>
-      <c r="BI4" s="55" t="s">
+      <c r="BD4" s="69"/>
+      <c r="BE4" s="69"/>
+      <c r="BF4" s="69"/>
+      <c r="BG4" s="69"/>
+      <c r="BH4" s="69"/>
+      <c r="BI4" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="BJ4" s="56"/>
-      <c r="BK4" s="71"/>
-      <c r="BL4" s="55" t="s">
+      <c r="BJ4" s="57"/>
+      <c r="BK4" s="70"/>
+      <c r="BL4" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="BM4" s="56"/>
-      <c r="BN4" s="71"/>
-      <c r="BO4" s="54" t="s">
+      <c r="BM4" s="57"/>
+      <c r="BN4" s="70"/>
+      <c r="BO4" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="BP4" s="54"/>
-      <c r="BQ4" s="54"/>
-      <c r="BR4" s="54"/>
-      <c r="BS4" s="54"/>
-      <c r="BT4" s="54"/>
-      <c r="BU4" s="54"/>
-      <c r="BV4" s="54"/>
-      <c r="BW4" s="54"/>
-      <c r="BX4" s="54" t="s">
+      <c r="BP4" s="73"/>
+      <c r="BQ4" s="73"/>
+      <c r="BR4" s="73"/>
+      <c r="BS4" s="73"/>
+      <c r="BT4" s="73"/>
+      <c r="BU4" s="73"/>
+      <c r="BV4" s="73"/>
+      <c r="BW4" s="73"/>
+      <c r="BX4" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="BY4" s="54"/>
-      <c r="BZ4" s="54"/>
-      <c r="CA4" s="54"/>
-      <c r="CB4" s="54"/>
-      <c r="CC4" s="54"/>
-      <c r="CD4" s="55" t="s">
+      <c r="BY4" s="73"/>
+      <c r="BZ4" s="73"/>
+      <c r="CA4" s="73"/>
+      <c r="CB4" s="73"/>
+      <c r="CC4" s="73"/>
+      <c r="CD4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="CE4" s="56"/>
-      <c r="CF4" s="57"/>
-      <c r="CG4" s="64" t="s">
+      <c r="CE4" s="57"/>
+      <c r="CF4" s="58"/>
+      <c r="CG4" s="82" t="s">
         <v>9</v>
       </c>
       <c r="CH4" s="65"/>
@@ -3613,1611 +3613,1611 @@
       <c r="CJ4" s="65"/>
       <c r="CK4" s="65"/>
       <c r="CL4" s="66"/>
-      <c r="CM4" s="70" t="s">
+      <c r="CM4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="CN4" s="70"/>
-      <c r="CO4" s="70"/>
-      <c r="CP4" s="70"/>
-      <c r="CQ4" s="70"/>
-      <c r="CR4" s="70"/>
-      <c r="CS4" s="55" t="s">
+      <c r="CN4" s="69"/>
+      <c r="CO4" s="69"/>
+      <c r="CP4" s="69"/>
+      <c r="CQ4" s="69"/>
+      <c r="CR4" s="69"/>
+      <c r="CS4" s="56" t="s">
         <v>11</v>
       </c>
-      <c r="CT4" s="56"/>
-      <c r="CU4" s="71"/>
-      <c r="CV4" s="55" t="s">
+      <c r="CT4" s="57"/>
+      <c r="CU4" s="70"/>
+      <c r="CV4" s="56" t="s">
         <v>12</v>
       </c>
-      <c r="CW4" s="56"/>
-      <c r="CX4" s="71"/>
-      <c r="CY4" s="54" t="s">
+      <c r="CW4" s="57"/>
+      <c r="CX4" s="70"/>
+      <c r="CY4" s="73" t="s">
         <v>13</v>
       </c>
-      <c r="CZ4" s="54"/>
-      <c r="DA4" s="54"/>
-      <c r="DB4" s="54"/>
-      <c r="DC4" s="54"/>
-      <c r="DD4" s="54"/>
-      <c r="DE4" s="54"/>
-      <c r="DF4" s="54"/>
-      <c r="DG4" s="54"/>
-      <c r="DH4" s="54" t="s">
+      <c r="CZ4" s="73"/>
+      <c r="DA4" s="73"/>
+      <c r="DB4" s="73"/>
+      <c r="DC4" s="73"/>
+      <c r="DD4" s="73"/>
+      <c r="DE4" s="73"/>
+      <c r="DF4" s="73"/>
+      <c r="DG4" s="73"/>
+      <c r="DH4" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="DI4" s="54"/>
-      <c r="DJ4" s="54"/>
-      <c r="DK4" s="54"/>
-      <c r="DL4" s="54"/>
-      <c r="DM4" s="54"/>
-      <c r="DN4" s="55" t="s">
+      <c r="DI4" s="73"/>
+      <c r="DJ4" s="73"/>
+      <c r="DK4" s="73"/>
+      <c r="DL4" s="73"/>
+      <c r="DM4" s="73"/>
+      <c r="DN4" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="DO4" s="56"/>
-      <c r="DP4" s="57"/>
-      <c r="DQ4" s="91" t="s">
+      <c r="DO4" s="57"/>
+      <c r="DP4" s="58"/>
+      <c r="DQ4" s="86" t="s">
         <v>15</v>
       </c>
-      <c r="DR4" s="92"/>
-      <c r="DS4" s="92"/>
-      <c r="DT4" s="92"/>
-      <c r="DU4" s="92"/>
-      <c r="DV4" s="92"/>
-      <c r="DW4" s="92"/>
-      <c r="DX4" s="92"/>
-      <c r="DY4" s="92"/>
-      <c r="DZ4" s="92"/>
-      <c r="EA4" s="92"/>
-      <c r="EB4" s="92"/>
-      <c r="EC4" s="92"/>
-      <c r="ED4" s="92"/>
-      <c r="EE4" s="92"/>
-      <c r="EF4" s="92"/>
-      <c r="EG4" s="92"/>
-      <c r="EH4" s="93"/>
-      <c r="EI4" s="81" t="s">
+      <c r="DR4" s="87"/>
+      <c r="DS4" s="87"/>
+      <c r="DT4" s="87"/>
+      <c r="DU4" s="87"/>
+      <c r="DV4" s="87"/>
+      <c r="DW4" s="87"/>
+      <c r="DX4" s="87"/>
+      <c r="DY4" s="87"/>
+      <c r="DZ4" s="87"/>
+      <c r="EA4" s="87"/>
+      <c r="EB4" s="87"/>
+      <c r="EC4" s="87"/>
+      <c r="ED4" s="87"/>
+      <c r="EE4" s="87"/>
+      <c r="EF4" s="87"/>
+      <c r="EG4" s="87"/>
+      <c r="EH4" s="88"/>
+      <c r="EI4" s="89" t="s">
         <v>10</v>
       </c>
-      <c r="EJ4" s="82"/>
-      <c r="EK4" s="82"/>
-      <c r="EL4" s="82"/>
-      <c r="EM4" s="82"/>
-      <c r="EN4" s="82"/>
-      <c r="EO4" s="82"/>
-      <c r="EP4" s="82"/>
-      <c r="EQ4" s="82"/>
-      <c r="ER4" s="82"/>
-      <c r="ES4" s="82"/>
-      <c r="ET4" s="82"/>
-      <c r="EU4" s="82"/>
-      <c r="EV4" s="82"/>
-      <c r="EW4" s="82"/>
-      <c r="EX4" s="82"/>
-      <c r="EY4" s="82"/>
-      <c r="EZ4" s="83"/>
-      <c r="FA4" s="81" t="s">
+      <c r="EJ4" s="90"/>
+      <c r="EK4" s="90"/>
+      <c r="EL4" s="90"/>
+      <c r="EM4" s="90"/>
+      <c r="EN4" s="90"/>
+      <c r="EO4" s="90"/>
+      <c r="EP4" s="90"/>
+      <c r="EQ4" s="90"/>
+      <c r="ER4" s="90"/>
+      <c r="ES4" s="90"/>
+      <c r="ET4" s="90"/>
+      <c r="EU4" s="90"/>
+      <c r="EV4" s="90"/>
+      <c r="EW4" s="90"/>
+      <c r="EX4" s="90"/>
+      <c r="EY4" s="90"/>
+      <c r="EZ4" s="91"/>
+      <c r="FA4" s="89" t="s">
         <v>11</v>
       </c>
-      <c r="FB4" s="82"/>
-      <c r="FC4" s="82"/>
-      <c r="FD4" s="82"/>
-      <c r="FE4" s="82"/>
-      <c r="FF4" s="83"/>
-      <c r="FG4" s="81" t="s">
+      <c r="FB4" s="90"/>
+      <c r="FC4" s="90"/>
+      <c r="FD4" s="90"/>
+      <c r="FE4" s="90"/>
+      <c r="FF4" s="91"/>
+      <c r="FG4" s="89" t="s">
         <v>12</v>
       </c>
-      <c r="FH4" s="82"/>
-      <c r="FI4" s="82"/>
-      <c r="FJ4" s="82"/>
-      <c r="FK4" s="82"/>
-      <c r="FL4" s="83"/>
-      <c r="FM4" s="87" t="s">
+      <c r="FH4" s="90"/>
+      <c r="FI4" s="90"/>
+      <c r="FJ4" s="90"/>
+      <c r="FK4" s="90"/>
+      <c r="FL4" s="91"/>
+      <c r="FM4" s="110" t="s">
         <v>13</v>
       </c>
-      <c r="FN4" s="88"/>
-      <c r="FO4" s="88"/>
-      <c r="FP4" s="88"/>
-      <c r="FQ4" s="88"/>
-      <c r="FR4" s="88"/>
-      <c r="FS4" s="88"/>
-      <c r="FT4" s="88"/>
-      <c r="FU4" s="88"/>
-      <c r="FV4" s="88"/>
-      <c r="FW4" s="88"/>
-      <c r="FX4" s="88"/>
-      <c r="FY4" s="88"/>
-      <c r="FZ4" s="88"/>
-      <c r="GA4" s="88"/>
-      <c r="GB4" s="88"/>
-      <c r="GC4" s="88"/>
-      <c r="GD4" s="88"/>
-      <c r="GE4" s="88"/>
-      <c r="GF4" s="88"/>
-      <c r="GG4" s="88"/>
-      <c r="GH4" s="88"/>
-      <c r="GI4" s="88"/>
-      <c r="GJ4" s="88"/>
-      <c r="GK4" s="89" t="s">
+      <c r="FN4" s="111"/>
+      <c r="FO4" s="111"/>
+      <c r="FP4" s="111"/>
+      <c r="FQ4" s="111"/>
+      <c r="FR4" s="111"/>
+      <c r="FS4" s="111"/>
+      <c r="FT4" s="111"/>
+      <c r="FU4" s="111"/>
+      <c r="FV4" s="111"/>
+      <c r="FW4" s="111"/>
+      <c r="FX4" s="111"/>
+      <c r="FY4" s="111"/>
+      <c r="FZ4" s="111"/>
+      <c r="GA4" s="111"/>
+      <c r="GB4" s="111"/>
+      <c r="GC4" s="111"/>
+      <c r="GD4" s="111"/>
+      <c r="GE4" s="111"/>
+      <c r="GF4" s="111"/>
+      <c r="GG4" s="111"/>
+      <c r="GH4" s="111"/>
+      <c r="GI4" s="111"/>
+      <c r="GJ4" s="111"/>
+      <c r="GK4" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="GL4" s="33" t="s">
+      <c r="GL4" s="80" t="s">
         <v>17</v>
       </c>
-      <c r="GM4" s="34" t="s">
+      <c r="GM4" s="84" t="s">
         <v>18</v>
       </c>
-      <c r="GN4" s="34"/>
-      <c r="GO4" s="34"/>
-      <c r="GP4" s="34"/>
-      <c r="GQ4" s="34" t="s">
+      <c r="GN4" s="84"/>
+      <c r="GO4" s="84"/>
+      <c r="GP4" s="84"/>
+      <c r="GQ4" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="GR4" s="34"/>
-      <c r="GS4" s="34"/>
-      <c r="GT4" s="34"/>
-      <c r="GU4" s="34"/>
-      <c r="GV4" s="34"/>
-      <c r="GW4" s="34" t="s">
+      <c r="GR4" s="84"/>
+      <c r="GS4" s="84"/>
+      <c r="GT4" s="84"/>
+      <c r="GU4" s="84"/>
+      <c r="GV4" s="84"/>
+      <c r="GW4" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="GX4" s="34"/>
-      <c r="GY4" s="34"/>
-      <c r="GZ4" s="34"/>
-      <c r="HA4" s="34"/>
-      <c r="HB4" s="34"/>
+      <c r="GX4" s="84"/>
+      <c r="GY4" s="84"/>
+      <c r="GZ4" s="84"/>
+      <c r="HA4" s="84"/>
+      <c r="HB4" s="84"/>
     </row>
     <row r="5" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="38"/>
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="38"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
       <c r="E5" s="12"/>
-      <c r="F5" s="38"/>
+      <c r="F5" s="43"/>
       <c r="G5" s="13"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="110"/>
-      <c r="K5" s="110"/>
-      <c r="L5" s="111"/>
-      <c r="M5" s="67"/>
-      <c r="N5" s="68"/>
-      <c r="O5" s="68"/>
-      <c r="P5" s="68"/>
-      <c r="Q5" s="68"/>
-      <c r="R5" s="69"/>
-      <c r="S5" s="70"/>
-      <c r="T5" s="70"/>
-      <c r="U5" s="70"/>
-      <c r="V5" s="70"/>
-      <c r="W5" s="70"/>
-      <c r="X5" s="70"/>
-      <c r="Y5" s="58"/>
-      <c r="Z5" s="59"/>
-      <c r="AA5" s="72"/>
-      <c r="AB5" s="58"/>
-      <c r="AC5" s="59"/>
-      <c r="AD5" s="72"/>
-      <c r="AE5" s="34" t="s">
+      <c r="H5" s="50"/>
+      <c r="I5" s="51"/>
+      <c r="J5" s="51"/>
+      <c r="K5" s="51"/>
+      <c r="L5" s="52"/>
+      <c r="M5" s="83"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="67"/>
+      <c r="P5" s="67"/>
+      <c r="Q5" s="67"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="69"/>
+      <c r="T5" s="69"/>
+      <c r="U5" s="69"/>
+      <c r="V5" s="69"/>
+      <c r="W5" s="69"/>
+      <c r="X5" s="69"/>
+      <c r="Y5" s="59"/>
+      <c r="Z5" s="60"/>
+      <c r="AA5" s="71"/>
+      <c r="AB5" s="59"/>
+      <c r="AC5" s="60"/>
+      <c r="AD5" s="71"/>
+      <c r="AE5" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="AF5" s="34"/>
-      <c r="AG5" s="34"/>
-      <c r="AH5" s="34"/>
-      <c r="AI5" s="34"/>
-      <c r="AJ5" s="34"/>
-      <c r="AK5" s="34"/>
-      <c r="AL5" s="34"/>
-      <c r="AM5" s="34"/>
-      <c r="AN5" s="54"/>
-      <c r="AO5" s="54"/>
-      <c r="AP5" s="54"/>
-      <c r="AQ5" s="54"/>
-      <c r="AR5" s="54"/>
-      <c r="AS5" s="54"/>
-      <c r="AT5" s="58"/>
-      <c r="AU5" s="59"/>
-      <c r="AV5" s="60"/>
-      <c r="AW5" s="68"/>
-      <c r="AX5" s="68"/>
-      <c r="AY5" s="68"/>
-      <c r="AZ5" s="68"/>
-      <c r="BA5" s="68"/>
-      <c r="BB5" s="69"/>
-      <c r="BC5" s="70"/>
-      <c r="BD5" s="70"/>
-      <c r="BE5" s="70"/>
-      <c r="BF5" s="70"/>
-      <c r="BG5" s="70"/>
-      <c r="BH5" s="70"/>
-      <c r="BI5" s="58"/>
-      <c r="BJ5" s="59"/>
-      <c r="BK5" s="72"/>
-      <c r="BL5" s="58"/>
-      <c r="BM5" s="59"/>
-      <c r="BN5" s="72"/>
-      <c r="BO5" s="34" t="s">
+      <c r="AF5" s="84"/>
+      <c r="AG5" s="84"/>
+      <c r="AH5" s="84"/>
+      <c r="AI5" s="84"/>
+      <c r="AJ5" s="84"/>
+      <c r="AK5" s="84"/>
+      <c r="AL5" s="84"/>
+      <c r="AM5" s="84"/>
+      <c r="AN5" s="73"/>
+      <c r="AO5" s="73"/>
+      <c r="AP5" s="73"/>
+      <c r="AQ5" s="73"/>
+      <c r="AR5" s="73"/>
+      <c r="AS5" s="73"/>
+      <c r="AT5" s="59"/>
+      <c r="AU5" s="60"/>
+      <c r="AV5" s="61"/>
+      <c r="AW5" s="67"/>
+      <c r="AX5" s="67"/>
+      <c r="AY5" s="67"/>
+      <c r="AZ5" s="67"/>
+      <c r="BA5" s="67"/>
+      <c r="BB5" s="68"/>
+      <c r="BC5" s="69"/>
+      <c r="BD5" s="69"/>
+      <c r="BE5" s="69"/>
+      <c r="BF5" s="69"/>
+      <c r="BG5" s="69"/>
+      <c r="BH5" s="69"/>
+      <c r="BI5" s="59"/>
+      <c r="BJ5" s="60"/>
+      <c r="BK5" s="71"/>
+      <c r="BL5" s="59"/>
+      <c r="BM5" s="60"/>
+      <c r="BN5" s="71"/>
+      <c r="BO5" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="BP5" s="34"/>
-      <c r="BQ5" s="34"/>
-      <c r="BR5" s="34"/>
-      <c r="BS5" s="34"/>
-      <c r="BT5" s="34"/>
-      <c r="BU5" s="34"/>
-      <c r="BV5" s="34"/>
-      <c r="BW5" s="34"/>
-      <c r="BX5" s="54"/>
-      <c r="BY5" s="54"/>
-      <c r="BZ5" s="54"/>
-      <c r="CA5" s="54"/>
-      <c r="CB5" s="54"/>
-      <c r="CC5" s="54"/>
-      <c r="CD5" s="58"/>
-      <c r="CE5" s="59"/>
-      <c r="CF5" s="60"/>
-      <c r="CG5" s="67"/>
-      <c r="CH5" s="68"/>
-      <c r="CI5" s="68"/>
-      <c r="CJ5" s="68"/>
-      <c r="CK5" s="68"/>
-      <c r="CL5" s="69"/>
-      <c r="CM5" s="70"/>
-      <c r="CN5" s="70"/>
-      <c r="CO5" s="70"/>
-      <c r="CP5" s="70"/>
-      <c r="CQ5" s="70"/>
-      <c r="CR5" s="70"/>
-      <c r="CS5" s="58"/>
-      <c r="CT5" s="59"/>
-      <c r="CU5" s="72"/>
-      <c r="CV5" s="58"/>
-      <c r="CW5" s="59"/>
-      <c r="CX5" s="72"/>
-      <c r="CY5" s="34" t="s">
+      <c r="BP5" s="84"/>
+      <c r="BQ5" s="84"/>
+      <c r="BR5" s="84"/>
+      <c r="BS5" s="84"/>
+      <c r="BT5" s="84"/>
+      <c r="BU5" s="84"/>
+      <c r="BV5" s="84"/>
+      <c r="BW5" s="84"/>
+      <c r="BX5" s="73"/>
+      <c r="BY5" s="73"/>
+      <c r="BZ5" s="73"/>
+      <c r="CA5" s="73"/>
+      <c r="CB5" s="73"/>
+      <c r="CC5" s="73"/>
+      <c r="CD5" s="59"/>
+      <c r="CE5" s="60"/>
+      <c r="CF5" s="61"/>
+      <c r="CG5" s="83"/>
+      <c r="CH5" s="67"/>
+      <c r="CI5" s="67"/>
+      <c r="CJ5" s="67"/>
+      <c r="CK5" s="67"/>
+      <c r="CL5" s="68"/>
+      <c r="CM5" s="69"/>
+      <c r="CN5" s="69"/>
+      <c r="CO5" s="69"/>
+      <c r="CP5" s="69"/>
+      <c r="CQ5" s="69"/>
+      <c r="CR5" s="69"/>
+      <c r="CS5" s="59"/>
+      <c r="CT5" s="60"/>
+      <c r="CU5" s="71"/>
+      <c r="CV5" s="59"/>
+      <c r="CW5" s="60"/>
+      <c r="CX5" s="71"/>
+      <c r="CY5" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="CZ5" s="34"/>
-      <c r="DA5" s="34"/>
-      <c r="DB5" s="34"/>
-      <c r="DC5" s="34"/>
-      <c r="DD5" s="34"/>
-      <c r="DE5" s="34"/>
-      <c r="DF5" s="34"/>
-      <c r="DG5" s="34"/>
-      <c r="DH5" s="54"/>
-      <c r="DI5" s="54"/>
-      <c r="DJ5" s="54"/>
-      <c r="DK5" s="54"/>
-      <c r="DL5" s="54"/>
-      <c r="DM5" s="54"/>
-      <c r="DN5" s="58"/>
-      <c r="DO5" s="59"/>
-      <c r="DP5" s="60"/>
-      <c r="DQ5" s="76" t="s">
+      <c r="CZ5" s="84"/>
+      <c r="DA5" s="84"/>
+      <c r="DB5" s="84"/>
+      <c r="DC5" s="84"/>
+      <c r="DD5" s="84"/>
+      <c r="DE5" s="84"/>
+      <c r="DF5" s="84"/>
+      <c r="DG5" s="84"/>
+      <c r="DH5" s="73"/>
+      <c r="DI5" s="73"/>
+      <c r="DJ5" s="73"/>
+      <c r="DK5" s="73"/>
+      <c r="DL5" s="73"/>
+      <c r="DM5" s="73"/>
+      <c r="DN5" s="59"/>
+      <c r="DO5" s="60"/>
+      <c r="DP5" s="61"/>
+      <c r="DQ5" s="105" t="s">
         <v>22</v>
       </c>
-      <c r="DR5" s="31" t="s">
+      <c r="DR5" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="DS5" s="45" t="s">
+      <c r="DS5" s="95" t="s">
         <v>479</v>
       </c>
-      <c r="DT5" s="46"/>
-      <c r="DU5" s="46"/>
-      <c r="DV5" s="47"/>
-      <c r="DW5" s="78" t="s">
+      <c r="DT5" s="96"/>
+      <c r="DU5" s="96"/>
+      <c r="DV5" s="97"/>
+      <c r="DW5" s="107" t="s">
         <v>24</v>
       </c>
-      <c r="DX5" s="79"/>
-      <c r="DY5" s="79"/>
-      <c r="DZ5" s="79"/>
-      <c r="EA5" s="79"/>
-      <c r="EB5" s="79"/>
-      <c r="EC5" s="79"/>
-      <c r="ED5" s="79"/>
-      <c r="EE5" s="79"/>
-      <c r="EF5" s="79"/>
-      <c r="EG5" s="79"/>
-      <c r="EH5" s="80"/>
-      <c r="EI5" s="31" t="s">
+      <c r="DX5" s="108"/>
+      <c r="DY5" s="108"/>
+      <c r="DZ5" s="108"/>
+      <c r="EA5" s="108"/>
+      <c r="EB5" s="108"/>
+      <c r="EC5" s="108"/>
+      <c r="ED5" s="108"/>
+      <c r="EE5" s="108"/>
+      <c r="EF5" s="108"/>
+      <c r="EG5" s="108"/>
+      <c r="EH5" s="109"/>
+      <c r="EI5" s="102" t="s">
         <v>25</v>
       </c>
-      <c r="EJ5" s="31" t="s">
+      <c r="EJ5" s="102" t="s">
         <v>23</v>
       </c>
-      <c r="EK5" s="45" t="s">
+      <c r="EK5" s="95" t="s">
         <v>480</v>
       </c>
-      <c r="EL5" s="46"/>
-      <c r="EM5" s="46"/>
-      <c r="EN5" s="47"/>
-      <c r="EO5" s="94" t="s">
+      <c r="EL5" s="96"/>
+      <c r="EM5" s="96"/>
+      <c r="EN5" s="97"/>
+      <c r="EO5" s="101" t="s">
         <v>21</v>
       </c>
-      <c r="EP5" s="94"/>
-      <c r="EQ5" s="94"/>
-      <c r="ER5" s="94"/>
-      <c r="ES5" s="94"/>
-      <c r="ET5" s="94"/>
-      <c r="EU5" s="94"/>
-      <c r="EV5" s="94"/>
-      <c r="EW5" s="94"/>
-      <c r="EX5" s="94"/>
-      <c r="EY5" s="94"/>
-      <c r="EZ5" s="94"/>
-      <c r="FA5" s="84"/>
-      <c r="FB5" s="85"/>
-      <c r="FC5" s="85"/>
-      <c r="FD5" s="85"/>
-      <c r="FE5" s="85"/>
-      <c r="FF5" s="86"/>
-      <c r="FG5" s="84"/>
-      <c r="FH5" s="85"/>
-      <c r="FI5" s="85"/>
-      <c r="FJ5" s="85"/>
-      <c r="FK5" s="85"/>
-      <c r="FL5" s="86"/>
-      <c r="FM5" s="24" t="s">
+      <c r="EP5" s="101"/>
+      <c r="EQ5" s="101"/>
+      <c r="ER5" s="101"/>
+      <c r="ES5" s="101"/>
+      <c r="ET5" s="101"/>
+      <c r="EU5" s="101"/>
+      <c r="EV5" s="101"/>
+      <c r="EW5" s="101"/>
+      <c r="EX5" s="101"/>
+      <c r="EY5" s="101"/>
+      <c r="EZ5" s="101"/>
+      <c r="FA5" s="92"/>
+      <c r="FB5" s="93"/>
+      <c r="FC5" s="93"/>
+      <c r="FD5" s="93"/>
+      <c r="FE5" s="93"/>
+      <c r="FF5" s="94"/>
+      <c r="FG5" s="92"/>
+      <c r="FH5" s="93"/>
+      <c r="FI5" s="93"/>
+      <c r="FJ5" s="93"/>
+      <c r="FK5" s="93"/>
+      <c r="FL5" s="94"/>
+      <c r="FM5" s="104" t="s">
         <v>26</v>
       </c>
-      <c r="FN5" s="24" t="s">
+      <c r="FN5" s="104" t="s">
         <v>27</v>
       </c>
-      <c r="FO5" s="45" t="s">
+      <c r="FO5" s="95" t="s">
         <v>28</v>
       </c>
-      <c r="FP5" s="46"/>
-      <c r="FQ5" s="46"/>
-      <c r="FR5" s="47"/>
-      <c r="FS5" s="26" t="s">
+      <c r="FP5" s="96"/>
+      <c r="FQ5" s="96"/>
+      <c r="FR5" s="97"/>
+      <c r="FS5" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="FT5" s="27"/>
-      <c r="FU5" s="27"/>
-      <c r="FV5" s="27"/>
-      <c r="FW5" s="27"/>
-      <c r="FX5" s="27"/>
-      <c r="FY5" s="27"/>
-      <c r="FZ5" s="27"/>
-      <c r="GA5" s="27"/>
-      <c r="GB5" s="27"/>
-      <c r="GC5" s="27"/>
-      <c r="GD5" s="27"/>
-      <c r="GE5" s="27"/>
-      <c r="GF5" s="27"/>
-      <c r="GG5" s="27"/>
-      <c r="GH5" s="27"/>
-      <c r="GI5" s="27"/>
-      <c r="GJ5" s="27"/>
-      <c r="GK5" s="89"/>
-      <c r="GL5" s="33"/>
-      <c r="GM5" s="34"/>
-      <c r="GN5" s="34"/>
-      <c r="GO5" s="34"/>
-      <c r="GP5" s="34"/>
-      <c r="GQ5" s="34"/>
-      <c r="GR5" s="34"/>
-      <c r="GS5" s="34"/>
-      <c r="GT5" s="34"/>
-      <c r="GU5" s="34"/>
-      <c r="GV5" s="34"/>
-      <c r="GW5" s="34"/>
-      <c r="GX5" s="34"/>
-      <c r="GY5" s="34"/>
-      <c r="GZ5" s="34"/>
-      <c r="HA5" s="34"/>
-      <c r="HB5" s="34"/>
+      <c r="FT5" s="75"/>
+      <c r="FU5" s="75"/>
+      <c r="FV5" s="75"/>
+      <c r="FW5" s="75"/>
+      <c r="FX5" s="75"/>
+      <c r="FY5" s="75"/>
+      <c r="FZ5" s="75"/>
+      <c r="GA5" s="75"/>
+      <c r="GB5" s="75"/>
+      <c r="GC5" s="75"/>
+      <c r="GD5" s="75"/>
+      <c r="GE5" s="75"/>
+      <c r="GF5" s="75"/>
+      <c r="GG5" s="75"/>
+      <c r="GH5" s="75"/>
+      <c r="GI5" s="75"/>
+      <c r="GJ5" s="75"/>
+      <c r="GK5" s="112"/>
+      <c r="GL5" s="80"/>
+      <c r="GM5" s="84"/>
+      <c r="GN5" s="84"/>
+      <c r="GO5" s="84"/>
+      <c r="GP5" s="84"/>
+      <c r="GQ5" s="84"/>
+      <c r="GR5" s="84"/>
+      <c r="GS5" s="84"/>
+      <c r="GT5" s="84"/>
+      <c r="GU5" s="84"/>
+      <c r="GV5" s="84"/>
+      <c r="GW5" s="84"/>
+      <c r="GX5" s="84"/>
+      <c r="GY5" s="84"/>
+      <c r="GZ5" s="84"/>
+      <c r="HA5" s="84"/>
+      <c r="HB5" s="84"/>
     </row>
     <row r="6" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="38"/>
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
       <c r="E6" s="12"/>
-      <c r="F6" s="38"/>
+      <c r="F6" s="43"/>
       <c r="G6" s="12"/>
-      <c r="H6" s="37" t="s">
+      <c r="H6" s="42" t="s">
         <v>29</v>
       </c>
-      <c r="I6" s="112" t="s">
+      <c r="I6" s="53" t="s">
         <v>30</v>
       </c>
-      <c r="J6" s="113"/>
-      <c r="K6" s="113"/>
-      <c r="L6" s="114"/>
-      <c r="M6" s="26" t="s">
+      <c r="J6" s="54"/>
+      <c r="K6" s="54"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="N6" s="27"/>
-      <c r="O6" s="28"/>
-      <c r="P6" s="26" t="s">
+      <c r="N6" s="75"/>
+      <c r="O6" s="76"/>
+      <c r="P6" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="28"/>
-      <c r="S6" s="51" t="s">
+      <c r="Q6" s="75"/>
+      <c r="R6" s="76"/>
+      <c r="S6" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="T6" s="52"/>
-      <c r="U6" s="53"/>
-      <c r="V6" s="51" t="s">
+      <c r="T6" s="78"/>
+      <c r="U6" s="79"/>
+      <c r="V6" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="W6" s="52"/>
-      <c r="X6" s="53"/>
-      <c r="Y6" s="61"/>
-      <c r="Z6" s="62"/>
-      <c r="AA6" s="73"/>
-      <c r="AB6" s="61"/>
-      <c r="AC6" s="62"/>
-      <c r="AD6" s="73"/>
-      <c r="AE6" s="33" t="s">
+      <c r="W6" s="78"/>
+      <c r="X6" s="79"/>
+      <c r="Y6" s="62"/>
+      <c r="Z6" s="63"/>
+      <c r="AA6" s="72"/>
+      <c r="AB6" s="62"/>
+      <c r="AC6" s="63"/>
+      <c r="AD6" s="72"/>
+      <c r="AE6" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="33"/>
-      <c r="AH6" s="34" t="s">
+      <c r="AF6" s="80"/>
+      <c r="AG6" s="80"/>
+      <c r="AH6" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="AI6" s="34"/>
-      <c r="AJ6" s="34"/>
-      <c r="AK6" s="33" t="s">
+      <c r="AI6" s="84"/>
+      <c r="AJ6" s="84"/>
+      <c r="AK6" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="AL6" s="33"/>
-      <c r="AM6" s="33"/>
-      <c r="AN6" s="34" t="s">
+      <c r="AL6" s="80"/>
+      <c r="AM6" s="80"/>
+      <c r="AN6" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="AO6" s="34"/>
-      <c r="AP6" s="34"/>
-      <c r="AQ6" s="34" t="s">
+      <c r="AO6" s="84"/>
+      <c r="AP6" s="84"/>
+      <c r="AQ6" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="AR6" s="34"/>
-      <c r="AS6" s="34"/>
-      <c r="AT6" s="61"/>
-      <c r="AU6" s="62"/>
-      <c r="AV6" s="63"/>
-      <c r="AW6" s="27" t="s">
+      <c r="AR6" s="84"/>
+      <c r="AS6" s="84"/>
+      <c r="AT6" s="62"/>
+      <c r="AU6" s="63"/>
+      <c r="AV6" s="64"/>
+      <c r="AW6" s="75" t="s">
         <v>31</v>
       </c>
-      <c r="AX6" s="27"/>
-      <c r="AY6" s="28"/>
-      <c r="AZ6" s="26" t="s">
+      <c r="AX6" s="75"/>
+      <c r="AY6" s="76"/>
+      <c r="AZ6" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="BA6" s="27"/>
-      <c r="BB6" s="28"/>
-      <c r="BC6" s="51" t="s">
+      <c r="BA6" s="75"/>
+      <c r="BB6" s="76"/>
+      <c r="BC6" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="BD6" s="52"/>
-      <c r="BE6" s="53"/>
-      <c r="BF6" s="51" t="s">
+      <c r="BD6" s="78"/>
+      <c r="BE6" s="79"/>
+      <c r="BF6" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="BG6" s="52"/>
-      <c r="BH6" s="53"/>
-      <c r="BI6" s="61"/>
-      <c r="BJ6" s="62"/>
-      <c r="BK6" s="73"/>
-      <c r="BL6" s="61"/>
-      <c r="BM6" s="62"/>
-      <c r="BN6" s="73"/>
-      <c r="BO6" s="33" t="s">
+      <c r="BG6" s="78"/>
+      <c r="BH6" s="79"/>
+      <c r="BI6" s="62"/>
+      <c r="BJ6" s="63"/>
+      <c r="BK6" s="72"/>
+      <c r="BL6" s="62"/>
+      <c r="BM6" s="63"/>
+      <c r="BN6" s="72"/>
+      <c r="BO6" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="BP6" s="33"/>
-      <c r="BQ6" s="33"/>
-      <c r="BR6" s="34" t="s">
+      <c r="BP6" s="80"/>
+      <c r="BQ6" s="80"/>
+      <c r="BR6" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="BS6" s="34"/>
-      <c r="BT6" s="34"/>
-      <c r="BU6" s="33" t="s">
+      <c r="BS6" s="84"/>
+      <c r="BT6" s="84"/>
+      <c r="BU6" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="BV6" s="33"/>
-      <c r="BW6" s="33"/>
-      <c r="BX6" s="34" t="s">
+      <c r="BV6" s="80"/>
+      <c r="BW6" s="80"/>
+      <c r="BX6" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="BY6" s="34"/>
-      <c r="BZ6" s="34"/>
-      <c r="CA6" s="34" t="s">
+      <c r="BY6" s="84"/>
+      <c r="BZ6" s="84"/>
+      <c r="CA6" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="CB6" s="34"/>
-      <c r="CC6" s="34"/>
-      <c r="CD6" s="61"/>
-      <c r="CE6" s="62"/>
-      <c r="CF6" s="63"/>
-      <c r="CG6" s="26" t="s">
+      <c r="CB6" s="84"/>
+      <c r="CC6" s="84"/>
+      <c r="CD6" s="62"/>
+      <c r="CE6" s="63"/>
+      <c r="CF6" s="64"/>
+      <c r="CG6" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="CH6" s="27"/>
-      <c r="CI6" s="28"/>
-      <c r="CJ6" s="26" t="s">
+      <c r="CH6" s="75"/>
+      <c r="CI6" s="76"/>
+      <c r="CJ6" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="CK6" s="27"/>
-      <c r="CL6" s="28"/>
-      <c r="CM6" s="51" t="s">
+      <c r="CK6" s="75"/>
+      <c r="CL6" s="76"/>
+      <c r="CM6" s="77" t="s">
         <v>33</v>
       </c>
-      <c r="CN6" s="52"/>
-      <c r="CO6" s="53"/>
-      <c r="CP6" s="51" t="s">
+      <c r="CN6" s="78"/>
+      <c r="CO6" s="79"/>
+      <c r="CP6" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="CQ6" s="52"/>
-      <c r="CR6" s="53"/>
-      <c r="CS6" s="61"/>
-      <c r="CT6" s="62"/>
-      <c r="CU6" s="73"/>
-      <c r="CV6" s="61"/>
-      <c r="CW6" s="62"/>
-      <c r="CX6" s="73"/>
-      <c r="CY6" s="33" t="s">
+      <c r="CQ6" s="78"/>
+      <c r="CR6" s="79"/>
+      <c r="CS6" s="62"/>
+      <c r="CT6" s="63"/>
+      <c r="CU6" s="72"/>
+      <c r="CV6" s="62"/>
+      <c r="CW6" s="63"/>
+      <c r="CX6" s="72"/>
+      <c r="CY6" s="80" t="s">
         <v>35</v>
       </c>
-      <c r="CZ6" s="33"/>
-      <c r="DA6" s="33"/>
-      <c r="DB6" s="34" t="s">
+      <c r="CZ6" s="80"/>
+      <c r="DA6" s="80"/>
+      <c r="DB6" s="84" t="s">
         <v>36</v>
       </c>
-      <c r="DC6" s="34"/>
-      <c r="DD6" s="34"/>
-      <c r="DE6" s="33" t="s">
+      <c r="DC6" s="84"/>
+      <c r="DD6" s="84"/>
+      <c r="DE6" s="80" t="s">
         <v>37</v>
       </c>
-      <c r="DF6" s="33"/>
-      <c r="DG6" s="33"/>
-      <c r="DH6" s="34" t="s">
+      <c r="DF6" s="80"/>
+      <c r="DG6" s="80"/>
+      <c r="DH6" s="84" t="s">
         <v>19</v>
       </c>
-      <c r="DI6" s="34"/>
-      <c r="DJ6" s="34"/>
-      <c r="DK6" s="34" t="s">
+      <c r="DI6" s="84"/>
+      <c r="DJ6" s="84"/>
+      <c r="DK6" s="84" t="s">
         <v>20</v>
       </c>
-      <c r="DL6" s="34"/>
-      <c r="DM6" s="34"/>
-      <c r="DN6" s="61"/>
-      <c r="DO6" s="62"/>
-      <c r="DP6" s="63"/>
-      <c r="DQ6" s="77"/>
-      <c r="DR6" s="32"/>
-      <c r="DS6" s="48"/>
-      <c r="DT6" s="49"/>
-      <c r="DU6" s="49"/>
-      <c r="DV6" s="50"/>
-      <c r="DW6" s="26" t="s">
+      <c r="DL6" s="84"/>
+      <c r="DM6" s="84"/>
+      <c r="DN6" s="62"/>
+      <c r="DO6" s="63"/>
+      <c r="DP6" s="64"/>
+      <c r="DQ6" s="106"/>
+      <c r="DR6" s="103"/>
+      <c r="DS6" s="98"/>
+      <c r="DT6" s="99"/>
+      <c r="DU6" s="99"/>
+      <c r="DV6" s="100"/>
+      <c r="DW6" s="74" t="s">
         <v>31</v>
       </c>
-      <c r="DX6" s="27"/>
-      <c r="DY6" s="27"/>
-      <c r="DZ6" s="27"/>
-      <c r="EA6" s="27"/>
-      <c r="EB6" s="28"/>
-      <c r="EC6" s="26" t="s">
+      <c r="DX6" s="75"/>
+      <c r="DY6" s="75"/>
+      <c r="DZ6" s="75"/>
+      <c r="EA6" s="75"/>
+      <c r="EB6" s="76"/>
+      <c r="EC6" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="ED6" s="27"/>
-      <c r="EE6" s="27"/>
-      <c r="EF6" s="27"/>
-      <c r="EG6" s="27"/>
-      <c r="EH6" s="28"/>
-      <c r="EI6" s="32"/>
-      <c r="EJ6" s="32"/>
-      <c r="EK6" s="48"/>
-      <c r="EL6" s="49"/>
-      <c r="EM6" s="49"/>
-      <c r="EN6" s="50"/>
-      <c r="EO6" s="45" t="s">
+      <c r="ED6" s="75"/>
+      <c r="EE6" s="75"/>
+      <c r="EF6" s="75"/>
+      <c r="EG6" s="75"/>
+      <c r="EH6" s="76"/>
+      <c r="EI6" s="103"/>
+      <c r="EJ6" s="103"/>
+      <c r="EK6" s="98"/>
+      <c r="EL6" s="99"/>
+      <c r="EM6" s="99"/>
+      <c r="EN6" s="100"/>
+      <c r="EO6" s="95" t="s">
         <v>33</v>
       </c>
-      <c r="EP6" s="46"/>
-      <c r="EQ6" s="46"/>
-      <c r="ER6" s="46"/>
-      <c r="ES6" s="46"/>
-      <c r="ET6" s="47"/>
-      <c r="EU6" s="34" t="s">
+      <c r="EP6" s="96"/>
+      <c r="EQ6" s="96"/>
+      <c r="ER6" s="96"/>
+      <c r="ES6" s="96"/>
+      <c r="ET6" s="97"/>
+      <c r="EU6" s="84" t="s">
         <v>34</v>
       </c>
-      <c r="EV6" s="34"/>
-      <c r="EW6" s="34"/>
-      <c r="EX6" s="34"/>
-      <c r="EY6" s="34"/>
-      <c r="EZ6" s="34"/>
-      <c r="FA6" s="33" t="s">
+      <c r="EV6" s="84"/>
+      <c r="EW6" s="84"/>
+      <c r="EX6" s="84"/>
+      <c r="EY6" s="84"/>
+      <c r="EZ6" s="84"/>
+      <c r="FA6" s="80" t="s">
         <v>38</v>
       </c>
-      <c r="FB6" s="33"/>
-      <c r="FC6" s="34" t="s">
+      <c r="FB6" s="80"/>
+      <c r="FC6" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="FD6" s="34"/>
-      <c r="FE6" s="34"/>
-      <c r="FF6" s="34"/>
-      <c r="FG6" s="33" t="s">
+      <c r="FD6" s="84"/>
+      <c r="FE6" s="84"/>
+      <c r="FF6" s="84"/>
+      <c r="FG6" s="80" t="s">
         <v>40</v>
       </c>
-      <c r="FH6" s="33"/>
-      <c r="FI6" s="34" t="s">
+      <c r="FH6" s="80"/>
+      <c r="FI6" s="84" t="s">
         <v>39</v>
       </c>
-      <c r="FJ6" s="34"/>
-      <c r="FK6" s="34"/>
-      <c r="FL6" s="34"/>
-      <c r="FM6" s="25"/>
-      <c r="FN6" s="25"/>
-      <c r="FO6" s="48"/>
-      <c r="FP6" s="49"/>
-      <c r="FQ6" s="49"/>
-      <c r="FR6" s="50"/>
-      <c r="FS6" s="26" t="s">
+      <c r="FJ6" s="84"/>
+      <c r="FK6" s="84"/>
+      <c r="FL6" s="84"/>
+      <c r="FM6" s="114"/>
+      <c r="FN6" s="114"/>
+      <c r="FO6" s="98"/>
+      <c r="FP6" s="99"/>
+      <c r="FQ6" s="99"/>
+      <c r="FR6" s="100"/>
+      <c r="FS6" s="74" t="s">
         <v>41</v>
       </c>
-      <c r="FT6" s="27"/>
-      <c r="FU6" s="27"/>
-      <c r="FV6" s="27"/>
-      <c r="FW6" s="27"/>
-      <c r="FX6" s="28"/>
-      <c r="FY6" s="26" t="s">
+      <c r="FT6" s="75"/>
+      <c r="FU6" s="75"/>
+      <c r="FV6" s="75"/>
+      <c r="FW6" s="75"/>
+      <c r="FX6" s="76"/>
+      <c r="FY6" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="FZ6" s="27"/>
-      <c r="GA6" s="27"/>
-      <c r="GB6" s="27"/>
-      <c r="GC6" s="27"/>
-      <c r="GD6" s="28"/>
-      <c r="GE6" s="26" t="s">
+      <c r="FZ6" s="75"/>
+      <c r="GA6" s="75"/>
+      <c r="GB6" s="75"/>
+      <c r="GC6" s="75"/>
+      <c r="GD6" s="76"/>
+      <c r="GE6" s="74" t="s">
         <v>37</v>
       </c>
-      <c r="GF6" s="27"/>
-      <c r="GG6" s="27"/>
-      <c r="GH6" s="27"/>
-      <c r="GI6" s="27"/>
-      <c r="GJ6" s="27"/>
-      <c r="GK6" s="89"/>
-      <c r="GL6" s="33"/>
-      <c r="GM6" s="34"/>
-      <c r="GN6" s="34"/>
-      <c r="GO6" s="34"/>
-      <c r="GP6" s="34"/>
-      <c r="GQ6" s="34"/>
-      <c r="GR6" s="34"/>
-      <c r="GS6" s="34"/>
-      <c r="GT6" s="34"/>
-      <c r="GU6" s="34"/>
-      <c r="GV6" s="34"/>
-      <c r="GW6" s="34"/>
-      <c r="GX6" s="34"/>
-      <c r="GY6" s="34"/>
-      <c r="GZ6" s="34"/>
-      <c r="HA6" s="34"/>
-      <c r="HB6" s="34"/>
+      <c r="GF6" s="75"/>
+      <c r="GG6" s="75"/>
+      <c r="GH6" s="75"/>
+      <c r="GI6" s="75"/>
+      <c r="GJ6" s="75"/>
+      <c r="GK6" s="112"/>
+      <c r="GL6" s="80"/>
+      <c r="GM6" s="84"/>
+      <c r="GN6" s="84"/>
+      <c r="GO6" s="84"/>
+      <c r="GP6" s="84"/>
+      <c r="GQ6" s="84"/>
+      <c r="GR6" s="84"/>
+      <c r="GS6" s="84"/>
+      <c r="GT6" s="84"/>
+      <c r="GU6" s="84"/>
+      <c r="GV6" s="84"/>
+      <c r="GW6" s="84"/>
+      <c r="GX6" s="84"/>
+      <c r="GY6" s="84"/>
+      <c r="GZ6" s="84"/>
+      <c r="HA6" s="84"/>
+      <c r="HB6" s="84"/>
     </row>
     <row r="7" spans="1:210" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="38"/>
-      <c r="B7" s="38"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="38"/>
+      <c r="A7" s="43"/>
+      <c r="B7" s="43"/>
+      <c r="C7" s="43"/>
+      <c r="D7" s="43"/>
       <c r="E7" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="F7" s="38"/>
+      <c r="F7" s="43"/>
       <c r="G7" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="H7" s="38"/>
-      <c r="I7" s="37" t="s">
+      <c r="H7" s="43"/>
+      <c r="I7" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="J7" s="42" t="s">
+      <c r="J7" s="119" t="s">
         <v>21</v>
       </c>
-      <c r="K7" s="43"/>
-      <c r="L7" s="44"/>
-      <c r="M7" s="33" t="s">
+      <c r="K7" s="120"/>
+      <c r="L7" s="121"/>
+      <c r="M7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="N7" s="34" t="s">
+      <c r="N7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="O7" s="31" t="s">
+      <c r="O7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="P7" s="33" t="s">
+      <c r="P7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="Q7" s="34" t="s">
+      <c r="Q7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="R7" s="31" t="s">
+      <c r="R7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="S7" s="33" t="s">
+      <c r="S7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="T7" s="34" t="s">
+      <c r="T7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="U7" s="31" t="s">
+      <c r="U7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="V7" s="33" t="s">
+      <c r="V7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="W7" s="34" t="s">
+      <c r="W7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="X7" s="31" t="s">
+      <c r="X7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="Y7" s="33" t="s">
+      <c r="Y7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="Z7" s="34" t="s">
+      <c r="Z7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AA7" s="31" t="s">
+      <c r="AA7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AB7" s="33" t="s">
+      <c r="AB7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AC7" s="34" t="s">
+      <c r="AC7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AD7" s="31" t="s">
+      <c r="AD7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AE7" s="33" t="s">
+      <c r="AE7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AF7" s="34" t="s">
+      <c r="AF7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AG7" s="31" t="s">
+      <c r="AG7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AH7" s="33" t="s">
+      <c r="AH7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AI7" s="34" t="s">
+      <c r="AI7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AJ7" s="31" t="s">
+      <c r="AJ7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AK7" s="33" t="s">
+      <c r="AK7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AL7" s="34" t="s">
+      <c r="AL7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AM7" s="31" t="s">
+      <c r="AM7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AN7" s="33" t="s">
+      <c r="AN7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AO7" s="34" t="s">
+      <c r="AO7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AP7" s="31" t="s">
+      <c r="AP7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AQ7" s="33" t="s">
+      <c r="AQ7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="AR7" s="34" t="s">
+      <c r="AR7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AS7" s="31" t="s">
+      <c r="AS7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AT7" s="34" t="s">
+      <c r="AT7" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="AU7" s="34" t="s">
+      <c r="AU7" s="84" t="s">
         <v>482</v>
       </c>
-      <c r="AV7" s="40" t="s">
+      <c r="AV7" s="122" t="s">
         <v>46</v>
       </c>
-      <c r="AW7" s="36" t="s">
+      <c r="AW7" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="AX7" s="34" t="s">
+      <c r="AX7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="AY7" s="31" t="s">
+      <c r="AY7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="AZ7" s="33" t="s">
+      <c r="AZ7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BA7" s="34" t="s">
+      <c r="BA7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BB7" s="31" t="s">
+      <c r="BB7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BC7" s="33" t="s">
+      <c r="BC7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BD7" s="34" t="s">
+      <c r="BD7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BE7" s="31" t="s">
+      <c r="BE7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BF7" s="33" t="s">
+      <c r="BF7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BG7" s="34" t="s">
+      <c r="BG7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BH7" s="31" t="s">
+      <c r="BH7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BI7" s="33" t="s">
+      <c r="BI7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BJ7" s="34" t="s">
+      <c r="BJ7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BK7" s="31" t="s">
+      <c r="BK7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BL7" s="33" t="s">
+      <c r="BL7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BM7" s="34" t="s">
+      <c r="BM7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BN7" s="31" t="s">
+      <c r="BN7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BO7" s="33" t="s">
+      <c r="BO7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BP7" s="34" t="s">
+      <c r="BP7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BQ7" s="31" t="s">
+      <c r="BQ7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BR7" s="33" t="s">
+      <c r="BR7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BS7" s="34" t="s">
+      <c r="BS7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BT7" s="31" t="s">
+      <c r="BT7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BU7" s="33" t="s">
+      <c r="BU7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BV7" s="34" t="s">
+      <c r="BV7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BW7" s="31" t="s">
+      <c r="BW7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="BX7" s="33" t="s">
+      <c r="BX7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="BY7" s="34" t="s">
+      <c r="BY7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="BZ7" s="31" t="s">
+      <c r="BZ7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CA7" s="33" t="s">
+      <c r="CA7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CB7" s="34" t="s">
+      <c r="CB7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="CC7" s="31" t="s">
+      <c r="CC7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CD7" s="34" t="s">
+      <c r="CD7" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="CE7" s="34" t="s">
+      <c r="CE7" s="84" t="s">
         <v>482</v>
       </c>
-      <c r="CF7" s="74" t="s">
+      <c r="CF7" s="117" t="s">
         <v>46</v>
       </c>
-      <c r="CG7" s="36" t="s">
+      <c r="CG7" s="116" t="s">
         <v>45</v>
       </c>
-      <c r="CH7" s="34" t="s">
+      <c r="CH7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="CI7" s="31" t="s">
+      <c r="CI7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CJ7" s="33" t="s">
+      <c r="CJ7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CK7" s="34" t="s">
+      <c r="CK7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="CL7" s="31" t="s">
+      <c r="CL7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CM7" s="33" t="s">
+      <c r="CM7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CN7" s="34" t="s">
+      <c r="CN7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="CO7" s="31" t="s">
+      <c r="CO7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CP7" s="33" t="s">
+      <c r="CP7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CQ7" s="34" t="s">
+      <c r="CQ7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="CR7" s="31" t="s">
+      <c r="CR7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CS7" s="33" t="s">
+      <c r="CS7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CT7" s="34" t="s">
+      <c r="CT7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="CU7" s="31" t="s">
+      <c r="CU7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CV7" s="33" t="s">
+      <c r="CV7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CW7" s="34" t="s">
+      <c r="CW7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="CX7" s="31" t="s">
+      <c r="CX7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="CY7" s="33" t="s">
+      <c r="CY7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="CZ7" s="34" t="s">
+      <c r="CZ7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="DA7" s="31" t="s">
+      <c r="DA7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="DB7" s="33" t="s">
+      <c r="DB7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DC7" s="34" t="s">
+      <c r="DC7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="DD7" s="31" t="s">
+      <c r="DD7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="DE7" s="33" t="s">
+      <c r="DE7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DF7" s="34" t="s">
+      <c r="DF7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="DG7" s="31" t="s">
+      <c r="DG7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="DH7" s="33" t="s">
+      <c r="DH7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DI7" s="34" t="s">
+      <c r="DI7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="DJ7" s="31" t="s">
+      <c r="DJ7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="DK7" s="33" t="s">
+      <c r="DK7" s="80" t="s">
         <v>45</v>
       </c>
-      <c r="DL7" s="34" t="s">
+      <c r="DL7" s="84" t="s">
         <v>481</v>
       </c>
-      <c r="DM7" s="31" t="s">
+      <c r="DM7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="DN7" s="34" t="s">
+      <c r="DN7" s="84" t="s">
         <v>47</v>
       </c>
-      <c r="DO7" s="34" t="s">
+      <c r="DO7" s="84" t="s">
         <v>482</v>
       </c>
-      <c r="DP7" s="31" t="s">
+      <c r="DP7" s="102" t="s">
         <v>46</v>
       </c>
-      <c r="DQ7" s="77"/>
-      <c r="DR7" s="32"/>
-      <c r="DS7" s="51"/>
-      <c r="DT7" s="52"/>
-      <c r="DU7" s="52"/>
-      <c r="DV7" s="53"/>
-      <c r="DW7" s="26" t="s">
+      <c r="DQ7" s="106"/>
+      <c r="DR7" s="103"/>
+      <c r="DS7" s="77"/>
+      <c r="DT7" s="78"/>
+      <c r="DU7" s="78"/>
+      <c r="DV7" s="79"/>
+      <c r="DW7" s="74" t="s">
         <v>48</v>
       </c>
-      <c r="DX7" s="28"/>
-      <c r="DY7" s="26" t="s">
+      <c r="DX7" s="76"/>
+      <c r="DY7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="DZ7" s="27"/>
-      <c r="EA7" s="27"/>
-      <c r="EB7" s="28"/>
-      <c r="EC7" s="26" t="s">
+      <c r="DZ7" s="75"/>
+      <c r="EA7" s="75"/>
+      <c r="EB7" s="76"/>
+      <c r="EC7" s="74" t="s">
         <v>49</v>
       </c>
-      <c r="ED7" s="28"/>
-      <c r="EE7" s="26" t="s">
+      <c r="ED7" s="76"/>
+      <c r="EE7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="EF7" s="27"/>
-      <c r="EG7" s="27"/>
-      <c r="EH7" s="28"/>
-      <c r="EI7" s="32"/>
-      <c r="EJ7" s="32"/>
-      <c r="EK7" s="51"/>
-      <c r="EL7" s="52"/>
-      <c r="EM7" s="52"/>
-      <c r="EN7" s="53"/>
-      <c r="EO7" s="26" t="s">
+      <c r="EF7" s="75"/>
+      <c r="EG7" s="75"/>
+      <c r="EH7" s="76"/>
+      <c r="EI7" s="103"/>
+      <c r="EJ7" s="103"/>
+      <c r="EK7" s="77"/>
+      <c r="EL7" s="78"/>
+      <c r="EM7" s="78"/>
+      <c r="EN7" s="79"/>
+      <c r="EO7" s="74" t="s">
         <v>50</v>
       </c>
-      <c r="EP7" s="28"/>
-      <c r="EQ7" s="26" t="s">
+      <c r="EP7" s="76"/>
+      <c r="EQ7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="ER7" s="27"/>
-      <c r="ES7" s="27"/>
-      <c r="ET7" s="28"/>
-      <c r="EU7" s="34" t="s">
+      <c r="ER7" s="75"/>
+      <c r="ES7" s="75"/>
+      <c r="ET7" s="76"/>
+      <c r="EU7" s="84" t="s">
         <v>50</v>
       </c>
-      <c r="EV7" s="34"/>
-      <c r="EW7" s="26" t="s">
+      <c r="EV7" s="84"/>
+      <c r="EW7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="EX7" s="27"/>
-      <c r="EY7" s="27"/>
-      <c r="EZ7" s="28"/>
-      <c r="FA7" s="33"/>
-      <c r="FB7" s="33"/>
-      <c r="FC7" s="34"/>
-      <c r="FD7" s="34"/>
-      <c r="FE7" s="34"/>
-      <c r="FF7" s="34"/>
-      <c r="FG7" s="33"/>
-      <c r="FH7" s="33"/>
-      <c r="FI7" s="34"/>
-      <c r="FJ7" s="34"/>
-      <c r="FK7" s="34"/>
-      <c r="FL7" s="34"/>
-      <c r="FM7" s="25"/>
-      <c r="FN7" s="25"/>
-      <c r="FO7" s="51"/>
-      <c r="FP7" s="52"/>
-      <c r="FQ7" s="52"/>
-      <c r="FR7" s="53"/>
-      <c r="FS7" s="35" t="s">
+      <c r="EX7" s="75"/>
+      <c r="EY7" s="75"/>
+      <c r="EZ7" s="76"/>
+      <c r="FA7" s="80"/>
+      <c r="FB7" s="80"/>
+      <c r="FC7" s="84"/>
+      <c r="FD7" s="84"/>
+      <c r="FE7" s="84"/>
+      <c r="FF7" s="84"/>
+      <c r="FG7" s="80"/>
+      <c r="FH7" s="80"/>
+      <c r="FI7" s="84"/>
+      <c r="FJ7" s="84"/>
+      <c r="FK7" s="84"/>
+      <c r="FL7" s="84"/>
+      <c r="FM7" s="114"/>
+      <c r="FN7" s="114"/>
+      <c r="FO7" s="77"/>
+      <c r="FP7" s="78"/>
+      <c r="FQ7" s="78"/>
+      <c r="FR7" s="79"/>
+      <c r="FS7" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="FT7" s="36"/>
-      <c r="FU7" s="26" t="s">
+      <c r="FT7" s="116"/>
+      <c r="FU7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="FV7" s="27"/>
-      <c r="FW7" s="27"/>
-      <c r="FX7" s="28"/>
-      <c r="FY7" s="35" t="s">
+      <c r="FV7" s="75"/>
+      <c r="FW7" s="75"/>
+      <c r="FX7" s="76"/>
+      <c r="FY7" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="FZ7" s="36"/>
-      <c r="GA7" s="26" t="s">
+      <c r="FZ7" s="116"/>
+      <c r="GA7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="GB7" s="27"/>
-      <c r="GC7" s="27"/>
-      <c r="GD7" s="28"/>
-      <c r="GE7" s="35" t="s">
+      <c r="GB7" s="75"/>
+      <c r="GC7" s="75"/>
+      <c r="GD7" s="76"/>
+      <c r="GE7" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="GF7" s="36"/>
-      <c r="GG7" s="26" t="s">
+      <c r="GF7" s="116"/>
+      <c r="GG7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="GH7" s="27"/>
-      <c r="GI7" s="27"/>
-      <c r="GJ7" s="27"/>
-      <c r="GK7" s="89"/>
-      <c r="GL7" s="33"/>
-      <c r="GM7" s="34"/>
-      <c r="GN7" s="34"/>
-      <c r="GO7" s="34"/>
-      <c r="GP7" s="34"/>
-      <c r="GQ7" s="39" t="s">
+      <c r="GH7" s="75"/>
+      <c r="GI7" s="75"/>
+      <c r="GJ7" s="75"/>
+      <c r="GK7" s="112"/>
+      <c r="GL7" s="80"/>
+      <c r="GM7" s="84"/>
+      <c r="GN7" s="84"/>
+      <c r="GO7" s="84"/>
+      <c r="GP7" s="84"/>
+      <c r="GQ7" s="125" t="s">
         <v>50</v>
       </c>
-      <c r="GR7" s="36"/>
-      <c r="GS7" s="26" t="s">
+      <c r="GR7" s="116"/>
+      <c r="GS7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="GT7" s="27"/>
-      <c r="GU7" s="27"/>
-      <c r="GV7" s="28"/>
-      <c r="GW7" s="35" t="s">
+      <c r="GT7" s="75"/>
+      <c r="GU7" s="75"/>
+      <c r="GV7" s="76"/>
+      <c r="GW7" s="115" t="s">
         <v>50</v>
       </c>
-      <c r="GX7" s="36"/>
-      <c r="GY7" s="26" t="s">
+      <c r="GX7" s="116"/>
+      <c r="GY7" s="74" t="s">
         <v>39</v>
       </c>
-      <c r="GZ7" s="27"/>
-      <c r="HA7" s="27"/>
-      <c r="HB7" s="28"/>
+      <c r="GZ7" s="75"/>
+      <c r="HA7" s="75"/>
+      <c r="HB7" s="76"/>
     </row>
     <row r="8" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="38"/>
-      <c r="B8" s="38"/>
-      <c r="C8" s="38"/>
-      <c r="D8" s="38"/>
+      <c r="A8" s="43"/>
+      <c r="B8" s="43"/>
+      <c r="C8" s="43"/>
+      <c r="D8" s="43"/>
       <c r="E8" s="12"/>
-      <c r="F8" s="38"/>
+      <c r="F8" s="43"/>
       <c r="G8" s="12"/>
-      <c r="H8" s="38"/>
-      <c r="I8" s="38"/>
-      <c r="J8" s="37" t="s">
+      <c r="H8" s="43"/>
+      <c r="I8" s="43"/>
+      <c r="J8" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="K8" s="37" t="s">
+      <c r="K8" s="42" t="s">
         <v>52</v>
       </c>
-      <c r="L8" s="37" t="s">
+      <c r="L8" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="M8" s="33"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="32"/>
-      <c r="P8" s="33"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="32"/>
-      <c r="S8" s="33"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="32"/>
-      <c r="V8" s="33"/>
-      <c r="W8" s="34"/>
-      <c r="X8" s="32"/>
-      <c r="Y8" s="33"/>
-      <c r="Z8" s="34"/>
-      <c r="AA8" s="32"/>
-      <c r="AB8" s="33"/>
-      <c r="AC8" s="34"/>
-      <c r="AD8" s="32"/>
-      <c r="AE8" s="33"/>
-      <c r="AF8" s="34"/>
-      <c r="AG8" s="32"/>
-      <c r="AH8" s="33"/>
-      <c r="AI8" s="34"/>
-      <c r="AJ8" s="32"/>
-      <c r="AK8" s="33"/>
-      <c r="AL8" s="34"/>
-      <c r="AM8" s="32"/>
-      <c r="AN8" s="33"/>
-      <c r="AO8" s="34"/>
-      <c r="AP8" s="32"/>
-      <c r="AQ8" s="33"/>
-      <c r="AR8" s="34"/>
-      <c r="AS8" s="32"/>
-      <c r="AT8" s="34"/>
-      <c r="AU8" s="34"/>
-      <c r="AV8" s="41"/>
-      <c r="AW8" s="36"/>
-      <c r="AX8" s="34"/>
-      <c r="AY8" s="32"/>
-      <c r="AZ8" s="33"/>
-      <c r="BA8" s="34"/>
-      <c r="BB8" s="32"/>
-      <c r="BC8" s="33"/>
-      <c r="BD8" s="34"/>
-      <c r="BE8" s="32"/>
-      <c r="BF8" s="33"/>
-      <c r="BG8" s="34"/>
-      <c r="BH8" s="32"/>
-      <c r="BI8" s="33"/>
-      <c r="BJ8" s="34"/>
-      <c r="BK8" s="32"/>
-      <c r="BL8" s="33"/>
-      <c r="BM8" s="34"/>
-      <c r="BN8" s="32"/>
-      <c r="BO8" s="33"/>
-      <c r="BP8" s="34"/>
-      <c r="BQ8" s="32"/>
-      <c r="BR8" s="33"/>
-      <c r="BS8" s="34"/>
-      <c r="BT8" s="32"/>
-      <c r="BU8" s="33"/>
-      <c r="BV8" s="34"/>
-      <c r="BW8" s="32"/>
-      <c r="BX8" s="33"/>
-      <c r="BY8" s="34"/>
-      <c r="BZ8" s="32"/>
-      <c r="CA8" s="33"/>
-      <c r="CB8" s="34"/>
-      <c r="CC8" s="32"/>
-      <c r="CD8" s="34"/>
-      <c r="CE8" s="34"/>
-      <c r="CF8" s="75"/>
-      <c r="CG8" s="36"/>
-      <c r="CH8" s="34"/>
-      <c r="CI8" s="32"/>
-      <c r="CJ8" s="33"/>
-      <c r="CK8" s="34"/>
-      <c r="CL8" s="32"/>
-      <c r="CM8" s="33"/>
-      <c r="CN8" s="34"/>
-      <c r="CO8" s="32"/>
-      <c r="CP8" s="33"/>
-      <c r="CQ8" s="34"/>
-      <c r="CR8" s="32"/>
-      <c r="CS8" s="33"/>
-      <c r="CT8" s="34"/>
-      <c r="CU8" s="32"/>
-      <c r="CV8" s="33"/>
-      <c r="CW8" s="34"/>
-      <c r="CX8" s="32"/>
-      <c r="CY8" s="33"/>
-      <c r="CZ8" s="34"/>
-      <c r="DA8" s="32"/>
-      <c r="DB8" s="33"/>
-      <c r="DC8" s="34"/>
-      <c r="DD8" s="32"/>
-      <c r="DE8" s="33"/>
-      <c r="DF8" s="34"/>
-      <c r="DG8" s="32"/>
-      <c r="DH8" s="33"/>
-      <c r="DI8" s="34"/>
-      <c r="DJ8" s="32"/>
-      <c r="DK8" s="33"/>
-      <c r="DL8" s="34"/>
-      <c r="DM8" s="32"/>
-      <c r="DN8" s="34"/>
-      <c r="DO8" s="34"/>
-      <c r="DP8" s="32"/>
-      <c r="DQ8" s="77"/>
-      <c r="DR8" s="32"/>
-      <c r="DS8" s="24" t="s">
+      <c r="M8" s="80"/>
+      <c r="N8" s="84"/>
+      <c r="O8" s="103"/>
+      <c r="P8" s="80"/>
+      <c r="Q8" s="84"/>
+      <c r="R8" s="103"/>
+      <c r="S8" s="80"/>
+      <c r="T8" s="84"/>
+      <c r="U8" s="103"/>
+      <c r="V8" s="80"/>
+      <c r="W8" s="84"/>
+      <c r="X8" s="103"/>
+      <c r="Y8" s="80"/>
+      <c r="Z8" s="84"/>
+      <c r="AA8" s="103"/>
+      <c r="AB8" s="80"/>
+      <c r="AC8" s="84"/>
+      <c r="AD8" s="103"/>
+      <c r="AE8" s="80"/>
+      <c r="AF8" s="84"/>
+      <c r="AG8" s="103"/>
+      <c r="AH8" s="80"/>
+      <c r="AI8" s="84"/>
+      <c r="AJ8" s="103"/>
+      <c r="AK8" s="80"/>
+      <c r="AL8" s="84"/>
+      <c r="AM8" s="103"/>
+      <c r="AN8" s="80"/>
+      <c r="AO8" s="84"/>
+      <c r="AP8" s="103"/>
+      <c r="AQ8" s="80"/>
+      <c r="AR8" s="84"/>
+      <c r="AS8" s="103"/>
+      <c r="AT8" s="84"/>
+      <c r="AU8" s="84"/>
+      <c r="AV8" s="123"/>
+      <c r="AW8" s="116"/>
+      <c r="AX8" s="84"/>
+      <c r="AY8" s="103"/>
+      <c r="AZ8" s="80"/>
+      <c r="BA8" s="84"/>
+      <c r="BB8" s="103"/>
+      <c r="BC8" s="80"/>
+      <c r="BD8" s="84"/>
+      <c r="BE8" s="103"/>
+      <c r="BF8" s="80"/>
+      <c r="BG8" s="84"/>
+      <c r="BH8" s="103"/>
+      <c r="BI8" s="80"/>
+      <c r="BJ8" s="84"/>
+      <c r="BK8" s="103"/>
+      <c r="BL8" s="80"/>
+      <c r="BM8" s="84"/>
+      <c r="BN8" s="103"/>
+      <c r="BO8" s="80"/>
+      <c r="BP8" s="84"/>
+      <c r="BQ8" s="103"/>
+      <c r="BR8" s="80"/>
+      <c r="BS8" s="84"/>
+      <c r="BT8" s="103"/>
+      <c r="BU8" s="80"/>
+      <c r="BV8" s="84"/>
+      <c r="BW8" s="103"/>
+      <c r="BX8" s="80"/>
+      <c r="BY8" s="84"/>
+      <c r="BZ8" s="103"/>
+      <c r="CA8" s="80"/>
+      <c r="CB8" s="84"/>
+      <c r="CC8" s="103"/>
+      <c r="CD8" s="84"/>
+      <c r="CE8" s="84"/>
+      <c r="CF8" s="118"/>
+      <c r="CG8" s="116"/>
+      <c r="CH8" s="84"/>
+      <c r="CI8" s="103"/>
+      <c r="CJ8" s="80"/>
+      <c r="CK8" s="84"/>
+      <c r="CL8" s="103"/>
+      <c r="CM8" s="80"/>
+      <c r="CN8" s="84"/>
+      <c r="CO8" s="103"/>
+      <c r="CP8" s="80"/>
+      <c r="CQ8" s="84"/>
+      <c r="CR8" s="103"/>
+      <c r="CS8" s="80"/>
+      <c r="CT8" s="84"/>
+      <c r="CU8" s="103"/>
+      <c r="CV8" s="80"/>
+      <c r="CW8" s="84"/>
+      <c r="CX8" s="103"/>
+      <c r="CY8" s="80"/>
+      <c r="CZ8" s="84"/>
+      <c r="DA8" s="103"/>
+      <c r="DB8" s="80"/>
+      <c r="DC8" s="84"/>
+      <c r="DD8" s="103"/>
+      <c r="DE8" s="80"/>
+      <c r="DF8" s="84"/>
+      <c r="DG8" s="103"/>
+      <c r="DH8" s="80"/>
+      <c r="DI8" s="84"/>
+      <c r="DJ8" s="103"/>
+      <c r="DK8" s="80"/>
+      <c r="DL8" s="84"/>
+      <c r="DM8" s="103"/>
+      <c r="DN8" s="84"/>
+      <c r="DO8" s="84"/>
+      <c r="DP8" s="103"/>
+      <c r="DQ8" s="106"/>
+      <c r="DR8" s="103"/>
+      <c r="DS8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="DT8" s="26" t="s">
+      <c r="DT8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="DU8" s="27"/>
-      <c r="DV8" s="28"/>
-      <c r="DW8" s="31" t="s">
+      <c r="DU8" s="75"/>
+      <c r="DV8" s="76"/>
+      <c r="DW8" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="DX8" s="31" t="s">
+      <c r="DX8" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="DY8" s="24" t="s">
+      <c r="DY8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="DZ8" s="26" t="s">
+      <c r="DZ8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="EA8" s="27"/>
-      <c r="EB8" s="28"/>
-      <c r="EC8" s="31" t="s">
+      <c r="EA8" s="75"/>
+      <c r="EB8" s="76"/>
+      <c r="EC8" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="ED8" s="31" t="s">
+      <c r="ED8" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="EE8" s="24" t="s">
+      <c r="EE8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="EF8" s="26" t="s">
+      <c r="EF8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="EG8" s="27"/>
-      <c r="EH8" s="28"/>
-      <c r="EI8" s="32"/>
-      <c r="EJ8" s="32"/>
-      <c r="EK8" s="24" t="s">
+      <c r="EG8" s="75"/>
+      <c r="EH8" s="76"/>
+      <c r="EI8" s="103"/>
+      <c r="EJ8" s="103"/>
+      <c r="EK8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="EL8" s="26" t="s">
+      <c r="EL8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="EM8" s="27"/>
-      <c r="EN8" s="28"/>
-      <c r="EO8" s="31" t="s">
+      <c r="EM8" s="75"/>
+      <c r="EN8" s="76"/>
+      <c r="EO8" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="EP8" s="31" t="s">
+      <c r="EP8" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="EQ8" s="24" t="s">
+      <c r="EQ8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="ER8" s="26" t="s">
+      <c r="ER8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="ES8" s="27"/>
-      <c r="ET8" s="28"/>
-      <c r="EU8" s="31" t="s">
+      <c r="ES8" s="75"/>
+      <c r="ET8" s="76"/>
+      <c r="EU8" s="102" t="s">
         <v>54</v>
       </c>
-      <c r="EV8" s="31" t="s">
+      <c r="EV8" s="102" t="s">
         <v>55</v>
       </c>
-      <c r="EW8" s="24" t="s">
+      <c r="EW8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="EX8" s="26" t="s">
+      <c r="EX8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="EY8" s="27"/>
-      <c r="EZ8" s="28"/>
-      <c r="FA8" s="24" t="s">
+      <c r="EY8" s="75"/>
+      <c r="EZ8" s="76"/>
+      <c r="FA8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FB8" s="24" t="s">
+      <c r="FB8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="FC8" s="24" t="s">
+      <c r="FC8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FD8" s="26" t="s">
+      <c r="FD8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="FE8" s="27"/>
-      <c r="FF8" s="28"/>
-      <c r="FG8" s="24" t="s">
+      <c r="FE8" s="75"/>
+      <c r="FF8" s="76"/>
+      <c r="FG8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FH8" s="24" t="s">
+      <c r="FH8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="FI8" s="24" t="s">
+      <c r="FI8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FJ8" s="26" t="s">
+      <c r="FJ8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="FK8" s="27"/>
-      <c r="FL8" s="28"/>
-      <c r="FM8" s="25"/>
-      <c r="FN8" s="25"/>
-      <c r="FO8" s="24" t="s">
+      <c r="FK8" s="75"/>
+      <c r="FL8" s="76"/>
+      <c r="FM8" s="114"/>
+      <c r="FN8" s="114"/>
+      <c r="FO8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FP8" s="26" t="s">
+      <c r="FP8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="FQ8" s="27"/>
-      <c r="FR8" s="28"/>
-      <c r="FS8" s="24" t="s">
+      <c r="FQ8" s="75"/>
+      <c r="FR8" s="76"/>
+      <c r="FS8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FT8" s="24" t="s">
+      <c r="FT8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="FU8" s="24" t="s">
+      <c r="FU8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FV8" s="26" t="s">
+      <c r="FV8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="FW8" s="27"/>
-      <c r="FX8" s="28"/>
-      <c r="FY8" s="24" t="s">
+      <c r="FW8" s="75"/>
+      <c r="FX8" s="76"/>
+      <c r="FY8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="FZ8" s="24" t="s">
+      <c r="FZ8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="GA8" s="24" t="s">
+      <c r="GA8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="GB8" s="26" t="s">
+      <c r="GB8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="GC8" s="27"/>
-      <c r="GD8" s="28"/>
-      <c r="GE8" s="24" t="s">
+      <c r="GC8" s="75"/>
+      <c r="GD8" s="76"/>
+      <c r="GE8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="GF8" s="24" t="s">
+      <c r="GF8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="GG8" s="24" t="s">
+      <c r="GG8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="GH8" s="26" t="s">
+      <c r="GH8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="GI8" s="27"/>
-      <c r="GJ8" s="27"/>
-      <c r="GK8" s="89"/>
-      <c r="GL8" s="33"/>
-      <c r="GM8" s="29" t="s">
+      <c r="GI8" s="75"/>
+      <c r="GJ8" s="75"/>
+      <c r="GK8" s="112"/>
+      <c r="GL8" s="80"/>
+      <c r="GM8" s="124" t="s">
         <v>54</v>
       </c>
-      <c r="GN8" s="26" t="s">
+      <c r="GN8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="GO8" s="27"/>
-      <c r="GP8" s="28"/>
-      <c r="GQ8" s="24" t="s">
+      <c r="GO8" s="75"/>
+      <c r="GP8" s="76"/>
+      <c r="GQ8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="GR8" s="24" t="s">
+      <c r="GR8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="GS8" s="24" t="s">
+      <c r="GS8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="GT8" s="26" t="s">
+      <c r="GT8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="GU8" s="27"/>
-      <c r="GV8" s="28"/>
-      <c r="GW8" s="24" t="s">
+      <c r="GU8" s="75"/>
+      <c r="GV8" s="76"/>
+      <c r="GW8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="GX8" s="24" t="s">
+      <c r="GX8" s="104" t="s">
         <v>55</v>
       </c>
-      <c r="GY8" s="24" t="s">
+      <c r="GY8" s="104" t="s">
         <v>54</v>
       </c>
-      <c r="GZ8" s="26" t="s">
+      <c r="GZ8" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="HA8" s="27"/>
-      <c r="HB8" s="28"/>
+      <c r="HA8" s="75"/>
+      <c r="HB8" s="76"/>
     </row>
     <row r="9" spans="1:210" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="38"/>
-      <c r="B9" s="38"/>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
+      <c r="A9" s="43"/>
+      <c r="B9" s="43"/>
+      <c r="C9" s="43"/>
+      <c r="D9" s="43"/>
       <c r="E9" s="14"/>
-      <c r="F9" s="38"/>
+      <c r="F9" s="43"/>
       <c r="G9" s="14"/>
-      <c r="H9" s="38"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="38"/>
-      <c r="K9" s="38"/>
-      <c r="L9" s="38"/>
-      <c r="M9" s="24"/>
-      <c r="N9" s="31"/>
-      <c r="O9" s="32"/>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="31"/>
-      <c r="R9" s="32"/>
-      <c r="S9" s="24"/>
-      <c r="T9" s="31"/>
-      <c r="U9" s="32"/>
-      <c r="V9" s="24"/>
-      <c r="W9" s="31"/>
-      <c r="X9" s="32"/>
-      <c r="Y9" s="24"/>
-      <c r="Z9" s="31"/>
-      <c r="AA9" s="32"/>
-      <c r="AB9" s="24"/>
-      <c r="AC9" s="31"/>
-      <c r="AD9" s="32"/>
-      <c r="AE9" s="24"/>
-      <c r="AF9" s="31"/>
-      <c r="AG9" s="32"/>
-      <c r="AH9" s="24"/>
-      <c r="AI9" s="31"/>
-      <c r="AJ9" s="32"/>
-      <c r="AK9" s="24"/>
-      <c r="AL9" s="31"/>
-      <c r="AM9" s="32"/>
-      <c r="AN9" s="24"/>
-      <c r="AO9" s="31"/>
-      <c r="AP9" s="32"/>
-      <c r="AQ9" s="24"/>
-      <c r="AR9" s="31"/>
-      <c r="AS9" s="32"/>
-      <c r="AT9" s="31"/>
-      <c r="AU9" s="31"/>
-      <c r="AV9" s="41"/>
-      <c r="AW9" s="29"/>
-      <c r="AX9" s="31"/>
-      <c r="AY9" s="32"/>
-      <c r="AZ9" s="24"/>
-      <c r="BA9" s="31"/>
-      <c r="BB9" s="32"/>
-      <c r="BC9" s="24"/>
-      <c r="BD9" s="31"/>
-      <c r="BE9" s="32"/>
-      <c r="BF9" s="24"/>
-      <c r="BG9" s="31"/>
-      <c r="BH9" s="32"/>
-      <c r="BI9" s="24"/>
-      <c r="BJ9" s="31"/>
-      <c r="BK9" s="32"/>
-      <c r="BL9" s="24"/>
-      <c r="BM9" s="31"/>
-      <c r="BN9" s="32"/>
-      <c r="BO9" s="24"/>
-      <c r="BP9" s="31"/>
-      <c r="BQ9" s="32"/>
-      <c r="BR9" s="24"/>
-      <c r="BS9" s="31"/>
-      <c r="BT9" s="32"/>
-      <c r="BU9" s="24"/>
-      <c r="BV9" s="31"/>
-      <c r="BW9" s="32"/>
-      <c r="BX9" s="24"/>
-      <c r="BY9" s="31"/>
-      <c r="BZ9" s="32"/>
-      <c r="CA9" s="24"/>
-      <c r="CB9" s="31"/>
-      <c r="CC9" s="32"/>
-      <c r="CD9" s="31"/>
-      <c r="CE9" s="31"/>
-      <c r="CF9" s="75"/>
-      <c r="CG9" s="29"/>
-      <c r="CH9" s="31"/>
-      <c r="CI9" s="32"/>
-      <c r="CJ9" s="24"/>
-      <c r="CK9" s="31"/>
-      <c r="CL9" s="32"/>
-      <c r="CM9" s="24"/>
-      <c r="CN9" s="31"/>
-      <c r="CO9" s="32"/>
-      <c r="CP9" s="24"/>
-      <c r="CQ9" s="31"/>
-      <c r="CR9" s="32"/>
-      <c r="CS9" s="24"/>
-      <c r="CT9" s="31"/>
-      <c r="CU9" s="32"/>
-      <c r="CV9" s="24"/>
-      <c r="CW9" s="31"/>
-      <c r="CX9" s="32"/>
-      <c r="CY9" s="24"/>
-      <c r="CZ9" s="31"/>
-      <c r="DA9" s="32"/>
-      <c r="DB9" s="24"/>
-      <c r="DC9" s="31"/>
-      <c r="DD9" s="32"/>
-      <c r="DE9" s="24"/>
-      <c r="DF9" s="31"/>
-      <c r="DG9" s="32"/>
-      <c r="DH9" s="24"/>
-      <c r="DI9" s="31"/>
-      <c r="DJ9" s="32"/>
-      <c r="DK9" s="24"/>
-      <c r="DL9" s="31"/>
-      <c r="DM9" s="32"/>
-      <c r="DN9" s="31"/>
-      <c r="DO9" s="31"/>
-      <c r="DP9" s="32"/>
-      <c r="DQ9" s="77"/>
-      <c r="DR9" s="32"/>
-      <c r="DS9" s="25"/>
+      <c r="H9" s="43"/>
+      <c r="I9" s="43"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="43"/>
+      <c r="L9" s="43"/>
+      <c r="M9" s="104"/>
+      <c r="N9" s="102"/>
+      <c r="O9" s="103"/>
+      <c r="P9" s="104"/>
+      <c r="Q9" s="102"/>
+      <c r="R9" s="103"/>
+      <c r="S9" s="104"/>
+      <c r="T9" s="102"/>
+      <c r="U9" s="103"/>
+      <c r="V9" s="104"/>
+      <c r="W9" s="102"/>
+      <c r="X9" s="103"/>
+      <c r="Y9" s="104"/>
+      <c r="Z9" s="102"/>
+      <c r="AA9" s="103"/>
+      <c r="AB9" s="104"/>
+      <c r="AC9" s="102"/>
+      <c r="AD9" s="103"/>
+      <c r="AE9" s="104"/>
+      <c r="AF9" s="102"/>
+      <c r="AG9" s="103"/>
+      <c r="AH9" s="104"/>
+      <c r="AI9" s="102"/>
+      <c r="AJ9" s="103"/>
+      <c r="AK9" s="104"/>
+      <c r="AL9" s="102"/>
+      <c r="AM9" s="103"/>
+      <c r="AN9" s="104"/>
+      <c r="AO9" s="102"/>
+      <c r="AP9" s="103"/>
+      <c r="AQ9" s="104"/>
+      <c r="AR9" s="102"/>
+      <c r="AS9" s="103"/>
+      <c r="AT9" s="102"/>
+      <c r="AU9" s="102"/>
+      <c r="AV9" s="123"/>
+      <c r="AW9" s="124"/>
+      <c r="AX9" s="102"/>
+      <c r="AY9" s="103"/>
+      <c r="AZ9" s="104"/>
+      <c r="BA9" s="102"/>
+      <c r="BB9" s="103"/>
+      <c r="BC9" s="104"/>
+      <c r="BD9" s="102"/>
+      <c r="BE9" s="103"/>
+      <c r="BF9" s="104"/>
+      <c r="BG9" s="102"/>
+      <c r="BH9" s="103"/>
+      <c r="BI9" s="104"/>
+      <c r="BJ9" s="102"/>
+      <c r="BK9" s="103"/>
+      <c r="BL9" s="104"/>
+      <c r="BM9" s="102"/>
+      <c r="BN9" s="103"/>
+      <c r="BO9" s="104"/>
+      <c r="BP9" s="102"/>
+      <c r="BQ9" s="103"/>
+      <c r="BR9" s="104"/>
+      <c r="BS9" s="102"/>
+      <c r="BT9" s="103"/>
+      <c r="BU9" s="104"/>
+      <c r="BV9" s="102"/>
+      <c r="BW9" s="103"/>
+      <c r="BX9" s="104"/>
+      <c r="BY9" s="102"/>
+      <c r="BZ9" s="103"/>
+      <c r="CA9" s="104"/>
+      <c r="CB9" s="102"/>
+      <c r="CC9" s="103"/>
+      <c r="CD9" s="102"/>
+      <c r="CE9" s="102"/>
+      <c r="CF9" s="118"/>
+      <c r="CG9" s="124"/>
+      <c r="CH9" s="102"/>
+      <c r="CI9" s="103"/>
+      <c r="CJ9" s="104"/>
+      <c r="CK9" s="102"/>
+      <c r="CL9" s="103"/>
+      <c r="CM9" s="104"/>
+      <c r="CN9" s="102"/>
+      <c r="CO9" s="103"/>
+      <c r="CP9" s="104"/>
+      <c r="CQ9" s="102"/>
+      <c r="CR9" s="103"/>
+      <c r="CS9" s="104"/>
+      <c r="CT9" s="102"/>
+      <c r="CU9" s="103"/>
+      <c r="CV9" s="104"/>
+      <c r="CW9" s="102"/>
+      <c r="CX9" s="103"/>
+      <c r="CY9" s="104"/>
+      <c r="CZ9" s="102"/>
+      <c r="DA9" s="103"/>
+      <c r="DB9" s="104"/>
+      <c r="DC9" s="102"/>
+      <c r="DD9" s="103"/>
+      <c r="DE9" s="104"/>
+      <c r="DF9" s="102"/>
+      <c r="DG9" s="103"/>
+      <c r="DH9" s="104"/>
+      <c r="DI9" s="102"/>
+      <c r="DJ9" s="103"/>
+      <c r="DK9" s="104"/>
+      <c r="DL9" s="102"/>
+      <c r="DM9" s="103"/>
+      <c r="DN9" s="102"/>
+      <c r="DO9" s="102"/>
+      <c r="DP9" s="103"/>
+      <c r="DQ9" s="106"/>
+      <c r="DR9" s="103"/>
+      <c r="DS9" s="114"/>
       <c r="DT9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5227,9 +5227,9 @@
       <c r="DV9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="DW9" s="32"/>
-      <c r="DX9" s="32"/>
-      <c r="DY9" s="25"/>
+      <c r="DW9" s="103"/>
+      <c r="DX9" s="103"/>
+      <c r="DY9" s="114"/>
       <c r="DZ9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5239,9 +5239,9 @@
       <c r="EB9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EC9" s="32"/>
-      <c r="ED9" s="32"/>
-      <c r="EE9" s="25"/>
+      <c r="EC9" s="103"/>
+      <c r="ED9" s="103"/>
+      <c r="EE9" s="114"/>
       <c r="EF9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5251,9 +5251,9 @@
       <c r="EH9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EI9" s="32"/>
-      <c r="EJ9" s="32"/>
-      <c r="EK9" s="25"/>
+      <c r="EI9" s="103"/>
+      <c r="EJ9" s="103"/>
+      <c r="EK9" s="114"/>
       <c r="EL9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5263,9 +5263,9 @@
       <c r="EN9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EO9" s="32"/>
-      <c r="EP9" s="32"/>
-      <c r="EQ9" s="25"/>
+      <c r="EO9" s="103"/>
+      <c r="EP9" s="103"/>
+      <c r="EQ9" s="114"/>
       <c r="ER9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5275,9 +5275,9 @@
       <c r="ET9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="EU9" s="32"/>
-      <c r="EV9" s="32"/>
-      <c r="EW9" s="25"/>
+      <c r="EU9" s="103"/>
+      <c r="EV9" s="103"/>
+      <c r="EW9" s="114"/>
       <c r="EX9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5287,9 +5287,9 @@
       <c r="EZ9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FA9" s="25"/>
-      <c r="FB9" s="25"/>
-      <c r="FC9" s="25"/>
+      <c r="FA9" s="114"/>
+      <c r="FB9" s="114"/>
+      <c r="FC9" s="114"/>
       <c r="FD9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5299,9 +5299,9 @@
       <c r="FF9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FG9" s="25"/>
-      <c r="FH9" s="25"/>
-      <c r="FI9" s="25"/>
+      <c r="FG9" s="114"/>
+      <c r="FH9" s="114"/>
+      <c r="FI9" s="114"/>
       <c r="FJ9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5311,9 +5311,9 @@
       <c r="FL9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FM9" s="25"/>
-      <c r="FN9" s="25"/>
-      <c r="FO9" s="25"/>
+      <c r="FM9" s="114"/>
+      <c r="FN9" s="114"/>
+      <c r="FO9" s="114"/>
       <c r="FP9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5323,9 +5323,9 @@
       <c r="FR9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FS9" s="25"/>
-      <c r="FT9" s="25"/>
-      <c r="FU9" s="25"/>
+      <c r="FS9" s="114"/>
+      <c r="FT9" s="114"/>
+      <c r="FU9" s="114"/>
       <c r="FV9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5335,9 +5335,9 @@
       <c r="FX9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="FY9" s="25"/>
-      <c r="FZ9" s="25"/>
-      <c r="GA9" s="25"/>
+      <c r="FY9" s="114"/>
+      <c r="FZ9" s="114"/>
+      <c r="GA9" s="114"/>
       <c r="GB9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5347,9 +5347,9 @@
       <c r="GD9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="GE9" s="25"/>
-      <c r="GF9" s="25"/>
-      <c r="GG9" s="25"/>
+      <c r="GE9" s="114"/>
+      <c r="GF9" s="114"/>
+      <c r="GG9" s="114"/>
       <c r="GH9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5359,9 +5359,9 @@
       <c r="GJ9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="GK9" s="90"/>
-      <c r="GL9" s="24"/>
-      <c r="GM9" s="30"/>
+      <c r="GK9" s="113"/>
+      <c r="GL9" s="104"/>
+      <c r="GM9" s="126"/>
       <c r="GN9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5371,9 +5371,9 @@
       <c r="GP9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="GQ9" s="25"/>
-      <c r="GR9" s="25"/>
-      <c r="GS9" s="25"/>
+      <c r="GQ9" s="114"/>
+      <c r="GR9" s="114"/>
+      <c r="GS9" s="114"/>
       <c r="GT9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5383,9 +5383,9 @@
       <c r="GV9" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="GW9" s="25"/>
-      <c r="GX9" s="25"/>
-      <c r="GY9" s="25"/>
+      <c r="GW9" s="114"/>
+      <c r="GX9" s="114"/>
+      <c r="GY9" s="114"/>
       <c r="GZ9" s="17" t="s">
         <v>51</v>
       </c>
@@ -5402,625 +5402,625 @@
         <v>228</v>
       </c>
       <c r="C10" s="21"/>
-      <c r="D10" s="115" t="s">
+      <c r="D10" s="24" t="s">
         <v>59</v>
       </c>
-      <c r="E10" s="115" t="s">
+      <c r="E10" s="24" t="s">
         <v>438</v>
       </c>
-      <c r="F10" s="115" t="s">
+      <c r="F10" s="24" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="115" t="s">
+      <c r="G10" s="24" t="s">
         <v>439</v>
       </c>
-      <c r="H10" s="115" t="s">
+      <c r="H10" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="115" t="s">
+      <c r="I10" s="24" t="s">
         <v>62</v>
       </c>
-      <c r="J10" s="115" t="s">
+      <c r="J10" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="K10" s="115" t="s">
+      <c r="K10" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="L10" s="115" t="s">
+      <c r="L10" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="M10" s="116" t="s">
+      <c r="M10" s="25" t="s">
         <v>66</v>
       </c>
-      <c r="N10" s="116" t="s">
+      <c r="N10" s="25" t="s">
         <v>67</v>
       </c>
-      <c r="O10" s="117" t="s">
+      <c r="O10" s="26" t="s">
         <v>440</v>
       </c>
-      <c r="P10" s="116" t="s">
+      <c r="P10" s="25" t="s">
         <v>68</v>
       </c>
-      <c r="Q10" s="116" t="s">
+      <c r="Q10" s="25" t="s">
         <v>69</v>
       </c>
-      <c r="R10" s="117" t="s">
+      <c r="R10" s="26" t="s">
         <v>441</v>
       </c>
-      <c r="S10" s="116" t="s">
+      <c r="S10" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="T10" s="116" t="s">
+      <c r="T10" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="U10" s="117" t="s">
+      <c r="U10" s="26" t="s">
         <v>442</v>
       </c>
-      <c r="V10" s="116" t="s">
+      <c r="V10" s="25" t="s">
         <v>72</v>
       </c>
-      <c r="W10" s="116" t="s">
+      <c r="W10" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="X10" s="117" t="s">
+      <c r="X10" s="26" t="s">
         <v>443</v>
       </c>
-      <c r="Y10" s="116" t="s">
+      <c r="Y10" s="25" t="s">
         <v>74</v>
       </c>
-      <c r="Z10" s="116" t="s">
+      <c r="Z10" s="25" t="s">
         <v>75</v>
       </c>
-      <c r="AA10" s="117" t="s">
+      <c r="AA10" s="26" t="s">
         <v>444</v>
       </c>
-      <c r="AB10" s="116" t="s">
+      <c r="AB10" s="25" t="s">
         <v>76</v>
       </c>
-      <c r="AC10" s="116" t="s">
+      <c r="AC10" s="25" t="s">
         <v>77</v>
       </c>
-      <c r="AD10" s="117" t="s">
+      <c r="AD10" s="26" t="s">
         <v>445</v>
       </c>
-      <c r="AE10" s="116" t="s">
+      <c r="AE10" s="25" t="s">
         <v>78</v>
       </c>
-      <c r="AF10" s="116" t="s">
+      <c r="AF10" s="25" t="s">
         <v>79</v>
       </c>
-      <c r="AG10" s="117" t="s">
+      <c r="AG10" s="26" t="s">
         <v>446</v>
       </c>
-      <c r="AH10" s="116" t="s">
+      <c r="AH10" s="25" t="s">
         <v>80</v>
       </c>
-      <c r="AI10" s="116" t="s">
+      <c r="AI10" s="25" t="s">
         <v>81</v>
       </c>
-      <c r="AJ10" s="117" t="s">
+      <c r="AJ10" s="26" t="s">
         <v>447</v>
       </c>
-      <c r="AK10" s="116" t="s">
+      <c r="AK10" s="25" t="s">
         <v>82</v>
       </c>
-      <c r="AL10" s="116" t="s">
+      <c r="AL10" s="25" t="s">
         <v>83</v>
       </c>
-      <c r="AM10" s="117" t="s">
+      <c r="AM10" s="26" t="s">
         <v>448</v>
       </c>
-      <c r="AN10" s="116" t="s">
+      <c r="AN10" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="AO10" s="116" t="s">
+      <c r="AO10" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="AP10" s="117" t="s">
+      <c r="AP10" s="26" t="s">
         <v>449</v>
       </c>
-      <c r="AQ10" s="116" t="s">
+      <c r="AQ10" s="25" t="s">
         <v>86</v>
       </c>
-      <c r="AR10" s="116" t="s">
+      <c r="AR10" s="25" t="s">
         <v>87</v>
       </c>
-      <c r="AS10" s="117" t="s">
+      <c r="AS10" s="26" t="s">
         <v>450</v>
       </c>
-      <c r="AT10" s="117" t="s">
+      <c r="AT10" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="AU10" s="117" t="s">
+      <c r="AU10" s="26" t="s">
         <v>89</v>
       </c>
-      <c r="AV10" s="117" t="s">
+      <c r="AV10" s="26" t="s">
         <v>451</v>
       </c>
-      <c r="AW10" s="116" t="s">
+      <c r="AW10" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="AX10" s="116" t="s">
+      <c r="AX10" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="AY10" s="117" t="s">
+      <c r="AY10" s="26" t="s">
         <v>452</v>
       </c>
-      <c r="AZ10" s="116" t="s">
+      <c r="AZ10" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="BA10" s="116" t="s">
+      <c r="BA10" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="BB10" s="117" t="s">
+      <c r="BB10" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="BC10" s="116" t="s">
+      <c r="BC10" s="25" t="s">
         <v>94</v>
       </c>
-      <c r="BD10" s="116" t="s">
+      <c r="BD10" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="BE10" s="117" t="s">
+      <c r="BE10" s="26" t="s">
         <v>454</v>
       </c>
-      <c r="BF10" s="116" t="s">
+      <c r="BF10" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="BG10" s="116" t="s">
+      <c r="BG10" s="25" t="s">
         <v>97</v>
       </c>
-      <c r="BH10" s="117" t="s">
+      <c r="BH10" s="26" t="s">
         <v>455</v>
       </c>
-      <c r="BI10" s="116" t="s">
+      <c r="BI10" s="25" t="s">
         <v>98</v>
       </c>
-      <c r="BJ10" s="116" t="s">
+      <c r="BJ10" s="25" t="s">
         <v>99</v>
       </c>
-      <c r="BK10" s="117" t="s">
+      <c r="BK10" s="26" t="s">
         <v>456</v>
       </c>
-      <c r="BL10" s="116" t="s">
+      <c r="BL10" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="BM10" s="116" t="s">
+      <c r="BM10" s="25" t="s">
         <v>101</v>
       </c>
-      <c r="BN10" s="117" t="s">
+      <c r="BN10" s="26" t="s">
         <v>457</v>
       </c>
-      <c r="BO10" s="116" t="s">
+      <c r="BO10" s="25" t="s">
         <v>102</v>
       </c>
-      <c r="BP10" s="116" t="s">
+      <c r="BP10" s="25" t="s">
         <v>103</v>
       </c>
-      <c r="BQ10" s="117" t="s">
+      <c r="BQ10" s="26" t="s">
         <v>458</v>
       </c>
-      <c r="BR10" s="116" t="s">
+      <c r="BR10" s="25" t="s">
         <v>104</v>
       </c>
-      <c r="BS10" s="116" t="s">
+      <c r="BS10" s="25" t="s">
         <v>105</v>
       </c>
-      <c r="BT10" s="117" t="s">
+      <c r="BT10" s="26" t="s">
         <v>459</v>
       </c>
-      <c r="BU10" s="116" t="s">
+      <c r="BU10" s="25" t="s">
         <v>106</v>
       </c>
-      <c r="BV10" s="116" t="s">
+      <c r="BV10" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="BW10" s="117" t="s">
+      <c r="BW10" s="26" t="s">
         <v>460</v>
       </c>
-      <c r="BX10" s="116" t="s">
+      <c r="BX10" s="25" t="s">
         <v>108</v>
       </c>
-      <c r="BY10" s="116" t="s">
+      <c r="BY10" s="25" t="s">
         <v>109</v>
       </c>
-      <c r="BZ10" s="117" t="s">
+      <c r="BZ10" s="26" t="s">
         <v>461</v>
       </c>
-      <c r="CA10" s="116" t="s">
+      <c r="CA10" s="25" t="s">
         <v>110</v>
       </c>
-      <c r="CB10" s="116" t="s">
+      <c r="CB10" s="25" t="s">
         <v>111</v>
       </c>
-      <c r="CC10" s="117" t="s">
+      <c r="CC10" s="26" t="s">
         <v>462</v>
       </c>
-      <c r="CD10" s="117" t="s">
+      <c r="CD10" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="CE10" s="117" t="s">
+      <c r="CE10" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="CF10" s="117" t="s">
+      <c r="CF10" s="26" t="s">
         <v>463</v>
       </c>
-      <c r="CG10" s="116" t="s">
+      <c r="CG10" s="25" t="s">
         <v>114</v>
       </c>
-      <c r="CH10" s="116" t="s">
+      <c r="CH10" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="CI10" s="117" t="s">
+      <c r="CI10" s="26" t="s">
         <v>464</v>
       </c>
-      <c r="CJ10" s="116" t="s">
+      <c r="CJ10" s="25" t="s">
         <v>116</v>
       </c>
-      <c r="CK10" s="116" t="s">
+      <c r="CK10" s="25" t="s">
         <v>117</v>
       </c>
-      <c r="CL10" s="117" t="s">
+      <c r="CL10" s="26" t="s">
         <v>465</v>
       </c>
-      <c r="CM10" s="116" t="s">
+      <c r="CM10" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="CN10" s="116" t="s">
+      <c r="CN10" s="25" t="s">
         <v>119</v>
       </c>
-      <c r="CO10" s="117" t="s">
+      <c r="CO10" s="26" t="s">
         <v>466</v>
       </c>
-      <c r="CP10" s="116" t="s">
+      <c r="CP10" s="25" t="s">
         <v>120</v>
       </c>
-      <c r="CQ10" s="116" t="s">
+      <c r="CQ10" s="25" t="s">
         <v>121</v>
       </c>
-      <c r="CR10" s="117" t="s">
+      <c r="CR10" s="26" t="s">
         <v>467</v>
       </c>
-      <c r="CS10" s="116" t="s">
+      <c r="CS10" s="25" t="s">
         <v>122</v>
       </c>
-      <c r="CT10" s="116" t="s">
+      <c r="CT10" s="25" t="s">
         <v>123</v>
       </c>
-      <c r="CU10" s="117" t="s">
+      <c r="CU10" s="26" t="s">
         <v>468</v>
       </c>
-      <c r="CV10" s="116" t="s">
+      <c r="CV10" s="25" t="s">
         <v>124</v>
       </c>
-      <c r="CW10" s="116" t="s">
+      <c r="CW10" s="25" t="s">
         <v>125</v>
       </c>
-      <c r="CX10" s="117" t="s">
+      <c r="CX10" s="26" t="s">
         <v>469</v>
       </c>
-      <c r="CY10" s="116" t="s">
+      <c r="CY10" s="25" t="s">
         <v>126</v>
       </c>
-      <c r="CZ10" s="116" t="s">
+      <c r="CZ10" s="25" t="s">
         <v>127</v>
       </c>
-      <c r="DA10" s="117" t="s">
+      <c r="DA10" s="26" t="s">
         <v>470</v>
       </c>
-      <c r="DB10" s="116" t="s">
+      <c r="DB10" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="DC10" s="116" t="s">
+      <c r="DC10" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="DD10" s="117" t="s">
+      <c r="DD10" s="26" t="s">
         <v>471</v>
       </c>
-      <c r="DE10" s="116" t="s">
+      <c r="DE10" s="25" t="s">
         <v>130</v>
       </c>
-      <c r="DF10" s="116" t="s">
+      <c r="DF10" s="25" t="s">
         <v>131</v>
       </c>
-      <c r="DG10" s="117" t="s">
+      <c r="DG10" s="26" t="s">
         <v>472</v>
       </c>
-      <c r="DH10" s="116" t="s">
+      <c r="DH10" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="DI10" s="116" t="s">
+      <c r="DI10" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="DJ10" s="117" t="s">
+      <c r="DJ10" s="26" t="s">
         <v>473</v>
       </c>
-      <c r="DK10" s="116" t="s">
+      <c r="DK10" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="DL10" s="116" t="s">
+      <c r="DL10" s="25" t="s">
         <v>135</v>
       </c>
-      <c r="DM10" s="117" t="s">
+      <c r="DM10" s="26" t="s">
         <v>474</v>
       </c>
-      <c r="DN10" s="117" t="s">
+      <c r="DN10" s="26" t="s">
         <v>136</v>
       </c>
-      <c r="DO10" s="117" t="s">
+      <c r="DO10" s="26" t="s">
         <v>137</v>
       </c>
-      <c r="DP10" s="117" t="s">
+      <c r="DP10" s="26" t="s">
         <v>475</v>
       </c>
-      <c r="DQ10" s="116" t="s">
+      <c r="DQ10" s="25" t="s">
         <v>138</v>
       </c>
-      <c r="DR10" s="117" t="s">
+      <c r="DR10" s="26" t="s">
         <v>139</v>
       </c>
-      <c r="DS10" s="117" t="s">
+      <c r="DS10" s="26" t="s">
         <v>140</v>
       </c>
-      <c r="DT10" s="117" t="s">
+      <c r="DT10" s="26" t="s">
         <v>141</v>
       </c>
-      <c r="DU10" s="117" t="s">
+      <c r="DU10" s="26" t="s">
         <v>142</v>
       </c>
-      <c r="DV10" s="117" t="s">
+      <c r="DV10" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="DW10" s="116" t="s">
+      <c r="DW10" s="25" t="s">
         <v>144</v>
       </c>
-      <c r="DX10" s="116" t="s">
+      <c r="DX10" s="25" t="s">
         <v>145</v>
       </c>
-      <c r="DY10" s="117" t="s">
+      <c r="DY10" s="26" t="s">
         <v>146</v>
       </c>
-      <c r="DZ10" s="117" t="s">
+      <c r="DZ10" s="26" t="s">
         <v>147</v>
       </c>
-      <c r="EA10" s="117" t="s">
+      <c r="EA10" s="26" t="s">
         <v>148</v>
       </c>
-      <c r="EB10" s="117" t="s">
+      <c r="EB10" s="26" t="s">
         <v>149</v>
       </c>
-      <c r="EC10" s="116" t="s">
+      <c r="EC10" s="25" t="s">
         <v>150</v>
       </c>
-      <c r="ED10" s="116" t="s">
+      <c r="ED10" s="25" t="s">
         <v>151</v>
       </c>
-      <c r="EE10" s="117" t="s">
+      <c r="EE10" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="EF10" s="117" t="s">
+      <c r="EF10" s="26" t="s">
         <v>153</v>
       </c>
-      <c r="EG10" s="117" t="s">
+      <c r="EG10" s="26" t="s">
         <v>154</v>
       </c>
-      <c r="EH10" s="117" t="s">
+      <c r="EH10" s="26" t="s">
         <v>155</v>
       </c>
-      <c r="EI10" s="117" t="s">
+      <c r="EI10" s="26" t="s">
         <v>156</v>
       </c>
-      <c r="EJ10" s="117" t="s">
+      <c r="EJ10" s="26" t="s">
         <v>157</v>
       </c>
-      <c r="EK10" s="117" t="s">
+      <c r="EK10" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="EL10" s="117" t="s">
+      <c r="EL10" s="26" t="s">
         <v>159</v>
       </c>
-      <c r="EM10" s="117" t="s">
+      <c r="EM10" s="26" t="s">
         <v>160</v>
       </c>
-      <c r="EN10" s="117" t="s">
+      <c r="EN10" s="26" t="s">
         <v>161</v>
       </c>
-      <c r="EO10" s="116" t="s">
+      <c r="EO10" s="25" t="s">
         <v>162</v>
       </c>
-      <c r="EP10" s="116" t="s">
+      <c r="EP10" s="25" t="s">
         <v>163</v>
       </c>
-      <c r="EQ10" s="117" t="s">
+      <c r="EQ10" s="26" t="s">
         <v>164</v>
       </c>
-      <c r="ER10" s="117" t="s">
+      <c r="ER10" s="26" t="s">
         <v>165</v>
       </c>
-      <c r="ES10" s="117" t="s">
+      <c r="ES10" s="26" t="s">
         <v>166</v>
       </c>
-      <c r="ET10" s="117" t="s">
+      <c r="ET10" s="26" t="s">
         <v>167</v>
       </c>
-      <c r="EU10" s="116" t="s">
+      <c r="EU10" s="25" t="s">
         <v>168</v>
       </c>
-      <c r="EV10" s="116" t="s">
+      <c r="EV10" s="25" t="s">
         <v>169</v>
       </c>
-      <c r="EW10" s="117" t="s">
+      <c r="EW10" s="26" t="s">
         <v>170</v>
       </c>
-      <c r="EX10" s="117" t="s">
+      <c r="EX10" s="26" t="s">
         <v>171</v>
       </c>
-      <c r="EY10" s="117" t="s">
+      <c r="EY10" s="26" t="s">
         <v>172</v>
       </c>
-      <c r="EZ10" s="117" t="s">
+      <c r="EZ10" s="26" t="s">
         <v>173</v>
       </c>
-      <c r="FA10" s="116" t="s">
+      <c r="FA10" s="25" t="s">
         <v>174</v>
       </c>
-      <c r="FB10" s="116" t="s">
+      <c r="FB10" s="25" t="s">
         <v>175</v>
       </c>
-      <c r="FC10" s="117" t="s">
+      <c r="FC10" s="26" t="s">
         <v>176</v>
       </c>
-      <c r="FD10" s="117" t="s">
+      <c r="FD10" s="26" t="s">
         <v>177</v>
       </c>
-      <c r="FE10" s="117" t="s">
+      <c r="FE10" s="26" t="s">
         <v>178</v>
       </c>
-      <c r="FF10" s="117" t="s">
+      <c r="FF10" s="26" t="s">
         <v>179</v>
       </c>
-      <c r="FG10" s="116" t="s">
+      <c r="FG10" s="25" t="s">
         <v>180</v>
       </c>
-      <c r="FH10" s="116" t="s">
+      <c r="FH10" s="25" t="s">
         <v>181</v>
       </c>
-      <c r="FI10" s="117" t="s">
+      <c r="FI10" s="26" t="s">
         <v>182</v>
       </c>
-      <c r="FJ10" s="117" t="s">
+      <c r="FJ10" s="26" t="s">
         <v>183</v>
       </c>
-      <c r="FK10" s="117" t="s">
+      <c r="FK10" s="26" t="s">
         <v>184</v>
       </c>
-      <c r="FL10" s="117" t="s">
+      <c r="FL10" s="26" t="s">
         <v>185</v>
       </c>
-      <c r="FM10" s="117" t="s">
+      <c r="FM10" s="26" t="s">
         <v>186</v>
       </c>
-      <c r="FN10" s="117" t="s">
+      <c r="FN10" s="26" t="s">
         <v>187</v>
       </c>
-      <c r="FO10" s="117" t="s">
+      <c r="FO10" s="26" t="s">
         <v>188</v>
       </c>
-      <c r="FP10" s="117" t="s">
+      <c r="FP10" s="26" t="s">
         <v>189</v>
       </c>
-      <c r="FQ10" s="117" t="s">
+      <c r="FQ10" s="26" t="s">
         <v>190</v>
       </c>
-      <c r="FR10" s="117" t="s">
+      <c r="FR10" s="26" t="s">
         <v>191</v>
       </c>
-      <c r="FS10" s="116" t="s">
+      <c r="FS10" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="FT10" s="116" t="s">
+      <c r="FT10" s="25" t="s">
         <v>193</v>
       </c>
-      <c r="FU10" s="117" t="s">
+      <c r="FU10" s="26" t="s">
         <v>194</v>
       </c>
-      <c r="FV10" s="117" t="s">
+      <c r="FV10" s="26" t="s">
         <v>195</v>
       </c>
-      <c r="FW10" s="117" t="s">
+      <c r="FW10" s="26" t="s">
         <v>196</v>
       </c>
-      <c r="FX10" s="117" t="s">
+      <c r="FX10" s="26" t="s">
         <v>197</v>
       </c>
-      <c r="FY10" s="116" t="s">
+      <c r="FY10" s="25" t="s">
         <v>198</v>
       </c>
-      <c r="FZ10" s="116" t="s">
+      <c r="FZ10" s="25" t="s">
         <v>199</v>
       </c>
-      <c r="GA10" s="117" t="s">
+      <c r="GA10" s="26" t="s">
         <v>200</v>
       </c>
-      <c r="GB10" s="117" t="s">
+      <c r="GB10" s="26" t="s">
         <v>201</v>
       </c>
-      <c r="GC10" s="117" t="s">
+      <c r="GC10" s="26" t="s">
         <v>202</v>
       </c>
-      <c r="GD10" s="117" t="s">
+      <c r="GD10" s="26" t="s">
         <v>203</v>
       </c>
-      <c r="GE10" s="116" t="s">
+      <c r="GE10" s="25" t="s">
         <v>204</v>
       </c>
-      <c r="GF10" s="116" t="s">
+      <c r="GF10" s="25" t="s">
         <v>205</v>
       </c>
-      <c r="GG10" s="117" t="s">
+      <c r="GG10" s="26" t="s">
         <v>206</v>
       </c>
-      <c r="GH10" s="117" t="s">
+      <c r="GH10" s="26" t="s">
         <v>207</v>
       </c>
-      <c r="GI10" s="117" t="s">
+      <c r="GI10" s="26" t="s">
         <v>208</v>
       </c>
-      <c r="GJ10" s="117" t="s">
+      <c r="GJ10" s="26" t="s">
         <v>209</v>
       </c>
-      <c r="GK10" s="117" t="s">
+      <c r="GK10" s="26" t="s">
         <v>210</v>
       </c>
-      <c r="GL10" s="117" t="s">
+      <c r="GL10" s="26" t="s">
         <v>211</v>
       </c>
-      <c r="GM10" s="117" t="s">
+      <c r="GM10" s="26" t="s">
         <v>212</v>
       </c>
-      <c r="GN10" s="117" t="s">
+      <c r="GN10" s="26" t="s">
         <v>213</v>
       </c>
-      <c r="GO10" s="117" t="s">
+      <c r="GO10" s="26" t="s">
         <v>214</v>
       </c>
-      <c r="GP10" s="117" t="s">
+      <c r="GP10" s="26" t="s">
         <v>215</v>
       </c>
-      <c r="GQ10" s="116" t="s">
+      <c r="GQ10" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="GR10" s="116" t="s">
+      <c r="GR10" s="25" t="s">
         <v>217</v>
       </c>
-      <c r="GS10" s="117" t="s">
+      <c r="GS10" s="26" t="s">
         <v>218</v>
       </c>
-      <c r="GT10" s="117" t="s">
+      <c r="GT10" s="26" t="s">
         <v>219</v>
       </c>
-      <c r="GU10" s="117" t="s">
+      <c r="GU10" s="26" t="s">
         <v>220</v>
       </c>
-      <c r="GV10" s="117" t="s">
+      <c r="GV10" s="26" t="s">
         <v>221</v>
       </c>
-      <c r="GW10" s="116" t="s">
+      <c r="GW10" s="25" t="s">
         <v>222</v>
       </c>
-      <c r="GX10" s="116" t="s">
+      <c r="GX10" s="25" t="s">
         <v>223</v>
       </c>
-      <c r="GY10" s="117" t="s">
+      <c r="GY10" s="26" t="s">
         <v>224</v>
       </c>
-      <c r="GZ10" s="117" t="s">
+      <c r="GZ10" s="26" t="s">
         <v>225</v>
       </c>
-      <c r="HA10" s="117" t="s">
+      <c r="HA10" s="26" t="s">
         <v>226</v>
       </c>
-      <c r="HB10" s="118" t="s">
+      <c r="HB10" s="27" t="s">
         <v>227</v>
       </c>
     </row>
@@ -6030,630 +6030,888 @@
       <c r="C11" s="23" t="s">
         <v>229</v>
       </c>
-      <c r="D11" s="119" t="s">
+      <c r="D11" s="28" t="s">
         <v>230</v>
       </c>
-      <c r="E11" s="120" t="s">
+      <c r="E11" s="29" t="s">
         <v>231</v>
       </c>
-      <c r="F11" s="119" t="s">
+      <c r="F11" s="28" t="s">
         <v>232</v>
       </c>
-      <c r="G11" s="120" t="s">
+      <c r="G11" s="29" t="s">
         <v>233</v>
       </c>
-      <c r="H11" s="119" t="s">
+      <c r="H11" s="28" t="s">
         <v>234</v>
       </c>
-      <c r="I11" s="119" t="s">
+      <c r="I11" s="28" t="s">
         <v>235</v>
       </c>
-      <c r="J11" s="119" t="s">
+      <c r="J11" s="28" t="s">
         <v>236</v>
       </c>
-      <c r="K11" s="119" t="s">
+      <c r="K11" s="28" t="s">
         <v>237</v>
       </c>
-      <c r="L11" s="119" t="s">
+      <c r="L11" s="28" t="s">
         <v>238</v>
       </c>
-      <c r="M11" s="121" t="s">
+      <c r="M11" s="30" t="s">
         <v>239</v>
       </c>
-      <c r="N11" s="121" t="s">
+      <c r="N11" s="30" t="s">
         <v>240</v>
       </c>
-      <c r="O11" s="119" t="s">
+      <c r="O11" s="28" t="s">
         <v>241</v>
       </c>
-      <c r="P11" s="121" t="s">
+      <c r="P11" s="30" t="s">
         <v>242</v>
       </c>
-      <c r="Q11" s="121" t="s">
+      <c r="Q11" s="30" t="s">
         <v>243</v>
       </c>
-      <c r="R11" s="119" t="s">
+      <c r="R11" s="28" t="s">
         <v>244</v>
       </c>
-      <c r="S11" s="121" t="s">
+      <c r="S11" s="30" t="s">
         <v>245</v>
       </c>
-      <c r="T11" s="121" t="s">
+      <c r="T11" s="30" t="s">
         <v>246</v>
       </c>
-      <c r="U11" s="119" t="s">
+      <c r="U11" s="28" t="s">
         <v>247</v>
       </c>
-      <c r="V11" s="121" t="s">
+      <c r="V11" s="30" t="s">
         <v>248</v>
       </c>
-      <c r="W11" s="121" t="s">
+      <c r="W11" s="30" t="s">
         <v>249</v>
       </c>
-      <c r="X11" s="119" t="s">
+      <c r="X11" s="28" t="s">
         <v>250</v>
       </c>
-      <c r="Y11" s="121" t="s">
+      <c r="Y11" s="30" t="s">
         <v>251</v>
       </c>
-      <c r="Z11" s="121" t="s">
+      <c r="Z11" s="30" t="s">
         <v>252</v>
       </c>
-      <c r="AA11" s="119" t="s">
+      <c r="AA11" s="28" t="s">
         <v>253</v>
       </c>
-      <c r="AB11" s="121" t="s">
+      <c r="AB11" s="30" t="s">
         <v>254</v>
       </c>
-      <c r="AC11" s="121" t="s">
+      <c r="AC11" s="30" t="s">
         <v>255</v>
       </c>
-      <c r="AD11" s="119" t="s">
+      <c r="AD11" s="28" t="s">
         <v>256</v>
       </c>
-      <c r="AE11" s="121" t="s">
+      <c r="AE11" s="30" t="s">
         <v>257</v>
       </c>
-      <c r="AF11" s="121" t="s">
+      <c r="AF11" s="30" t="s">
         <v>258</v>
       </c>
-      <c r="AG11" s="119" t="s">
+      <c r="AG11" s="28" t="s">
         <v>259</v>
       </c>
-      <c r="AH11" s="121" t="s">
+      <c r="AH11" s="30" t="s">
         <v>260</v>
       </c>
-      <c r="AI11" s="121" t="s">
+      <c r="AI11" s="30" t="s">
         <v>261</v>
       </c>
-      <c r="AJ11" s="119" t="s">
+      <c r="AJ11" s="28" t="s">
         <v>262</v>
       </c>
-      <c r="AK11" s="121" t="s">
+      <c r="AK11" s="30" t="s">
         <v>263</v>
       </c>
-      <c r="AL11" s="121" t="s">
+      <c r="AL11" s="30" t="s">
         <v>264</v>
       </c>
-      <c r="AM11" s="119" t="s">
+      <c r="AM11" s="28" t="s">
         <v>265</v>
       </c>
-      <c r="AN11" s="121" t="s">
+      <c r="AN11" s="30" t="s">
         <v>266</v>
       </c>
-      <c r="AO11" s="121" t="s">
+      <c r="AO11" s="30" t="s">
         <v>267</v>
       </c>
-      <c r="AP11" s="119" t="s">
+      <c r="AP11" s="28" t="s">
         <v>268</v>
       </c>
-      <c r="AQ11" s="121" t="s">
+      <c r="AQ11" s="30" t="s">
         <v>269</v>
       </c>
-      <c r="AR11" s="121" t="s">
+      <c r="AR11" s="30" t="s">
         <v>270</v>
       </c>
-      <c r="AS11" s="119" t="s">
+      <c r="AS11" s="28" t="s">
         <v>271</v>
       </c>
-      <c r="AT11" s="119" t="s">
+      <c r="AT11" s="28" t="s">
         <v>272</v>
       </c>
-      <c r="AU11" s="119" t="s">
+      <c r="AU11" s="28" t="s">
         <v>273</v>
       </c>
-      <c r="AV11" s="122" t="s">
+      <c r="AV11" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="AW11" s="123" t="s">
+      <c r="AW11" s="32" t="s">
         <v>275</v>
       </c>
-      <c r="AX11" s="121" t="s">
+      <c r="AX11" s="30" t="s">
         <v>276</v>
       </c>
-      <c r="AY11" s="119" t="s">
+      <c r="AY11" s="28" t="s">
         <v>277</v>
       </c>
-      <c r="AZ11" s="121" t="s">
+      <c r="AZ11" s="30" t="s">
         <v>278</v>
       </c>
-      <c r="BA11" s="121" t="s">
+      <c r="BA11" s="30" t="s">
         <v>279</v>
       </c>
-      <c r="BB11" s="119" t="s">
+      <c r="BB11" s="28" t="s">
         <v>280</v>
       </c>
-      <c r="BC11" s="121" t="s">
+      <c r="BC11" s="30" t="s">
         <v>281</v>
       </c>
-      <c r="BD11" s="121" t="s">
+      <c r="BD11" s="30" t="s">
         <v>282</v>
       </c>
-      <c r="BE11" s="119" t="s">
+      <c r="BE11" s="28" t="s">
         <v>283</v>
       </c>
-      <c r="BF11" s="121" t="s">
+      <c r="BF11" s="30" t="s">
         <v>284</v>
       </c>
-      <c r="BG11" s="121" t="s">
+      <c r="BG11" s="30" t="s">
         <v>285</v>
       </c>
-      <c r="BH11" s="119" t="s">
+      <c r="BH11" s="28" t="s">
         <v>286</v>
       </c>
-      <c r="BI11" s="121" t="s">
+      <c r="BI11" s="30" t="s">
         <v>287</v>
       </c>
-      <c r="BJ11" s="121" t="s">
+      <c r="BJ11" s="30" t="s">
         <v>288</v>
       </c>
-      <c r="BK11" s="119" t="s">
+      <c r="BK11" s="28" t="s">
         <v>289</v>
       </c>
-      <c r="BL11" s="121" t="s">
+      <c r="BL11" s="30" t="s">
         <v>290</v>
       </c>
-      <c r="BM11" s="121" t="s">
+      <c r="BM11" s="30" t="s">
         <v>291</v>
       </c>
-      <c r="BN11" s="119" t="s">
+      <c r="BN11" s="28" t="s">
         <v>292</v>
       </c>
-      <c r="BO11" s="121" t="s">
+      <c r="BO11" s="30" t="s">
         <v>293</v>
       </c>
-      <c r="BP11" s="121" t="s">
+      <c r="BP11" s="30" t="s">
         <v>294</v>
       </c>
-      <c r="BQ11" s="119" t="s">
+      <c r="BQ11" s="28" t="s">
         <v>295</v>
       </c>
-      <c r="BR11" s="121" t="s">
+      <c r="BR11" s="30" t="s">
         <v>296</v>
       </c>
-      <c r="BS11" s="121" t="s">
+      <c r="BS11" s="30" t="s">
         <v>297</v>
       </c>
-      <c r="BT11" s="119" t="s">
+      <c r="BT11" s="28" t="s">
         <v>298</v>
       </c>
-      <c r="BU11" s="121" t="s">
+      <c r="BU11" s="30" t="s">
         <v>299</v>
       </c>
-      <c r="BV11" s="121" t="s">
+      <c r="BV11" s="30" t="s">
         <v>300</v>
       </c>
-      <c r="BW11" s="119" t="s">
+      <c r="BW11" s="28" t="s">
         <v>301</v>
       </c>
-      <c r="BX11" s="121" t="s">
+      <c r="BX11" s="30" t="s">
         <v>302</v>
       </c>
-      <c r="BY11" s="121" t="s">
+      <c r="BY11" s="30" t="s">
         <v>303</v>
       </c>
-      <c r="BZ11" s="119" t="s">
+      <c r="BZ11" s="28" t="s">
         <v>304</v>
       </c>
-      <c r="CA11" s="121" t="s">
+      <c r="CA11" s="30" t="s">
         <v>305</v>
       </c>
-      <c r="CB11" s="121" t="s">
+      <c r="CB11" s="30" t="s">
         <v>306</v>
       </c>
-      <c r="CC11" s="119" t="s">
+      <c r="CC11" s="28" t="s">
         <v>307</v>
       </c>
-      <c r="CD11" s="119" t="s">
+      <c r="CD11" s="28" t="s">
         <v>308</v>
       </c>
-      <c r="CE11" s="119" t="s">
+      <c r="CE11" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="CF11" s="122" t="s">
+      <c r="CF11" s="31" t="s">
         <v>310</v>
       </c>
-      <c r="CG11" s="123" t="s">
+      <c r="CG11" s="32" t="s">
         <v>311</v>
       </c>
-      <c r="CH11" s="121" t="s">
+      <c r="CH11" s="30" t="s">
         <v>312</v>
       </c>
-      <c r="CI11" s="119" t="s">
+      <c r="CI11" s="28" t="s">
         <v>313</v>
       </c>
-      <c r="CJ11" s="121" t="s">
+      <c r="CJ11" s="30" t="s">
         <v>314</v>
       </c>
-      <c r="CK11" s="121" t="s">
+      <c r="CK11" s="30" t="s">
         <v>315</v>
       </c>
-      <c r="CL11" s="119" t="s">
+      <c r="CL11" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="CM11" s="121" t="s">
+      <c r="CM11" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="CN11" s="121" t="s">
+      <c r="CN11" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="CO11" s="119" t="s">
+      <c r="CO11" s="28" t="s">
         <v>319</v>
       </c>
-      <c r="CP11" s="121" t="s">
+      <c r="CP11" s="30" t="s">
         <v>320</v>
       </c>
-      <c r="CQ11" s="121" t="s">
+      <c r="CQ11" s="30" t="s">
         <v>321</v>
       </c>
-      <c r="CR11" s="119" t="s">
+      <c r="CR11" s="28" t="s">
         <v>322</v>
       </c>
-      <c r="CS11" s="121" t="s">
+      <c r="CS11" s="30" t="s">
         <v>323</v>
       </c>
-      <c r="CT11" s="121" t="s">
+      <c r="CT11" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="CU11" s="119" t="s">
+      <c r="CU11" s="28" t="s">
         <v>325</v>
       </c>
-      <c r="CV11" s="121" t="s">
+      <c r="CV11" s="30" t="s">
         <v>326</v>
       </c>
-      <c r="CW11" s="121" t="s">
+      <c r="CW11" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="CX11" s="119" t="s">
+      <c r="CX11" s="28" t="s">
         <v>328</v>
       </c>
-      <c r="CY11" s="121" t="s">
+      <c r="CY11" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="CZ11" s="121" t="s">
+      <c r="CZ11" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="DA11" s="119" t="s">
+      <c r="DA11" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="DB11" s="121" t="s">
+      <c r="DB11" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="DC11" s="121" t="s">
+      <c r="DC11" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="DD11" s="119" t="s">
+      <c r="DD11" s="28" t="s">
         <v>334</v>
       </c>
-      <c r="DE11" s="121" t="s">
+      <c r="DE11" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="DF11" s="121" t="s">
+      <c r="DF11" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="DG11" s="119" t="s">
+      <c r="DG11" s="28" t="s">
         <v>337</v>
       </c>
-      <c r="DH11" s="121" t="s">
+      <c r="DH11" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="DI11" s="121" t="s">
+      <c r="DI11" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="DJ11" s="119" t="s">
+      <c r="DJ11" s="28" t="s">
         <v>340</v>
       </c>
-      <c r="DK11" s="121" t="s">
+      <c r="DK11" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="DL11" s="121" t="s">
+      <c r="DL11" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="DM11" s="119" t="s">
+      <c r="DM11" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="DN11" s="119" t="s">
+      <c r="DN11" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="DO11" s="119" t="s">
+      <c r="DO11" s="28" t="s">
         <v>345</v>
       </c>
-      <c r="DP11" s="119" t="s">
+      <c r="DP11" s="28" t="s">
         <v>346</v>
       </c>
-      <c r="DQ11" s="124" t="s">
+      <c r="DQ11" s="33" t="s">
         <v>347</v>
       </c>
-      <c r="DR11" s="119" t="s">
+      <c r="DR11" s="28" t="s">
         <v>348</v>
       </c>
-      <c r="DS11" s="119" t="s">
+      <c r="DS11" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="DT11" s="119" t="s">
+      <c r="DT11" s="28" t="s">
         <v>350</v>
       </c>
-      <c r="DU11" s="119" t="s">
+      <c r="DU11" s="28" t="s">
         <v>351</v>
       </c>
-      <c r="DV11" s="119" t="s">
+      <c r="DV11" s="28" t="s">
         <v>352</v>
       </c>
-      <c r="DW11" s="121" t="s">
+      <c r="DW11" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="DX11" s="121" t="s">
+      <c r="DX11" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="DY11" s="119" t="s">
+      <c r="DY11" s="28" t="s">
         <v>355</v>
       </c>
-      <c r="DZ11" s="119" t="s">
+      <c r="DZ11" s="28" t="s">
         <v>356</v>
       </c>
-      <c r="EA11" s="119" t="s">
+      <c r="EA11" s="28" t="s">
         <v>357</v>
       </c>
-      <c r="EB11" s="119" t="s">
+      <c r="EB11" s="28" t="s">
         <v>358</v>
       </c>
-      <c r="EC11" s="121" t="s">
+      <c r="EC11" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="ED11" s="121" t="s">
+      <c r="ED11" s="30" t="s">
         <v>360</v>
       </c>
-      <c r="EE11" s="119" t="s">
+      <c r="EE11" s="28" t="s">
         <v>361</v>
       </c>
-      <c r="EF11" s="119" t="s">
+      <c r="EF11" s="28" t="s">
         <v>362</v>
       </c>
-      <c r="EG11" s="119" t="s">
+      <c r="EG11" s="28" t="s">
         <v>363</v>
       </c>
-      <c r="EH11" s="119" t="s">
+      <c r="EH11" s="28" t="s">
         <v>364</v>
       </c>
-      <c r="EI11" s="119" t="s">
+      <c r="EI11" s="28" t="s">
         <v>365</v>
       </c>
-      <c r="EJ11" s="119" t="s">
+      <c r="EJ11" s="28" t="s">
         <v>366</v>
       </c>
-      <c r="EK11" s="119" t="s">
+      <c r="EK11" s="28" t="s">
         <v>367</v>
       </c>
-      <c r="EL11" s="119" t="s">
+      <c r="EL11" s="28" t="s">
         <v>368</v>
       </c>
-      <c r="EM11" s="119" t="s">
+      <c r="EM11" s="28" t="s">
         <v>369</v>
       </c>
-      <c r="EN11" s="119" t="s">
+      <c r="EN11" s="28" t="s">
         <v>370</v>
       </c>
-      <c r="EO11" s="121" t="s">
+      <c r="EO11" s="30" t="s">
         <v>371</v>
       </c>
-      <c r="EP11" s="121" t="s">
+      <c r="EP11" s="30" t="s">
         <v>372</v>
       </c>
-      <c r="EQ11" s="119" t="s">
+      <c r="EQ11" s="28" t="s">
         <v>373</v>
       </c>
-      <c r="ER11" s="119" t="s">
+      <c r="ER11" s="28" t="s">
         <v>374</v>
       </c>
-      <c r="ES11" s="119" t="s">
+      <c r="ES11" s="28" t="s">
         <v>375</v>
       </c>
-      <c r="ET11" s="119" t="s">
+      <c r="ET11" s="28" t="s">
         <v>376</v>
       </c>
-      <c r="EU11" s="121" t="s">
+      <c r="EU11" s="30" t="s">
         <v>377</v>
       </c>
-      <c r="EV11" s="121" t="s">
+      <c r="EV11" s="30" t="s">
         <v>378</v>
       </c>
-      <c r="EW11" s="119" t="s">
+      <c r="EW11" s="28" t="s">
         <v>379</v>
       </c>
-      <c r="EX11" s="119" t="s">
+      <c r="EX11" s="28" t="s">
         <v>380</v>
       </c>
-      <c r="EY11" s="119" t="s">
+      <c r="EY11" s="28" t="s">
         <v>381</v>
       </c>
-      <c r="EZ11" s="119" t="s">
+      <c r="EZ11" s="28" t="s">
         <v>382</v>
       </c>
-      <c r="FA11" s="121" t="s">
+      <c r="FA11" s="30" t="s">
         <v>383</v>
       </c>
-      <c r="FB11" s="121" t="s">
+      <c r="FB11" s="30" t="s">
         <v>384</v>
       </c>
-      <c r="FC11" s="119" t="s">
+      <c r="FC11" s="28" t="s">
         <v>385</v>
       </c>
-      <c r="FD11" s="119" t="s">
+      <c r="FD11" s="28" t="s">
         <v>386</v>
       </c>
-      <c r="FE11" s="119" t="s">
+      <c r="FE11" s="28" t="s">
         <v>387</v>
       </c>
-      <c r="FF11" s="119" t="s">
+      <c r="FF11" s="28" t="s">
         <v>388</v>
       </c>
-      <c r="FG11" s="121" t="s">
+      <c r="FG11" s="30" t="s">
         <v>389</v>
       </c>
-      <c r="FH11" s="121" t="s">
+      <c r="FH11" s="30" t="s">
         <v>390</v>
       </c>
-      <c r="FI11" s="119" t="s">
+      <c r="FI11" s="28" t="s">
         <v>391</v>
       </c>
-      <c r="FJ11" s="119" t="s">
+      <c r="FJ11" s="28" t="s">
         <v>392</v>
       </c>
-      <c r="FK11" s="119" t="s">
+      <c r="FK11" s="28" t="s">
         <v>393</v>
       </c>
-      <c r="FL11" s="119" t="s">
+      <c r="FL11" s="28" t="s">
         <v>394</v>
       </c>
-      <c r="FM11" s="119" t="s">
+      <c r="FM11" s="28" t="s">
         <v>395</v>
       </c>
-      <c r="FN11" s="119" t="s">
+      <c r="FN11" s="28" t="s">
         <v>396</v>
       </c>
-      <c r="FO11" s="119" t="s">
+      <c r="FO11" s="28" t="s">
         <v>397</v>
       </c>
-      <c r="FP11" s="119" t="s">
+      <c r="FP11" s="28" t="s">
         <v>398</v>
       </c>
-      <c r="FQ11" s="119" t="s">
+      <c r="FQ11" s="28" t="s">
         <v>399</v>
       </c>
-      <c r="FR11" s="119" t="s">
+      <c r="FR11" s="28" t="s">
         <v>400</v>
       </c>
-      <c r="FS11" s="121" t="s">
+      <c r="FS11" s="30" t="s">
         <v>401</v>
       </c>
-      <c r="FT11" s="121" t="s">
+      <c r="FT11" s="30" t="s">
         <v>402</v>
       </c>
-      <c r="FU11" s="119" t="s">
+      <c r="FU11" s="28" t="s">
         <v>403</v>
       </c>
-      <c r="FV11" s="119" t="s">
+      <c r="FV11" s="28" t="s">
         <v>404</v>
       </c>
-      <c r="FW11" s="119" t="s">
+      <c r="FW11" s="28" t="s">
         <v>405</v>
       </c>
-      <c r="FX11" s="119" t="s">
+      <c r="FX11" s="28" t="s">
         <v>406</v>
       </c>
-      <c r="FY11" s="121" t="s">
+      <c r="FY11" s="30" t="s">
         <v>407</v>
       </c>
-      <c r="FZ11" s="121" t="s">
+      <c r="FZ11" s="30" t="s">
         <v>408</v>
       </c>
-      <c r="GA11" s="119" t="s">
+      <c r="GA11" s="28" t="s">
         <v>409</v>
       </c>
-      <c r="GB11" s="119" t="s">
+      <c r="GB11" s="28" t="s">
         <v>410</v>
       </c>
-      <c r="GC11" s="119" t="s">
+      <c r="GC11" s="28" t="s">
         <v>411</v>
       </c>
-      <c r="GD11" s="119" t="s">
+      <c r="GD11" s="28" t="s">
         <v>412</v>
       </c>
-      <c r="GE11" s="121" t="s">
+      <c r="GE11" s="30" t="s">
         <v>413</v>
       </c>
-      <c r="GF11" s="121" t="s">
+      <c r="GF11" s="30" t="s">
         <v>414</v>
       </c>
-      <c r="GG11" s="119" t="s">
+      <c r="GG11" s="28" t="s">
         <v>415</v>
       </c>
-      <c r="GH11" s="119" t="s">
+      <c r="GH11" s="28" t="s">
         <v>416</v>
       </c>
-      <c r="GI11" s="119" t="s">
+      <c r="GI11" s="28" t="s">
         <v>417</v>
       </c>
-      <c r="GJ11" s="125" t="s">
+      <c r="GJ11" s="34" t="s">
         <v>418</v>
       </c>
-      <c r="GK11" s="126" t="s">
+      <c r="GK11" s="35" t="s">
         <v>419</v>
       </c>
-      <c r="GL11" s="119" t="s">
+      <c r="GL11" s="28" t="s">
         <v>420</v>
       </c>
-      <c r="GM11" s="119" t="s">
+      <c r="GM11" s="28" t="s">
         <v>421</v>
       </c>
-      <c r="GN11" s="119" t="s">
+      <c r="GN11" s="28" t="s">
         <v>422</v>
       </c>
-      <c r="GO11" s="119" t="s">
+      <c r="GO11" s="28" t="s">
         <v>423</v>
       </c>
-      <c r="GP11" s="119" t="s">
+      <c r="GP11" s="28" t="s">
         <v>424</v>
       </c>
-      <c r="GQ11" s="121" t="s">
+      <c r="GQ11" s="30" t="s">
         <v>425</v>
       </c>
-      <c r="GR11" s="121" t="s">
+      <c r="GR11" s="30" t="s">
         <v>426</v>
       </c>
-      <c r="GS11" s="119" t="s">
+      <c r="GS11" s="28" t="s">
         <v>427</v>
       </c>
-      <c r="GT11" s="119" t="s">
+      <c r="GT11" s="28" t="s">
         <v>428</v>
       </c>
-      <c r="GU11" s="119" t="s">
+      <c r="GU11" s="28" t="s">
         <v>429</v>
       </c>
-      <c r="GV11" s="125" t="s">
+      <c r="GV11" s="34" t="s">
         <v>430</v>
       </c>
-      <c r="GW11" s="121" t="s">
+      <c r="GW11" s="30" t="s">
         <v>431</v>
       </c>
-      <c r="GX11" s="121" t="s">
+      <c r="GX11" s="30" t="s">
         <v>432</v>
       </c>
-      <c r="GY11" s="119" t="s">
+      <c r="GY11" s="28" t="s">
         <v>433</v>
       </c>
-      <c r="GZ11" s="119" t="s">
+      <c r="GZ11" s="28" t="s">
         <v>434</v>
       </c>
-      <c r="HA11" s="119" t="s">
+      <c r="HA11" s="28" t="s">
         <v>435</v>
       </c>
-      <c r="HB11" s="119" t="s">
+      <c r="HB11" s="28" t="s">
         <v>436</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="282">
+    <mergeCell ref="FZ8:FZ9"/>
+    <mergeCell ref="GA8:GA9"/>
+    <mergeCell ref="GB8:GD8"/>
+    <mergeCell ref="GE8:GE9"/>
+    <mergeCell ref="GF8:GF9"/>
+    <mergeCell ref="GG8:GG9"/>
+    <mergeCell ref="FP8:FR8"/>
+    <mergeCell ref="FS8:FS9"/>
+    <mergeCell ref="FT8:FT9"/>
+    <mergeCell ref="FU8:FU9"/>
+    <mergeCell ref="FV8:FX8"/>
+    <mergeCell ref="FY8:FY9"/>
+    <mergeCell ref="GT8:GV8"/>
+    <mergeCell ref="GW8:GW9"/>
+    <mergeCell ref="GX8:GX9"/>
+    <mergeCell ref="GY8:GY9"/>
+    <mergeCell ref="GZ8:HB8"/>
+    <mergeCell ref="GH8:GJ8"/>
+    <mergeCell ref="GM8:GM9"/>
+    <mergeCell ref="GN8:GP8"/>
+    <mergeCell ref="GQ8:GQ9"/>
+    <mergeCell ref="GR8:GR9"/>
+    <mergeCell ref="GS8:GS9"/>
+    <mergeCell ref="FD8:FF8"/>
+    <mergeCell ref="FG8:FG9"/>
+    <mergeCell ref="FH8:FH9"/>
+    <mergeCell ref="FI8:FI9"/>
+    <mergeCell ref="FJ8:FL8"/>
+    <mergeCell ref="FO8:FO9"/>
+    <mergeCell ref="EV8:EV9"/>
+    <mergeCell ref="EW8:EW9"/>
+    <mergeCell ref="EX8:EZ8"/>
+    <mergeCell ref="FA8:FA9"/>
+    <mergeCell ref="FB8:FB9"/>
+    <mergeCell ref="FC8:FC9"/>
+    <mergeCell ref="DK7:DK9"/>
+    <mergeCell ref="DL7:DL9"/>
+    <mergeCell ref="EL8:EN8"/>
+    <mergeCell ref="EO8:EO9"/>
+    <mergeCell ref="EP8:EP9"/>
+    <mergeCell ref="EQ8:EQ9"/>
+    <mergeCell ref="ER8:ET8"/>
+    <mergeCell ref="EU8:EU9"/>
+    <mergeCell ref="DZ8:EB8"/>
+    <mergeCell ref="EC8:EC9"/>
+    <mergeCell ref="ED8:ED9"/>
+    <mergeCell ref="EE8:EE9"/>
+    <mergeCell ref="EF8:EH8"/>
+    <mergeCell ref="EK8:EK9"/>
+    <mergeCell ref="DI7:DI9"/>
+    <mergeCell ref="DJ7:DJ9"/>
+    <mergeCell ref="GW7:GX7"/>
+    <mergeCell ref="GY7:HB7"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="DS8:DS9"/>
+    <mergeCell ref="DT8:DV8"/>
+    <mergeCell ref="DW8:DW9"/>
+    <mergeCell ref="DX8:DX9"/>
+    <mergeCell ref="DY8:DY9"/>
+    <mergeCell ref="FY7:FZ7"/>
+    <mergeCell ref="GA7:GD7"/>
+    <mergeCell ref="GE7:GF7"/>
+    <mergeCell ref="GG7:GJ7"/>
+    <mergeCell ref="GQ7:GR7"/>
+    <mergeCell ref="GS7:GV7"/>
+    <mergeCell ref="DW7:DX7"/>
+    <mergeCell ref="DY7:EB7"/>
+    <mergeCell ref="EC7:ED7"/>
+    <mergeCell ref="EE7:EH7"/>
+    <mergeCell ref="EO7:EP7"/>
+    <mergeCell ref="EQ7:ET7"/>
+    <mergeCell ref="CR7:CR9"/>
+    <mergeCell ref="CG7:CG9"/>
+    <mergeCell ref="CH7:CH9"/>
+    <mergeCell ref="CI7:CI9"/>
+    <mergeCell ref="CJ7:CJ9"/>
+    <mergeCell ref="CK7:CK9"/>
+    <mergeCell ref="CL7:CL9"/>
+    <mergeCell ref="CY7:CY9"/>
+    <mergeCell ref="CZ7:CZ9"/>
+    <mergeCell ref="CS7:CS9"/>
+    <mergeCell ref="CT7:CT9"/>
+    <mergeCell ref="CU7:CU9"/>
+    <mergeCell ref="CV7:CV9"/>
+    <mergeCell ref="CW7:CW9"/>
+    <mergeCell ref="CX7:CX9"/>
+    <mergeCell ref="BW7:BW9"/>
+    <mergeCell ref="BX7:BX9"/>
+    <mergeCell ref="BY7:BY9"/>
+    <mergeCell ref="BZ7:BZ9"/>
+    <mergeCell ref="CM7:CM9"/>
+    <mergeCell ref="CN7:CN9"/>
+    <mergeCell ref="CO7:CO9"/>
+    <mergeCell ref="CP7:CP9"/>
+    <mergeCell ref="CQ7:CQ9"/>
+    <mergeCell ref="BO7:BO9"/>
+    <mergeCell ref="BP7:BP9"/>
+    <mergeCell ref="BQ7:BQ9"/>
+    <mergeCell ref="BR7:BR9"/>
+    <mergeCell ref="BS7:BS9"/>
+    <mergeCell ref="BT7:BT9"/>
+    <mergeCell ref="BI7:BI9"/>
+    <mergeCell ref="BJ7:BJ9"/>
+    <mergeCell ref="BK7:BK9"/>
+    <mergeCell ref="BL7:BL9"/>
+    <mergeCell ref="BM7:BM9"/>
+    <mergeCell ref="BN7:BN9"/>
+    <mergeCell ref="BC7:BC9"/>
+    <mergeCell ref="BD7:BD9"/>
+    <mergeCell ref="BE7:BE9"/>
+    <mergeCell ref="BF7:BF9"/>
+    <mergeCell ref="BG7:BG9"/>
+    <mergeCell ref="BH7:BH9"/>
+    <mergeCell ref="AW7:AW9"/>
+    <mergeCell ref="AX7:AX9"/>
+    <mergeCell ref="AY7:AY9"/>
+    <mergeCell ref="AZ7:AZ9"/>
+    <mergeCell ref="BA7:BA9"/>
+    <mergeCell ref="BB7:BB9"/>
+    <mergeCell ref="AQ7:AQ9"/>
+    <mergeCell ref="AR7:AR9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AT7:AT9"/>
+    <mergeCell ref="AU7:AU9"/>
+    <mergeCell ref="AV7:AV9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AP7:AP9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="FY6:GD6"/>
+    <mergeCell ref="GE6:GJ6"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:Q9"/>
+    <mergeCell ref="R7:R9"/>
+    <mergeCell ref="EU6:EZ6"/>
+    <mergeCell ref="FA6:FB7"/>
+    <mergeCell ref="FC6:FF7"/>
+    <mergeCell ref="FG6:FH7"/>
+    <mergeCell ref="FI6:FL7"/>
+    <mergeCell ref="FS6:FX6"/>
+    <mergeCell ref="EU7:EV7"/>
+    <mergeCell ref="EW7:EZ7"/>
+    <mergeCell ref="BR6:BT6"/>
+    <mergeCell ref="BU6:BW6"/>
+    <mergeCell ref="BX6:BZ6"/>
+    <mergeCell ref="CA6:CC6"/>
+    <mergeCell ref="CG6:CI6"/>
+    <mergeCell ref="CJ6:CL6"/>
+    <mergeCell ref="FO5:FR7"/>
+    <mergeCell ref="FS5:GJ5"/>
+    <mergeCell ref="BX4:CC5"/>
+    <mergeCell ref="CD4:CF6"/>
+    <mergeCell ref="CG4:CL5"/>
+    <mergeCell ref="CM4:CR5"/>
+    <mergeCell ref="CS4:CU6"/>
+    <mergeCell ref="CV4:CX6"/>
+    <mergeCell ref="CM6:CO6"/>
+    <mergeCell ref="CP6:CR6"/>
+    <mergeCell ref="CA7:CA9"/>
+    <mergeCell ref="CB7:CB9"/>
+    <mergeCell ref="CC7:CC9"/>
+    <mergeCell ref="CD7:CD9"/>
+    <mergeCell ref="CE7:CE9"/>
+    <mergeCell ref="CF7:CF9"/>
+    <mergeCell ref="BU7:BU9"/>
+    <mergeCell ref="BV7:BV9"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="GW4:HB6"/>
+    <mergeCell ref="AE5:AM5"/>
+    <mergeCell ref="BO5:BW5"/>
+    <mergeCell ref="CY5:DG5"/>
+    <mergeCell ref="DQ5:DQ9"/>
+    <mergeCell ref="DR5:DR9"/>
+    <mergeCell ref="DS5:DV7"/>
+    <mergeCell ref="DW5:EH5"/>
+    <mergeCell ref="EI5:EI9"/>
+    <mergeCell ref="EJ5:EJ9"/>
+    <mergeCell ref="FG4:FL5"/>
+    <mergeCell ref="FM4:GJ4"/>
+    <mergeCell ref="GK4:GK9"/>
+    <mergeCell ref="GL4:GL9"/>
+    <mergeCell ref="GM4:GP7"/>
+    <mergeCell ref="GQ4:GV6"/>
+    <mergeCell ref="FM5:FM9"/>
+    <mergeCell ref="FN5:FN9"/>
+    <mergeCell ref="FS7:FT7"/>
+    <mergeCell ref="FU7:FX7"/>
+    <mergeCell ref="DE6:DG6"/>
+    <mergeCell ref="DH6:DJ6"/>
+    <mergeCell ref="DK6:DM6"/>
+    <mergeCell ref="DH4:DM5"/>
+    <mergeCell ref="DN4:DP6"/>
+    <mergeCell ref="DQ4:EH4"/>
+    <mergeCell ref="EI4:EZ4"/>
+    <mergeCell ref="FA4:FF5"/>
+    <mergeCell ref="EK5:EN7"/>
+    <mergeCell ref="EO5:EZ5"/>
+    <mergeCell ref="CY6:DA6"/>
+    <mergeCell ref="DB6:DD6"/>
+    <mergeCell ref="DW6:EB6"/>
+    <mergeCell ref="EC6:EH6"/>
+    <mergeCell ref="EO6:ET6"/>
+    <mergeCell ref="DA7:DA9"/>
+    <mergeCell ref="DB7:DB9"/>
+    <mergeCell ref="DC7:DC9"/>
+    <mergeCell ref="DD7:DD9"/>
+    <mergeCell ref="DM7:DM9"/>
+    <mergeCell ref="DN7:DN9"/>
+    <mergeCell ref="DO7:DO9"/>
+    <mergeCell ref="DP7:DP9"/>
+    <mergeCell ref="DE7:DE9"/>
+    <mergeCell ref="DF7:DF9"/>
+    <mergeCell ref="DG7:DG9"/>
+    <mergeCell ref="DH7:DH9"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="Y4:AA6"/>
+    <mergeCell ref="AB4:AD6"/>
+    <mergeCell ref="AE4:AM4"/>
+    <mergeCell ref="AN4:AS5"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="S6:U6"/>
+    <mergeCell ref="V6:X6"/>
+    <mergeCell ref="AE6:AG6"/>
+    <mergeCell ref="AH6:AJ6"/>
+    <mergeCell ref="AK6:AM6"/>
+    <mergeCell ref="AN6:AP6"/>
+    <mergeCell ref="AQ6:AS6"/>
+    <mergeCell ref="M3:AR3"/>
     <mergeCell ref="AW3:CF3"/>
     <mergeCell ref="CG3:DP3"/>
     <mergeCell ref="DQ3:FL3"/>
@@ -6678,264 +6936,6 @@
     <mergeCell ref="BF6:BH6"/>
     <mergeCell ref="BO6:BQ6"/>
     <mergeCell ref="CY4:DG4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="S4:X5"/>
-    <mergeCell ref="Y4:AA6"/>
-    <mergeCell ref="AB4:AD6"/>
-    <mergeCell ref="AE4:AM4"/>
-    <mergeCell ref="AN4:AS5"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="S6:U6"/>
-    <mergeCell ref="V6:X6"/>
-    <mergeCell ref="AE6:AG6"/>
-    <mergeCell ref="AH6:AJ6"/>
-    <mergeCell ref="AK6:AM6"/>
-    <mergeCell ref="AN6:AP6"/>
-    <mergeCell ref="AQ6:AS6"/>
-    <mergeCell ref="M3:AR3"/>
-    <mergeCell ref="DH4:DM5"/>
-    <mergeCell ref="DN4:DP6"/>
-    <mergeCell ref="DQ4:EH4"/>
-    <mergeCell ref="EI4:EZ4"/>
-    <mergeCell ref="FA4:FF5"/>
-    <mergeCell ref="EK5:EN7"/>
-    <mergeCell ref="EO5:EZ5"/>
-    <mergeCell ref="CY6:DA6"/>
-    <mergeCell ref="DB6:DD6"/>
-    <mergeCell ref="DW6:EB6"/>
-    <mergeCell ref="EC6:EH6"/>
-    <mergeCell ref="EO6:ET6"/>
-    <mergeCell ref="DA7:DA9"/>
-    <mergeCell ref="DB7:DB9"/>
-    <mergeCell ref="DC7:DC9"/>
-    <mergeCell ref="DD7:DD9"/>
-    <mergeCell ref="DM7:DM9"/>
-    <mergeCell ref="DN7:DN9"/>
-    <mergeCell ref="DO7:DO9"/>
-    <mergeCell ref="DP7:DP9"/>
-    <mergeCell ref="DE7:DE9"/>
-    <mergeCell ref="DF7:DF9"/>
-    <mergeCell ref="DG7:DG9"/>
-    <mergeCell ref="DH7:DH9"/>
-    <mergeCell ref="AW6:AY6"/>
-    <mergeCell ref="GW4:HB6"/>
-    <mergeCell ref="AE5:AM5"/>
-    <mergeCell ref="BO5:BW5"/>
-    <mergeCell ref="CY5:DG5"/>
-    <mergeCell ref="DQ5:DQ9"/>
-    <mergeCell ref="DR5:DR9"/>
-    <mergeCell ref="DS5:DV7"/>
-    <mergeCell ref="DW5:EH5"/>
-    <mergeCell ref="EI5:EI9"/>
-    <mergeCell ref="EJ5:EJ9"/>
-    <mergeCell ref="FG4:FL5"/>
-    <mergeCell ref="FM4:GJ4"/>
-    <mergeCell ref="GK4:GK9"/>
-    <mergeCell ref="GL4:GL9"/>
-    <mergeCell ref="GM4:GP7"/>
-    <mergeCell ref="GQ4:GV6"/>
-    <mergeCell ref="FM5:FM9"/>
-    <mergeCell ref="FN5:FN9"/>
-    <mergeCell ref="FS7:FT7"/>
-    <mergeCell ref="FU7:FX7"/>
-    <mergeCell ref="DE6:DG6"/>
-    <mergeCell ref="DH6:DJ6"/>
-    <mergeCell ref="DK6:DM6"/>
-    <mergeCell ref="BR6:BT6"/>
-    <mergeCell ref="BU6:BW6"/>
-    <mergeCell ref="BX6:BZ6"/>
-    <mergeCell ref="CA6:CC6"/>
-    <mergeCell ref="CG6:CI6"/>
-    <mergeCell ref="CJ6:CL6"/>
-    <mergeCell ref="FO5:FR7"/>
-    <mergeCell ref="FS5:GJ5"/>
-    <mergeCell ref="BX4:CC5"/>
-    <mergeCell ref="CD4:CF6"/>
-    <mergeCell ref="CG4:CL5"/>
-    <mergeCell ref="CM4:CR5"/>
-    <mergeCell ref="CS4:CU6"/>
-    <mergeCell ref="CV4:CX6"/>
-    <mergeCell ref="CM6:CO6"/>
-    <mergeCell ref="CP6:CR6"/>
-    <mergeCell ref="CA7:CA9"/>
-    <mergeCell ref="CB7:CB9"/>
-    <mergeCell ref="CC7:CC9"/>
-    <mergeCell ref="CD7:CD9"/>
-    <mergeCell ref="CE7:CE9"/>
-    <mergeCell ref="CF7:CF9"/>
-    <mergeCell ref="BU7:BU9"/>
-    <mergeCell ref="BV7:BV9"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="T7:T9"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="FY6:GD6"/>
-    <mergeCell ref="GE6:GJ6"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="Q7:Q9"/>
-    <mergeCell ref="R7:R9"/>
-    <mergeCell ref="EU6:EZ6"/>
-    <mergeCell ref="FA6:FB7"/>
-    <mergeCell ref="FC6:FF7"/>
-    <mergeCell ref="FG6:FH7"/>
-    <mergeCell ref="FI6:FL7"/>
-    <mergeCell ref="FS6:FX6"/>
-    <mergeCell ref="EU7:EV7"/>
-    <mergeCell ref="EW7:EZ7"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AQ7:AQ9"/>
-    <mergeCell ref="AR7:AR9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AT7:AT9"/>
-    <mergeCell ref="AU7:AU9"/>
-    <mergeCell ref="AV7:AV9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AP7:AP9"/>
-    <mergeCell ref="BC7:BC9"/>
-    <mergeCell ref="BD7:BD9"/>
-    <mergeCell ref="BE7:BE9"/>
-    <mergeCell ref="BF7:BF9"/>
-    <mergeCell ref="BG7:BG9"/>
-    <mergeCell ref="BH7:BH9"/>
-    <mergeCell ref="AW7:AW9"/>
-    <mergeCell ref="AX7:AX9"/>
-    <mergeCell ref="AY7:AY9"/>
-    <mergeCell ref="AZ7:AZ9"/>
-    <mergeCell ref="BA7:BA9"/>
-    <mergeCell ref="BB7:BB9"/>
-    <mergeCell ref="BO7:BO9"/>
-    <mergeCell ref="BP7:BP9"/>
-    <mergeCell ref="BQ7:BQ9"/>
-    <mergeCell ref="BR7:BR9"/>
-    <mergeCell ref="BS7:BS9"/>
-    <mergeCell ref="BT7:BT9"/>
-    <mergeCell ref="BI7:BI9"/>
-    <mergeCell ref="BJ7:BJ9"/>
-    <mergeCell ref="BK7:BK9"/>
-    <mergeCell ref="BL7:BL9"/>
-    <mergeCell ref="BM7:BM9"/>
-    <mergeCell ref="BN7:BN9"/>
-    <mergeCell ref="BW7:BW9"/>
-    <mergeCell ref="BX7:BX9"/>
-    <mergeCell ref="BY7:BY9"/>
-    <mergeCell ref="BZ7:BZ9"/>
-    <mergeCell ref="CM7:CM9"/>
-    <mergeCell ref="CN7:CN9"/>
-    <mergeCell ref="CO7:CO9"/>
-    <mergeCell ref="CP7:CP9"/>
-    <mergeCell ref="CQ7:CQ9"/>
-    <mergeCell ref="CR7:CR9"/>
-    <mergeCell ref="CG7:CG9"/>
-    <mergeCell ref="CH7:CH9"/>
-    <mergeCell ref="CI7:CI9"/>
-    <mergeCell ref="CJ7:CJ9"/>
-    <mergeCell ref="CK7:CK9"/>
-    <mergeCell ref="CL7:CL9"/>
-    <mergeCell ref="CY7:CY9"/>
-    <mergeCell ref="CZ7:CZ9"/>
-    <mergeCell ref="CS7:CS9"/>
-    <mergeCell ref="CT7:CT9"/>
-    <mergeCell ref="CU7:CU9"/>
-    <mergeCell ref="CV7:CV9"/>
-    <mergeCell ref="CW7:CW9"/>
-    <mergeCell ref="CX7:CX9"/>
-    <mergeCell ref="DI7:DI9"/>
-    <mergeCell ref="DJ7:DJ9"/>
-    <mergeCell ref="GW7:GX7"/>
-    <mergeCell ref="GY7:HB7"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="DS8:DS9"/>
-    <mergeCell ref="DT8:DV8"/>
-    <mergeCell ref="DW8:DW9"/>
-    <mergeCell ref="DX8:DX9"/>
-    <mergeCell ref="DY8:DY9"/>
-    <mergeCell ref="FY7:FZ7"/>
-    <mergeCell ref="GA7:GD7"/>
-    <mergeCell ref="GE7:GF7"/>
-    <mergeCell ref="GG7:GJ7"/>
-    <mergeCell ref="GQ7:GR7"/>
-    <mergeCell ref="GS7:GV7"/>
-    <mergeCell ref="DW7:DX7"/>
-    <mergeCell ref="DY7:EB7"/>
-    <mergeCell ref="EC7:ED7"/>
-    <mergeCell ref="EE7:EH7"/>
-    <mergeCell ref="EO7:EP7"/>
-    <mergeCell ref="EQ7:ET7"/>
-    <mergeCell ref="DK7:DK9"/>
-    <mergeCell ref="DL7:DL9"/>
-    <mergeCell ref="EL8:EN8"/>
-    <mergeCell ref="EO8:EO9"/>
-    <mergeCell ref="EP8:EP9"/>
-    <mergeCell ref="EQ8:EQ9"/>
-    <mergeCell ref="ER8:ET8"/>
-    <mergeCell ref="EU8:EU9"/>
-    <mergeCell ref="DZ8:EB8"/>
-    <mergeCell ref="EC8:EC9"/>
-    <mergeCell ref="ED8:ED9"/>
-    <mergeCell ref="EE8:EE9"/>
-    <mergeCell ref="EF8:EH8"/>
-    <mergeCell ref="EK8:EK9"/>
-    <mergeCell ref="FD8:FF8"/>
-    <mergeCell ref="FG8:FG9"/>
-    <mergeCell ref="FH8:FH9"/>
-    <mergeCell ref="FI8:FI9"/>
-    <mergeCell ref="FJ8:FL8"/>
-    <mergeCell ref="FO8:FO9"/>
-    <mergeCell ref="EV8:EV9"/>
-    <mergeCell ref="EW8:EW9"/>
-    <mergeCell ref="EX8:EZ8"/>
-    <mergeCell ref="FA8:FA9"/>
-    <mergeCell ref="FB8:FB9"/>
-    <mergeCell ref="FC8:FC9"/>
-    <mergeCell ref="GT8:GV8"/>
-    <mergeCell ref="GW8:GW9"/>
-    <mergeCell ref="GX8:GX9"/>
-    <mergeCell ref="GY8:GY9"/>
-    <mergeCell ref="GZ8:HB8"/>
-    <mergeCell ref="GH8:GJ8"/>
-    <mergeCell ref="GM8:GM9"/>
-    <mergeCell ref="GN8:GP8"/>
-    <mergeCell ref="GQ8:GQ9"/>
-    <mergeCell ref="GR8:GR9"/>
-    <mergeCell ref="GS8:GS9"/>
-    <mergeCell ref="FZ8:FZ9"/>
-    <mergeCell ref="GA8:GA9"/>
-    <mergeCell ref="GB8:GD8"/>
-    <mergeCell ref="GE8:GE9"/>
-    <mergeCell ref="GF8:GF9"/>
-    <mergeCell ref="GG8:GG9"/>
-    <mergeCell ref="FP8:FR8"/>
-    <mergeCell ref="FS8:FS9"/>
-    <mergeCell ref="FT8:FT9"/>
-    <mergeCell ref="FU8:FU9"/>
-    <mergeCell ref="FV8:FX8"/>
-    <mergeCell ref="FY8:FY9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
